--- a/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
+++ b/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5311" uniqueCount="679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5311" uniqueCount="678">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T13:09:12+00:00</t>
+    <t>2026-06-22T13:13:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -882,9 +882,6 @@
   </si>
   <si>
     <t>Will generally be set to show that the immunization has been completed or not done.  This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
-  </si>
-  <si>
-    <t>completed</t>
   </si>
   <si>
     <t>required</t>
@@ -9159,28 +9156,28 @@
         <v>79</v>
       </c>
       <c r="S58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X58" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="T58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X58" t="s" s="2">
+      <c r="Y58" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="Y58" t="s" s="2">
+      <c r="Z58" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>79</v>
@@ -9213,16 +9210,16 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AL58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM58" t="s" s="2">
+      <c r="AN58" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>79</v>
@@ -9230,10 +9227,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9259,13 +9256,13 @@
         <v>195</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9291,14 +9288,14 @@
         <v>79</v>
       </c>
       <c r="X59" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="Y59" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="Y59" t="s" s="2">
+      <c r="Z59" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="Z59" t="s" s="2">
-        <v>291</v>
-      </c>
       <c r="AA59" t="s" s="2">
         <v>79</v>
       </c>
@@ -9315,7 +9312,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9330,13 +9327,13 @@
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>79</v>
@@ -9347,10 +9344,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9376,10 +9373,10 @@
         <v>195</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9409,11 +9406,11 @@
         <v>114</v>
       </c>
       <c r="Y60" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="Z60" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="Z60" t="s" s="2">
-        <v>298</v>
-      </c>
       <c r="AA60" t="s" s="2">
         <v>79</v>
       </c>
@@ -9430,7 +9427,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>90</v>
@@ -9445,27 +9442,27 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AL60" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="AL60" t="s" s="2">
+      <c r="AM60" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="AM60" t="s" s="2">
+      <c r="AN60" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="AN60" t="s" s="2">
+      <c r="AO60" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>303</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9577,10 +9574,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9694,10 +9691,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9720,19 +9717,19 @@
         <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>79</v>
@@ -9769,10 +9766,10 @@
         <v>79</v>
       </c>
       <c r="AB63" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AC63" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>79</v>
@@ -9781,7 +9778,7 @@
         <v>139</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9799,10 +9796,10 @@
         <v>79</v>
       </c>
       <c r="AL63" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>79</v>
@@ -9813,13 +9810,13 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="C64" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="C64" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>79</v>
@@ -9841,19 +9838,19 @@
         <v>91</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>79</v>
@@ -9878,11 +9875,11 @@
         <v>79</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>79</v>
@@ -9900,7 +9897,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9918,10 +9915,10 @@
         <v>79</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AM64" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>79</v>
@@ -9932,13 +9929,13 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="C65" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="C65" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>79</v>
@@ -9960,19 +9957,19 @@
         <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="N65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>79</v>
@@ -9997,11 +9994,11 @@
         <v>79</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>79</v>
@@ -10019,7 +10016,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10037,10 +10034,10 @@
         <v>79</v>
       </c>
       <c r="AL65" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AM65" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>79</v>
@@ -10051,10 +10048,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="B66" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10166,10 +10163,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="B67" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10283,10 +10280,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="B68" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10312,16 +10309,16 @@
         <v>104</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="N68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>79</v>
@@ -10370,7 +10367,7 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10388,10 +10385,10 @@
         <v>79</v>
       </c>
       <c r="AL68" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AM68" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>79</v>
@@ -10402,10 +10399,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="B69" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10431,13 +10428,13 @@
         <v>151</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10487,7 +10484,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10505,10 +10502,10 @@
         <v>79</v>
       </c>
       <c r="AL69" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AM69" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>79</v>
@@ -10519,10 +10516,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="B70" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10548,14 +10545,14 @@
         <v>110</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>79</v>
@@ -10604,7 +10601,7 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10622,10 +10619,10 @@
         <v>79</v>
       </c>
       <c r="AL70" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AM70" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>79</v>
@@ -10636,10 +10633,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="B71" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10665,14 +10662,14 @@
         <v>151</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>79</v>
@@ -10721,7 +10718,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10739,10 +10736,10 @@
         <v>79</v>
       </c>
       <c r="AL71" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AM71" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>79</v>
@@ -10753,10 +10750,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="B72" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10779,19 +10776,19 @@
         <v>91</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="N72" t="s" s="2">
+      <c r="O72" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>79</v>
@@ -10840,7 +10837,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10858,10 +10855,10 @@
         <v>79</v>
       </c>
       <c r="AL72" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AM72" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>79</v>
@@ -10872,10 +10869,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10901,16 +10898,16 @@
         <v>151</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="N73" t="s" s="2">
+      <c r="O73" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>79</v>
@@ -10959,7 +10956,7 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10977,10 +10974,10 @@
         <v>79</v>
       </c>
       <c r="AL73" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AM73" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>79</v>
@@ -10991,10 +10988,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11017,13 +11014,13 @@
         <v>91</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11074,7 +11071,7 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>90</v>
@@ -11089,16 +11086,16 @@
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AL74" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AL74" t="s" s="2">
+      <c r="AM74" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="AM74" t="s" s="2">
+      <c r="AN74" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>79</v>
@@ -11106,10 +11103,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11132,13 +11129,13 @@
         <v>79</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11189,7 +11186,7 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11204,16 +11201,16 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AL75" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="AL75" t="s" s="2">
+      <c r="AM75" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AM75" t="s" s="2">
+      <c r="AN75" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>79</v>
@@ -11221,10 +11218,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11247,16 +11244,16 @@
         <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="M76" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11294,17 +11291,17 @@
         <v>79</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AC76" s="2"/>
       <c r="AD76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>90</v>
@@ -11319,30 +11316,30 @@
         <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AL76" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AL76" t="s" s="2">
+      <c r="AM76" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AM76" t="s" s="2">
+      <c r="AN76" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="AN76" t="s" s="2">
+      <c r="AO76" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>405</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="C77" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>79</v>
@@ -11364,16 +11361,16 @@
         <v>91</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="M77" t="s" s="2">
-        <v>409</v>
-      </c>
       <c r="N77" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11423,7 +11420,7 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>90</v>
@@ -11438,27 +11435,27 @@
         <v>102</v>
       </c>
       <c r="AK77" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AL77" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AL77" t="s" s="2">
+      <c r="AM77" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AM77" t="s" s="2">
+      <c r="AN77" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="AN77" t="s" s="2">
+      <c r="AO77" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>405</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="B78" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11484,10 +11481,10 @@
         <v>151</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11570,10 +11567,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="B79" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11683,13 +11680,13 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="C80" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="C80" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="D80" t="s" s="2">
         <v>79</v>
@@ -11711,13 +11708,13 @@
         <v>79</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="L80" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="L80" t="s" s="2">
+      <c r="M80" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11800,10 +11797,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="B81" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11915,10 +11912,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="B82" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12030,10 +12027,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="B83" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12073,7 +12070,7 @@
       </c>
       <c r="Q83" s="2"/>
       <c r="R83" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="S83" t="s" s="2">
         <v>79</v>
@@ -12147,10 +12144,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="B84" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12210,7 +12207,7 @@
       </c>
       <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>79</v>
@@ -12260,10 +12257,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="B85" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12286,13 +12283,13 @@
         <v>79</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12343,7 +12340,7 @@
         <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12375,10 +12372,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12401,13 +12398,13 @@
         <v>79</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12458,7 +12455,7 @@
         <v>79</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12479,10 +12476,10 @@
         <v>79</v>
       </c>
       <c r="AM86" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AN86" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>79</v>
@@ -12490,10 +12487,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12516,16 +12513,16 @@
         <v>91</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12575,7 +12572,7 @@
         <v>79</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12593,13 +12590,13 @@
         <v>79</v>
       </c>
       <c r="AL87" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AM87" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="AM87" t="s" s="2">
+      <c r="AN87" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>79</v>
@@ -12607,10 +12604,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12636,13 +12633,13 @@
         <v>195</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12668,10 +12665,10 @@
         <v>79</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="Z88" t="s" s="2">
         <v>231</v>
@@ -12692,7 +12689,7 @@
         <v>79</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12710,13 +12707,13 @@
         <v>79</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>79</v>
@@ -12724,10 +12721,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12750,13 +12747,13 @@
         <v>79</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="L89" t="s" s="2">
+      <c r="M89" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12807,7 +12804,7 @@
         <v>79</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12822,16 +12819,16 @@
         <v>102</v>
       </c>
       <c r="AK89" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AL89" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="AL89" t="s" s="2">
+      <c r="AM89" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="AM89" t="s" s="2">
+      <c r="AN89" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>79</v>
@@ -12839,10 +12836,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12865,13 +12862,13 @@
         <v>79</v>
       </c>
       <c r="K90" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="L90" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="L90" t="s" s="2">
+      <c r="M90" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12922,7 +12919,7 @@
         <v>79</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12940,24 +12937,24 @@
         <v>79</v>
       </c>
       <c r="AL90" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AM90" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="AM90" t="s" s="2">
+      <c r="AN90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO90" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO90" t="s" s="2">
-        <v>468</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12983,10 +12980,10 @@
         <v>151</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -13037,7 +13034,7 @@
         <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13055,24 +13052,24 @@
         <v>79</v>
       </c>
       <c r="AL91" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AM91" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="AM91" t="s" s="2">
+      <c r="AN91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO91" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>474</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13095,13 +13092,13 @@
         <v>79</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="L92" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="L92" t="s" s="2">
+      <c r="M92" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13152,7 +13149,7 @@
         <v>79</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13170,10 +13167,10 @@
         <v>79</v>
       </c>
       <c r="AL92" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AM92" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="AM92" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>79</v>
@@ -13184,10 +13181,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13213,10 +13210,10 @@
         <v>195</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13243,11 +13240,11 @@
         <v>79</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Y93" s="2"/>
       <c r="Z93" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>79</v>
@@ -13265,7 +13262,7 @@
         <v>79</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13283,24 +13280,24 @@
         <v>79</v>
       </c>
       <c r="AL93" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AM93" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="AM93" t="s" s="2">
+      <c r="AN93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO93" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>487</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13326,10 +13323,10 @@
         <v>195</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13356,11 +13353,11 @@
         <v>79</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Y94" s="2"/>
       <c r="Z94" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>79</v>
@@ -13378,7 +13375,7 @@
         <v>79</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13396,24 +13393,24 @@
         <v>79</v>
       </c>
       <c r="AL94" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AM94" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="AM94" t="s" s="2">
+      <c r="AN94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO94" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>494</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13436,13 +13433,13 @@
         <v>79</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="M95" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13493,7 +13490,7 @@
         <v>79</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13511,10 +13508,10 @@
         <v>79</v>
       </c>
       <c r="AL95" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AM95" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>79</v>
@@ -13525,10 +13522,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13551,13 +13548,13 @@
         <v>91</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="L96" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="L96" t="s" s="2">
+      <c r="M96" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13596,7 +13593,7 @@
         <v>79</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AC96" s="2"/>
       <c r="AD96" t="s" s="2">
@@ -13606,7 +13603,7 @@
         <v>139</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13621,13 +13618,13 @@
         <v>102</v>
       </c>
       <c r="AK96" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AL96" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="AL96" t="s" s="2">
+      <c r="AM96" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>79</v>
@@ -13638,10 +13635,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13753,10 +13750,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13870,14 +13867,14 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -13899,10 +13896,10 @@
         <v>135</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>171</v>
@@ -13957,7 +13954,7 @@
         <v>79</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -13989,10 +13986,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14018,10 +14015,10 @@
         <v>195</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -14048,14 +14045,14 @@
         <v>79</v>
       </c>
       <c r="X100" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="Y100" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="Y100" t="s" s="2">
+      <c r="Z100" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="Z100" t="s" s="2">
-        <v>521</v>
-      </c>
       <c r="AA100" t="s" s="2">
         <v>79</v>
       </c>
@@ -14072,7 +14069,7 @@
         <v>79</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14087,13 +14084,13 @@
         <v>102</v>
       </c>
       <c r="AK100" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM100" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="AL100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>79</v>
@@ -14104,10 +14101,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14130,16 +14127,16 @@
         <v>91</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="L101" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="M101" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14189,7 +14186,7 @@
         <v>79</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>90</v>
@@ -14204,16 +14201,16 @@
         <v>102</v>
       </c>
       <c r="AK101" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM101" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="AL101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM101" t="s" s="2">
+      <c r="AN101" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>79</v>
@@ -14221,13 +14218,13 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="C102" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="C102" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="D102" t="s" s="2">
         <v>79</v>
@@ -14249,13 +14246,13 @@
         <v>91</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14306,7 +14303,7 @@
         <v>79</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14321,13 +14318,13 @@
         <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AL102" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="AL102" t="s" s="2">
+      <c r="AM102" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>79</v>
@@ -14338,10 +14335,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14453,10 +14450,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14570,14 +14567,14 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -14599,10 +14596,10 @@
         <v>135</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="N105" t="s" s="2">
         <v>171</v>
@@ -14657,7 +14654,7 @@
         <v>79</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14689,10 +14686,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14718,10 +14715,10 @@
         <v>195</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14733,7 +14730,7 @@
         <v>79</v>
       </c>
       <c r="S106" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="T106" t="s" s="2">
         <v>79</v>
@@ -14748,14 +14745,14 @@
         <v>79</v>
       </c>
       <c r="X106" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="Y106" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="Y106" t="s" s="2">
+      <c r="Z106" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="Z106" t="s" s="2">
-        <v>521</v>
-      </c>
       <c r="AA106" t="s" s="2">
         <v>79</v>
       </c>
@@ -14772,7 +14769,7 @@
         <v>79</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -14787,13 +14784,13 @@
         <v>102</v>
       </c>
       <c r="AK106" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM106" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="AL106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>79</v>
@@ -14804,10 +14801,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14830,16 +14827,16 @@
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="N107" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14889,7 +14886,7 @@
         <v>79</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>90</v>
@@ -14904,16 +14901,16 @@
         <v>102</v>
       </c>
       <c r="AK107" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM107" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="AL107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM107" t="s" s="2">
+      <c r="AN107" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>79</v>
@@ -14921,10 +14918,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14947,13 +14944,13 @@
         <v>91</v>
       </c>
       <c r="K108" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="L108" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="L108" t="s" s="2">
+      <c r="M108" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15004,7 +15001,7 @@
         <v>79</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15019,13 +15016,13 @@
         <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AL108" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="AL108" t="s" s="2">
+      <c r="AM108" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="AM108" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>79</v>
@@ -15036,10 +15033,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15151,10 +15148,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15268,10 +15265,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15294,16 +15291,16 @@
         <v>91</v>
       </c>
       <c r="K111" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="L111" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="L111" t="s" s="2">
+      <c r="M111" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="M111" t="s" s="2">
+      <c r="N111" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -15353,7 +15350,7 @@
         <v>79</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15374,7 +15371,7 @@
         <v>133</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>79</v>
@@ -15385,10 +15382,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15411,13 +15408,13 @@
         <v>91</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -15468,7 +15465,7 @@
         <v>79</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -15489,7 +15486,7 @@
         <v>133</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>79</v>
@@ -15500,10 +15497,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15526,13 +15523,13 @@
         <v>91</v>
       </c>
       <c r="K113" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="L113" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="L113" t="s" s="2">
+      <c r="M113" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -15583,7 +15580,7 @@
         <v>79</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>90</v>
@@ -15604,7 +15601,7 @@
         <v>133</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>79</v>
@@ -15615,10 +15612,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15644,10 +15641,10 @@
         <v>195</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>571</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -15674,14 +15671,14 @@
         <v>79</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Y114" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="Z114" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="Z114" t="s" s="2">
-        <v>573</v>
-      </c>
       <c r="AA114" t="s" s="2">
         <v>79</v>
       </c>
@@ -15698,7 +15695,7 @@
         <v>79</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -15713,13 +15710,13 @@
         <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM114" t="s" s="2">
         <v>574</v>
-      </c>
-      <c r="AL114" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM114" t="s" s="2">
-        <v>575</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>79</v>
@@ -15730,10 +15727,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15756,13 +15753,13 @@
         <v>79</v>
       </c>
       <c r="K115" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="L115" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="L115" t="s" s="2">
+      <c r="M115" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -15813,7 +15810,7 @@
         <v>79</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -15828,7 +15825,7 @@
         <v>102</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AL115" t="s" s="2">
         <v>79</v>
@@ -15845,10 +15842,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15871,23 +15868,23 @@
         <v>91</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="M116" t="s" s="2">
+      <c r="N116" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q116" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="R116" t="s" s="2">
         <v>79</v>
@@ -15932,7 +15929,7 @@
         <v>79</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -15950,7 +15947,7 @@
         <v>79</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>133</v>
@@ -15964,10 +15961,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15993,10 +15990,10 @@
         <v>195</v>
       </c>
       <c r="L117" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M117" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -16023,14 +16020,14 @@
         <v>79</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Y117" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="Z117" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="Z117" t="s" s="2">
-        <v>591</v>
-      </c>
       <c r="AA117" t="s" s="2">
         <v>79</v>
       </c>
@@ -16047,7 +16044,7 @@
         <v>79</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16079,10 +16076,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16105,13 +16102,13 @@
         <v>79</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16162,7 +16159,7 @@
         <v>79</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16174,7 +16171,7 @@
         <v>79</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>79</v>
@@ -16194,10 +16191,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16309,10 +16306,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16426,14 +16423,14 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
@@ -16455,10 +16452,10 @@
         <v>135</v>
       </c>
       <c r="L121" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="M121" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="N121" t="s" s="2">
         <v>171</v>
@@ -16513,7 +16510,7 @@
         <v>79</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -16545,10 +16542,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16574,10 +16571,10 @@
         <v>151</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -16628,7 +16625,7 @@
         <v>79</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -16646,7 +16643,7 @@
         <v>79</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>133</v>
@@ -16660,10 +16657,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16689,10 +16686,10 @@
         <v>104</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>605</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -16743,7 +16740,7 @@
         <v>79</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -16775,10 +16772,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16801,13 +16798,13 @@
         <v>79</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -16858,7 +16855,7 @@
         <v>79</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -16876,7 +16873,7 @@
         <v>79</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>133</v>
@@ -16890,10 +16887,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16916,13 +16913,13 @@
         <v>79</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -16973,7 +16970,7 @@
         <v>79</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -16991,7 +16988,7 @@
         <v>79</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>133</v>
@@ -17005,10 +17002,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17034,10 +17031,10 @@
         <v>195</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -17064,14 +17061,14 @@
         <v>79</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Y126" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="Z126" t="s" s="2">
         <v>617</v>
       </c>
-      <c r="Z126" t="s" s="2">
-        <v>618</v>
-      </c>
       <c r="AA126" t="s" s="2">
         <v>79</v>
       </c>
@@ -17088,7 +17085,7 @@
         <v>79</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17106,7 +17103,7 @@
         <v>79</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>133</v>
@@ -17120,10 +17117,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17149,10 +17146,10 @@
         <v>195</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="M127" t="s" s="2">
         <v>621</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>622</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -17179,14 +17176,14 @@
         <v>79</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Y127" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="Z127" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="Z127" t="s" s="2">
-        <v>624</v>
-      </c>
       <c r="AA127" t="s" s="2">
         <v>79</v>
       </c>
@@ -17203,7 +17200,7 @@
         <v>79</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17235,10 +17232,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17261,16 +17258,16 @@
         <v>79</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="L128" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="M128" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="M128" t="s" s="2">
+      <c r="N128" t="s" s="2">
         <v>627</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>628</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -17320,7 +17317,7 @@
         <v>79</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -17338,10 +17335,10 @@
         <v>79</v>
       </c>
       <c r="AL128" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="AM128" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="AM128" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>79</v>
@@ -17352,10 +17349,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17467,10 +17464,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17584,14 +17581,14 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
@@ -17613,10 +17610,10 @@
         <v>135</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="M131" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="N131" t="s" s="2">
         <v>171</v>
@@ -17671,7 +17668,7 @@
         <v>79</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -17703,10 +17700,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17729,13 +17726,13 @@
         <v>79</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="M132" t="s" s="2">
         <v>635</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>636</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -17786,7 +17783,7 @@
         <v>79</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -17804,10 +17801,10 @@
         <v>79</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>79</v>
@@ -17818,10 +17815,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17844,13 +17841,13 @@
         <v>79</v>
       </c>
       <c r="K133" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="L133" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="L133" t="s" s="2">
+      <c r="M133" t="s" s="2">
         <v>640</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>641</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -17901,7 +17898,7 @@
         <v>79</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -17919,10 +17916,10 @@
         <v>79</v>
       </c>
       <c r="AL133" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AM133" t="s" s="2">
         <v>642</v>
-      </c>
-      <c r="AM133" t="s" s="2">
-        <v>643</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>79</v>
@@ -17933,10 +17930,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17959,13 +17956,13 @@
         <v>79</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>646</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -18016,7 +18013,7 @@
         <v>79</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -18034,10 +18031,10 @@
         <v>79</v>
       </c>
       <c r="AL134" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="AM134" t="s" s="2">
         <v>647</v>
-      </c>
-      <c r="AM134" t="s" s="2">
-        <v>648</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>79</v>
@@ -18048,10 +18045,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18074,13 +18071,13 @@
         <v>79</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="M135" t="s" s="2">
         <v>650</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>651</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -18131,7 +18128,7 @@
         <v>79</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18163,10 +18160,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18278,10 +18275,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18395,14 +18392,14 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -18424,10 +18421,10 @@
         <v>135</v>
       </c>
       <c r="L138" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="M138" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="M138" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="N138" t="s" s="2">
         <v>171</v>
@@ -18482,7 +18479,7 @@
         <v>79</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -18514,10 +18511,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18543,10 +18540,10 @@
         <v>151</v>
       </c>
       <c r="L139" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="M139" t="s" s="2">
         <v>656</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>657</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -18573,11 +18570,11 @@
         <v>79</v>
       </c>
       <c r="X139" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Y139" s="2"/>
       <c r="Z139" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>79</v>
@@ -18595,7 +18592,7 @@
         <v>79</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -18627,10 +18624,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18653,13 +18650,13 @@
         <v>79</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="L140" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="M140" t="s" s="2">
         <v>660</v>
-      </c>
-      <c r="M140" t="s" s="2">
-        <v>661</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -18710,7 +18707,7 @@
         <v>79</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -18742,10 +18739,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18771,10 +18768,10 @@
         <v>195</v>
       </c>
       <c r="L141" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="M141" t="s" s="2">
         <v>663</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>664</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -18804,11 +18801,11 @@
         <v>114</v>
       </c>
       <c r="Y141" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="Z141" t="s" s="2">
         <v>665</v>
       </c>
-      <c r="Z141" t="s" s="2">
-        <v>666</v>
-      </c>
       <c r="AA141" t="s" s="2">
         <v>79</v>
       </c>
@@ -18825,7 +18822,7 @@
         <v>79</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -18857,10 +18854,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18883,16 +18880,16 @@
         <v>79</v>
       </c>
       <c r="K142" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="L142" t="s" s="2">
         <v>668</v>
       </c>
-      <c r="L142" t="s" s="2">
+      <c r="M142" t="s" s="2">
         <v>669</v>
       </c>
-      <c r="M142" t="s" s="2">
+      <c r="N142" t="s" s="2">
         <v>670</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>671</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -18930,7 +18927,7 @@
         <v>79</v>
       </c>
       <c r="AB142" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AC142" s="2"/>
       <c r="AD142" t="s" s="2">
@@ -18940,7 +18937,7 @@
         <v>139</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>90</v>
@@ -18972,13 +18969,13 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="B143" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="C143" t="s" s="2">
         <v>672</v>
-      </c>
-      <c r="B143" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="C143" t="s" s="2">
-        <v>673</v>
       </c>
       <c r="D143" t="s" s="2">
         <v>79</v>
@@ -19000,16 +18997,16 @@
         <v>79</v>
       </c>
       <c r="K143" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="L143" t="s" s="2">
         <v>674</v>
       </c>
-      <c r="L143" t="s" s="2">
-        <v>675</v>
-      </c>
       <c r="M143" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="N143" t="s" s="2">
         <v>670</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>671</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -19059,7 +19056,7 @@
         <v>79</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>90</v>
@@ -19091,10 +19088,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19117,16 +19114,16 @@
         <v>79</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="L144" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="M144" t="s" s="2">
         <v>677</v>
       </c>
-      <c r="M144" t="s" s="2">
-        <v>678</v>
-      </c>
       <c r="N144" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -19176,7 +19173,7 @@
         <v>79</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>

--- a/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
+++ b/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T13:13:25+00:00</t>
+    <t>2026-06-22T13:33:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -854,7 +854,7 @@
 </t>
   </si>
   <si>
-    <t>Identifiant</t>
+    <t>Identifier of the immunization</t>
   </si>
   <si>
     <t>A unique identifier assigned to this immunization record.</t>

--- a/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
+++ b/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T13:33:44+00:00</t>
+    <t>2026-06-22T13:44:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2044,7 +2044,7 @@
     <t>Immunization.protocolApplied.series</t>
   </si>
   <si>
-    <t>Name of vaccine series</t>
+    <t>Type de vaccination : BOOSTER (Rappel de vaccin) | IMMUNIZ (Vaccination sans autre précision) | INITIMMUNIZ (1ère série vaccinante)</t>
   </si>
   <si>
     <t>One possible path to achieve presumed immunity against a disease - within the context of an authority.</t>

--- a/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
+++ b/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T13:44:32+00:00</t>
+    <t>2026-06-22T13:47:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
+++ b/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5311" uniqueCount="678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5274" uniqueCount="673">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T13:47:42+00:00</t>
+    <t>2026-06-22T14:04:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -764,22 +764,6 @@
   </si>
   <si>
     <t>Immunization.extension:informationSource.value[x]</t>
-  </si>
-  <si>
-    <t>Immunization.extension:productName</t>
-  </si>
-  <si>
-    <t>productName</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://profiles.ihe.net/PHARM/MPD/StructureDefinition/ihe-ext-medication-productname|1.0.0-comment-2}
-</t>
-  </si>
-  <si>
-    <t>Nom de marque du produit.</t>
-  </si>
-  <si>
-    <t>Name of the medicinal product. This is typically the name of a real product as registered. This element should not contain display names of virtual product concepts.</t>
   </si>
   <si>
     <t>Immunization.extension:basedOnRequestR5</t>
@@ -2422,7 +2406,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO144"/>
+  <dimension ref="A1:AO143"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="66.5703125" customWidth="true" bestFit="true"/>
@@ -3420,7 +3404,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>81</v>
@@ -8189,7 +8173,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>90</v>
@@ -8212,7 +8196,9 @@
       <c r="M50" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="N50" s="2"/>
+      <c r="N50" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>79</v>
@@ -8293,14 +8279,12 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>247</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>79</v>
       </c>
@@ -8321,17 +8305,15 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>248</v>
+        <v>151</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>249</v>
+        <v>152</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>79</v>
@@ -8380,19 +8362,19 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>141</v>
+        <v>79</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>79</v>
@@ -8401,7 +8383,7 @@
         <v>79</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>79</v>
+        <v>155</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>79</v>
@@ -8412,10 +8394,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8426,7 +8408,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>79</v>
@@ -8438,13 +8420,13 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8483,31 +8465,31 @@
         <v>79</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>79</v>
@@ -8516,7 +8498,7 @@
         <v>79</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>155</v>
+        <v>79</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>79</v>
@@ -8527,10 +8509,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>157</v>
+        <v>208</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8538,10 +8520,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>79</v>
@@ -8553,22 +8535,24 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q53" s="2"/>
       <c r="R53" t="s" s="2">
-        <v>79</v>
+        <v>250</v>
       </c>
       <c r="S53" t="s" s="2">
         <v>79</v>
@@ -8598,31 +8582,31 @@
         <v>79</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>141</v>
+        <v>79</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>79</v>
@@ -8631,7 +8615,7 @@
         <v>79</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>79</v>
@@ -8642,10 +8626,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8668,16 +8652,16 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>104</v>
+        <v>252</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>174</v>
+        <v>253</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>175</v>
+        <v>254</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>176</v>
+        <v>255</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8685,7 +8669,7 @@
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
-        <v>255</v>
+        <v>79</v>
       </c>
       <c r="S54" t="s" s="2">
         <v>79</v>
@@ -8727,10 +8711,10 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>90</v>
@@ -8739,7 +8723,7 @@
         <v>79</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>79</v>
@@ -8762,41 +8746,43 @@
         <v>256</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>211</v>
+        <v>256</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="O55" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="N55" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>79</v>
       </c>
@@ -8844,19 +8830,19 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>185</v>
+        <v>260</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>79</v>
@@ -8883,7 +8869,7 @@
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8896,26 +8882,22 @@
         <v>79</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>135</v>
+        <v>262</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O56" t="s" s="2">
         <v>264</v>
       </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>79</v>
       </c>
@@ -8963,7 +8945,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8975,30 +8957,30 @@
         <v>79</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>79</v>
+        <v>265</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>133</v>
+        <v>266</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>79</v>
+        <v>267</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>79</v>
+        <v>268</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9006,30 +8988,32 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>267</v>
+        <v>110</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>271</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>79</v>
@@ -9054,13 +9038,13 @@
         <v>79</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>79</v>
+        <v>273</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>79</v>
+        <v>274</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>79</v>
+        <v>275</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>79</v>
@@ -9078,13 +9062,13 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>79</v>
@@ -9093,27 +9077,27 @@
         <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>273</v>
+        <v>79</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9121,7 +9105,7 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>90</v>
@@ -9130,22 +9114,22 @@
         <v>79</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>110</v>
+        <v>195</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9171,34 +9155,34 @@
         <v>79</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="Y58" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF58" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="Z58" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>274</v>
-      </c>
       <c r="AG58" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>90</v>
@@ -9210,16 +9194,16 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>283</v>
+        <v>79</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>79</v>
@@ -9227,10 +9211,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9238,7 +9222,7 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>90</v>
@@ -9250,20 +9234,18 @@
         <v>79</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
         <v>195</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>79</v>
@@ -9288,34 +9270,34 @@
         <v>79</v>
       </c>
       <c r="X59" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF59" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="Y59" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>284</v>
-      </c>
       <c r="AG59" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>90</v>
@@ -9327,27 +9309,27 @@
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>79</v>
+        <v>294</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>79</v>
+        <v>296</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>79</v>
+        <v>297</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9355,7 +9337,7 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>90</v>
@@ -9367,16 +9349,16 @@
         <v>79</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>195</v>
+        <v>151</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>294</v>
+        <v>152</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>295</v>
+        <v>153</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9403,13 +9385,13 @@
         <v>79</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>296</v>
+        <v>79</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>297</v>
+        <v>79</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>79</v>
@@ -9427,10 +9409,10 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>293</v>
+        <v>154</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>90</v>
@@ -9439,41 +9421,41 @@
         <v>79</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>298</v>
+        <v>79</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>299</v>
+        <v>79</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>300</v>
+        <v>155</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>301</v>
+        <v>79</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>302</v>
+        <v>79</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>79</v>
@@ -9485,15 +9467,17 @@
         <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>79</v>
@@ -9530,31 +9514,31 @@
         <v>79</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>79</v>
@@ -9574,18 +9558,18 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>81</v>
@@ -9597,21 +9581,23 @@
         <v>79</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>135</v>
+        <v>301</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>169</v>
+        <v>302</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>170</v>
+        <v>303</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>79</v>
       </c>
@@ -9647,10 +9633,10 @@
         <v>79</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>138</v>
+        <v>306</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>158</v>
+        <v>307</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>79</v>
@@ -9659,7 +9645,7 @@
         <v>139</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>159</v>
+        <v>308</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9671,16 +9657,16 @@
         <v>79</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>79</v>
+        <v>309</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>155</v>
+        <v>310</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>79</v>
@@ -9691,12 +9677,14 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="C63" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="C63" t="s" s="2">
+        <v>312</v>
+      </c>
       <c r="D63" t="s" s="2">
         <v>79</v>
       </c>
@@ -9705,7 +9693,7 @@
         <v>90</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>79</v>
@@ -9717,19 +9705,19 @@
         <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>79</v>
@@ -9754,31 +9742,29 @@
         <v>79</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>79</v>
+        <v>313</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>311</v>
+        <v>79</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>312</v>
+        <v>79</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9796,10 +9782,10 @@
         <v>79</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>79</v>
@@ -9810,23 +9796,23 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>79</v>
@@ -9838,19 +9824,19 @@
         <v>91</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>79</v>
@@ -9875,11 +9861,11 @@
         <v>79</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>79</v>
@@ -9897,7 +9883,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9915,10 +9901,10 @@
         <v>79</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>79</v>
@@ -9929,14 +9915,12 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="C65" t="s" s="2">
-        <v>320</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>79</v>
       </c>
@@ -9945,7 +9929,7 @@
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>79</v>
@@ -9954,23 +9938,19 @@
         <v>79</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>306</v>
+        <v>151</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>307</v>
+        <v>152</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>310</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>79</v>
       </c>
@@ -9994,11 +9974,13 @@
         <v>79</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="Y65" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z65" t="s" s="2">
-        <v>321</v>
+        <v>79</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>79</v>
@@ -10016,28 +9998,28 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>313</v>
+        <v>154</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>314</v>
+        <v>79</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>315</v>
+        <v>155</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>79</v>
@@ -10048,21 +10030,21 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>79</v>
@@ -10074,15 +10056,17 @@
         <v>79</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>79</v>
@@ -10119,31 +10103,31 @@
         <v>79</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>79</v>
@@ -10163,21 +10147,21 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>79</v>
@@ -10186,21 +10170,23 @@
         <v>79</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>169</v>
+        <v>323</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>170</v>
+        <v>324</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O67" s="2"/>
+        <v>325</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>326</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>79</v>
       </c>
@@ -10236,40 +10222,40 @@
         <v>79</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>159</v>
+        <v>327</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>79</v>
+        <v>328</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>155</v>
+        <v>329</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>79</v>
@@ -10280,10 +10266,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10291,7 +10277,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>90</v>
@@ -10306,20 +10292,18 @@
         <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>104</v>
+        <v>151</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>79</v>
       </c>
@@ -10367,7 +10351,7 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10385,10 +10369,10 @@
         <v>79</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>79</v>
@@ -10399,10 +10383,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10425,18 +10409,18 @@
         <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>341</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" t="s" s="2">
+        <v>342</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>79</v>
       </c>
@@ -10484,7 +10468,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10502,10 +10486,10 @@
         <v>79</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>79</v>
@@ -10516,10 +10500,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10542,17 +10526,17 @@
         <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>110</v>
+        <v>151</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>79</v>
@@ -10601,7 +10585,7 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10619,10 +10603,10 @@
         <v>79</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>79</v>
@@ -10633,10 +10617,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10659,17 +10643,19 @@
         <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>151</v>
+        <v>356</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="O71" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>79</v>
@@ -10718,7 +10704,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10736,10 +10722,10 @@
         <v>79</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>79</v>
@@ -10750,10 +10736,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10776,19 +10762,19 @@
         <v>91</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>361</v>
+        <v>151</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>79</v>
@@ -10837,7 +10823,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10855,10 +10841,10 @@
         <v>79</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>79</v>
@@ -10869,10 +10855,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10880,7 +10866,7 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>90</v>
@@ -10895,20 +10881,16 @@
         <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>151</v>
+        <v>373</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>373</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>79</v>
       </c>
@@ -10956,10 +10938,10 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>90</v>
@@ -10971,16 +10953,16 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>79</v>
+        <v>376</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>79</v>
+        <v>379</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>79</v>
@@ -10988,10 +10970,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10999,7 +10981,7 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>90</v>
@@ -11011,16 +10993,16 @@
         <v>79</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11071,10 +11053,10 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>90</v>
@@ -11086,16 +11068,16 @@
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>79</v>
@@ -11103,10 +11085,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11114,7 +11096,7 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>90</v>
@@ -11126,18 +11108,20 @@
         <v>79</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>79</v>
@@ -11174,22 +11158,20 @@
         <v>79</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="AC75" s="2"/>
       <c r="AD75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>79</v>
+        <v>394</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>90</v>
@@ -11201,35 +11183,37 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>79</v>
+        <v>399</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="C76" s="2"/>
+        <v>388</v>
+      </c>
+      <c r="C76" t="s" s="2">
+        <v>401</v>
+      </c>
       <c r="D76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>90</v>
@@ -11244,16 +11228,16 @@
         <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11291,17 +11275,19 @@
         <v>79</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="AC76" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>399</v>
+        <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>90</v>
@@ -11316,31 +11302,29 @@
         <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>404</v>
+        <v>399</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="B77" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="B77" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>406</v>
-      </c>
+      <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
         <v>79</v>
       </c>
@@ -11358,20 +11342,18 @@
         <v>79</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>394</v>
+        <v>151</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M77" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>397</v>
-      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>79</v>
@@ -11420,10 +11402,10 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>393</v>
+        <v>154</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>90</v>
@@ -11432,30 +11414,30 @@
         <v>79</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>400</v>
+        <v>79</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>401</v>
+        <v>79</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>402</v>
+        <v>79</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>403</v>
+        <v>79</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>404</v>
+        <v>79</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="B78" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11466,7 +11448,7 @@
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>79</v>
@@ -11478,13 +11460,13 @@
         <v>79</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>411</v>
+        <v>136</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>412</v>
+        <v>137</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11523,31 +11505,29 @@
         <v>79</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AC78" s="2"/>
       <c r="AD78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>79</v>
@@ -11567,12 +11547,14 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="C79" s="2"/>
+        <v>409</v>
+      </c>
+      <c r="C79" t="s" s="2">
+        <v>411</v>
+      </c>
       <c r="D79" t="s" s="2">
         <v>79</v>
       </c>
@@ -11581,7 +11563,7 @@
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>79</v>
@@ -11593,13 +11575,13 @@
         <v>79</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>135</v>
+        <v>412</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>136</v>
+        <v>413</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>137</v>
+        <v>414</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11638,14 +11620,16 @@
         <v>79</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AC79" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
         <v>159</v>
@@ -11657,7 +11641,7 @@
         <v>81</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>79</v>
+        <v>148</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>141</v>
@@ -11683,11 +11667,9 @@
         <v>415</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="C80" t="s" s="2">
         <v>416</v>
       </c>
+      <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
         <v>79</v>
       </c>
@@ -11708,13 +11690,13 @@
         <v>79</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>417</v>
+        <v>151</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>418</v>
+        <v>152</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>419</v>
+        <v>153</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11765,19 +11747,19 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>141</v>
+        <v>79</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>79</v>
@@ -11786,7 +11768,7 @@
         <v>79</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>79</v>
+        <v>155</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>79</v>
@@ -11797,10 +11779,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11811,7 +11793,7 @@
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>79</v>
@@ -11823,13 +11805,13 @@
         <v>79</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11868,31 +11850,31 @@
         <v>79</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>79</v>
@@ -11901,7 +11883,7 @@
         <v>79</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>155</v>
+        <v>79</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>79</v>
@@ -11912,10 +11894,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11923,10 +11905,10 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>79</v>
@@ -11938,22 +11920,24 @@
         <v>79</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N82" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q82" s="2"/>
       <c r="R82" t="s" s="2">
-        <v>79</v>
+        <v>421</v>
       </c>
       <c r="S82" t="s" s="2">
         <v>79</v>
@@ -11983,31 +11967,31 @@
         <v>79</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>141</v>
+        <v>79</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>79</v>
@@ -12016,7 +12000,7 @@
         <v>79</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>79</v>
@@ -12027,10 +12011,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12038,7 +12022,7 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
         <v>90</v>
@@ -12053,24 +12037,22 @@
         <v>79</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>104</v>
+        <v>195</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q83" s="2"/>
       <c r="R83" t="s" s="2">
-        <v>426</v>
+        <v>79</v>
       </c>
       <c r="S83" t="s" s="2">
         <v>79</v>
@@ -12088,13 +12070,11 @@
         <v>79</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="Y83" s="2"/>
       <c r="Z83" t="s" s="2">
-        <v>79</v>
+        <v>424</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>79</v>
@@ -12112,10 +12092,10 @@
         <v>79</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>90</v>
@@ -12124,7 +12104,7 @@
         <v>79</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>79</v>
@@ -12144,10 +12124,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12170,13 +12150,13 @@
         <v>79</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>195</v>
+        <v>389</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>181</v>
+        <v>427</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>182</v>
+        <v>428</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12203,30 +12183,32 @@
         <v>79</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="Y84" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF84" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="AA84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>185</v>
-      </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
@@ -12237,7 +12219,7 @@
         <v>79</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>79</v>
@@ -12246,7 +12228,7 @@
         <v>79</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>79</v>
@@ -12260,7 +12242,7 @@
         <v>430</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12283,13 +12265,13 @@
         <v>79</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12340,31 +12322,31 @@
         <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AN85" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="AG85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH85" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>79</v>
@@ -12395,10 +12377,10 @@
         <v>79</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>394</v>
+        <v>356</v>
       </c>
       <c r="L86" t="s" s="2">
         <v>436</v>
@@ -12406,7 +12388,9 @@
       <c r="M86" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="N86" s="2"/>
+      <c r="N86" t="s" s="2">
+        <v>438</v>
+      </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>79</v>
@@ -12473,13 +12457,13 @@
         <v>79</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>79</v>
+        <v>439</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>79</v>
@@ -12487,10 +12471,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12510,19 +12494,19 @@
         <v>79</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>361</v>
+        <v>195</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12548,13 +12532,13 @@
         <v>79</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>79</v>
+        <v>283</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>79</v>
+        <v>446</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>79</v>
+        <v>231</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>79</v>
@@ -12572,7 +12556,7 @@
         <v>79</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12590,13 +12574,13 @@
         <v>79</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>79</v>
@@ -12604,10 +12588,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12630,17 +12614,15 @@
         <v>79</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>195</v>
+        <v>449</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>450</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>79</v>
@@ -12665,13 +12647,13 @@
         <v>79</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>288</v>
+        <v>79</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>451</v>
+        <v>79</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>231</v>
+        <v>79</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>79</v>
@@ -12689,7 +12671,7 @@
         <v>79</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12704,16 +12686,16 @@
         <v>102</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>79</v>
+        <v>452</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>79</v>
@@ -12721,10 +12703,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12747,13 +12729,13 @@
         <v>79</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12804,7 +12786,7 @@
         <v>79</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12819,27 +12801,27 @@
         <v>102</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>457</v>
+        <v>79</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>460</v>
+        <v>79</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>79</v>
+        <v>462</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12862,13 +12844,13 @@
         <v>79</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>462</v>
+        <v>151</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12919,7 +12901,7 @@
         <v>79</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12937,24 +12919,24 @@
         <v>79</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12977,13 +12959,13 @@
         <v>79</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>151</v>
+        <v>470</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -13034,7 +13016,7 @@
         <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13052,24 +13034,24 @@
         <v>79</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>473</v>
+        <v>79</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13092,7 +13074,7 @@
         <v>79</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>475</v>
+        <v>195</v>
       </c>
       <c r="L92" t="s" s="2">
         <v>476</v>
@@ -13125,13 +13107,11 @@
         <v>79</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="Y92" s="2"/>
       <c r="Z92" t="s" s="2">
-        <v>79</v>
+        <v>478</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>79</v>
@@ -13149,7 +13129,7 @@
         <v>79</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13167,24 +13147,24 @@
         <v>79</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>79</v>
+        <v>481</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13210,10 +13190,10 @@
         <v>195</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13240,11 +13220,11 @@
         <v>79</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="Y93" s="2"/>
       <c r="Z93" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>79</v>
@@ -13262,7 +13242,7 @@
         <v>79</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13280,24 +13260,24 @@
         <v>79</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13320,13 +13300,13 @@
         <v>79</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>195</v>
+        <v>490</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13353,11 +13333,13 @@
         <v>79</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="Y94" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z94" t="s" s="2">
-        <v>490</v>
+        <v>79</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>79</v>
@@ -13375,7 +13357,7 @@
         <v>79</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13393,24 +13375,24 @@
         <v>79</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>493</v>
+        <v>79</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13421,7 +13403,7 @@
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>79</v>
@@ -13430,16 +13412,16 @@
         <v>79</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13478,25 +13460,23 @@
         <v>79</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>499</v>
+      </c>
+      <c r="AC95" s="2"/>
       <c r="AD95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>79</v>
@@ -13505,13 +13485,13 @@
         <v>102</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>79</v>
+        <v>500</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>79</v>
@@ -13522,10 +13502,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13536,7 +13516,7 @@
         <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>79</v>
@@ -13545,16 +13525,16 @@
         <v>79</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>501</v>
+        <v>151</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>502</v>
+        <v>152</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>503</v>
+        <v>153</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13593,38 +13573,40 @@
         <v>79</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="AC96" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>500</v>
+        <v>154</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>505</v>
+        <v>79</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>506</v>
+        <v>79</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>507</v>
+        <v>155</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>79</v>
@@ -13635,21 +13617,21 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>79</v>
@@ -13661,15 +13643,17 @@
         <v>79</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N97" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>79</v>
@@ -13718,19 +13702,19 @@
         <v>79</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>79</v>
@@ -13750,14 +13734,14 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>168</v>
+        <v>506</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -13770,24 +13754,26 @@
         <v>79</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K98" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>169</v>
+        <v>507</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>170</v>
+        <v>508</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="O98" s="2"/>
+      <c r="O98" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>79</v>
       </c>
@@ -13835,7 +13821,7 @@
         <v>79</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>159</v>
+        <v>509</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -13856,7 +13842,7 @@
         <v>79</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>79</v>
@@ -13874,39 +13860,35 @@
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>511</v>
+        <v>79</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J99" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>135</v>
+        <v>195</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="M99" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>264</v>
-      </c>
+      <c r="N99" s="2"/>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>79</v>
       </c>
@@ -13930,13 +13912,13 @@
         <v>79</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>79</v>
+        <v>513</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>79</v>
+        <v>514</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>79</v>
+        <v>515</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>79</v>
@@ -13954,28 +13936,28 @@
         <v>79</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>79</v>
+        <v>516</v>
       </c>
       <c r="AL99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>133</v>
+        <v>517</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>79</v>
@@ -13986,10 +13968,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13997,7 +13979,7 @@
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G100" t="s" s="2">
         <v>90</v>
@@ -14012,15 +13994,17 @@
         <v>91</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>195</v>
+        <v>519</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="N100" s="2"/>
+        <v>521</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>522</v>
+      </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>79</v>
@@ -14045,34 +14029,34 @@
         <v>79</v>
       </c>
       <c r="X100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF100" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="Y100" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="Z100" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>515</v>
-      </c>
       <c r="AG100" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>90</v>
@@ -14084,16 +14068,16 @@
         <v>102</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>79</v>
+        <v>525</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>79</v>
@@ -14101,21 +14085,23 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="C101" s="2"/>
+        <v>495</v>
+      </c>
+      <c r="C101" t="s" s="2">
+        <v>527</v>
+      </c>
       <c r="D101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>79</v>
@@ -14127,17 +14113,15 @@
         <v>91</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>524</v>
+        <v>496</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>527</v>
-      </c>
+        <v>498</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>79</v>
@@ -14186,13 +14170,13 @@
         <v>79</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>523</v>
+        <v>495</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>79</v>
@@ -14201,16 +14185,16 @@
         <v>102</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>528</v>
+        <v>500</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>79</v>
+        <v>501</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>529</v>
+        <v>502</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>530</v>
+        <v>79</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>79</v>
@@ -14218,14 +14202,12 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="C102" t="s" s="2">
-        <v>532</v>
-      </c>
+        <v>503</v>
+      </c>
+      <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
         <v>79</v>
       </c>
@@ -14234,7 +14216,7 @@
         <v>80</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>79</v>
@@ -14243,16 +14225,16 @@
         <v>79</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>501</v>
+        <v>151</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>533</v>
+        <v>152</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>503</v>
+        <v>153</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14303,28 +14285,28 @@
         <v>79</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>500</v>
+        <v>154</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>505</v>
+        <v>79</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>506</v>
+        <v>79</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>507</v>
+        <v>155</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>79</v>
@@ -14335,21 +14317,21 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>79</v>
@@ -14361,15 +14343,17 @@
         <v>79</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N103" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>79</v>
@@ -14418,19 +14402,19 @@
         <v>79</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>79</v>
@@ -14450,14 +14434,14 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>168</v>
+        <v>506</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -14470,24 +14454,26 @@
         <v>79</v>
       </c>
       <c r="I104" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K104" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>169</v>
+        <v>507</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>170</v>
+        <v>508</v>
       </c>
       <c r="N104" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="O104" s="2"/>
+      <c r="O104" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P104" t="s" s="2">
         <v>79</v>
       </c>
@@ -14535,7 +14521,7 @@
         <v>79</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>159</v>
+        <v>509</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14556,7 +14542,7 @@
         <v>79</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>79</v>
@@ -14567,46 +14553,42 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>510</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>511</v>
+        <v>79</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I105" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J105" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>135</v>
+        <v>195</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="M105" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>264</v>
-      </c>
+      <c r="N105" s="2"/>
+      <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>79</v>
       </c>
@@ -14615,7 +14597,7 @@
         <v>79</v>
       </c>
       <c r="S105" t="s" s="2">
-        <v>79</v>
+        <v>533</v>
       </c>
       <c r="T105" t="s" s="2">
         <v>79</v>
@@ -14630,13 +14612,13 @@
         <v>79</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>79</v>
+        <v>513</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>79</v>
+        <v>514</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>79</v>
+        <v>515</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>79</v>
@@ -14654,28 +14636,28 @@
         <v>79</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>79</v>
+        <v>516</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>133</v>
+        <v>517</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>79</v>
@@ -14686,10 +14668,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14697,7 +14679,7 @@
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G106" t="s" s="2">
         <v>90</v>
@@ -14712,15 +14694,17 @@
         <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>195</v>
+        <v>535</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="N106" s="2"/>
+        <v>521</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>522</v>
+      </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>79</v>
@@ -14730,7 +14714,7 @@
         <v>79</v>
       </c>
       <c r="S106" t="s" s="2">
-        <v>538</v>
+        <v>79</v>
       </c>
       <c r="T106" t="s" s="2">
         <v>79</v>
@@ -14745,34 +14729,34 @@
         <v>79</v>
       </c>
       <c r="X106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF106" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="Y106" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="Z106" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>515</v>
-      </c>
       <c r="AG106" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH106" t="s" s="2">
         <v>90</v>
@@ -14784,16 +14768,16 @@
         <v>102</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>79</v>
+        <v>525</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>79</v>
@@ -14801,10 +14785,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>523</v>
+        <v>536</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14812,7 +14796,7 @@
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G107" t="s" s="2">
         <v>90</v>
@@ -14827,17 +14811,15 @@
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>525</v>
+        <v>538</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>527</v>
-      </c>
+        <v>539</v>
+      </c>
+      <c r="N107" s="2"/>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>79</v>
@@ -14886,13 +14868,13 @@
         <v>79</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>523</v>
+        <v>536</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>79</v>
@@ -14901,16 +14883,16 @@
         <v>102</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>79</v>
+        <v>541</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>529</v>
+        <v>542</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>530</v>
+        <v>79</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>79</v>
@@ -14918,10 +14900,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14941,16 +14923,16 @@
         <v>79</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>542</v>
+        <v>151</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>543</v>
+        <v>152</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>544</v>
+        <v>153</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15001,28 +14983,28 @@
         <v>79</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>541</v>
+        <v>154</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>545</v>
+        <v>79</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>546</v>
+        <v>79</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>547</v>
+        <v>155</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>79</v>
@@ -15033,21 +15015,21 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>79</v>
@@ -15059,15 +15041,17 @@
         <v>79</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N109" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>79</v>
@@ -15104,31 +15088,31 @@
         <v>79</v>
       </c>
       <c r="AB109" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AC109" t="s" s="2">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="AD109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE109" t="s" s="2">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>79</v>
@@ -15148,21 +15132,21 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>79</v>
@@ -15171,19 +15155,19 @@
         <v>79</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>135</v>
+        <v>546</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>169</v>
+        <v>547</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>170</v>
+        <v>548</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>171</v>
+        <v>549</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15221,40 +15205,40 @@
         <v>79</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AC110" t="s" s="2">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="AD110" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>159</v>
+        <v>550</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>155</v>
+        <v>551</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>79</v>
@@ -15265,10 +15249,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15291,17 +15275,15 @@
         <v>91</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>551</v>
+        <v>389</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="N111" t="s" s="2">
         <v>554</v>
       </c>
+      <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>79</v>
@@ -15393,7 +15375,7 @@
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G112" t="s" s="2">
         <v>90</v>
@@ -15408,13 +15390,13 @@
         <v>91</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>394</v>
+        <v>558</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -15465,10 +15447,10 @@
         <v>79</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH112" t="s" s="2">
         <v>90</v>
@@ -15486,7 +15468,7 @@
         <v>133</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>79</v>
@@ -15497,10 +15479,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15508,10 +15490,10 @@
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>79</v>
@@ -15520,10 +15502,10 @@
         <v>79</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>563</v>
+        <v>195</v>
       </c>
       <c r="L113" t="s" s="2">
         <v>564</v>
@@ -15556,13 +15538,13 @@
         <v>79</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>79</v>
+        <v>283</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>79</v>
+        <v>566</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>79</v>
+        <v>567</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>79</v>
@@ -15580,13 +15562,13 @@
         <v>79</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>79</v>
@@ -15595,13 +15577,13 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>79</v>
+        <v>568</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>79</v>
@@ -15612,10 +15594,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15638,13 +15620,13 @@
         <v>79</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>195</v>
+        <v>571</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -15671,13 +15653,13 @@
         <v>79</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>288</v>
+        <v>79</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>571</v>
+        <v>79</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>572</v>
+        <v>79</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>79</v>
@@ -15695,7 +15677,7 @@
         <v>79</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -15710,13 +15692,13 @@
         <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>574</v>
+        <v>133</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>79</v>
@@ -15741,32 +15723,36 @@
         <v>80</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I115" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K115" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="L115" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="L115" t="s" s="2">
+      <c r="M115" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="M115" t="s" s="2">
+      <c r="N115" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="N115" s="2"/>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="Q115" s="2"/>
+      <c r="Q115" t="s" s="2">
+        <v>579</v>
+      </c>
       <c r="R115" t="s" s="2">
         <v>79</v>
       </c>
@@ -15816,7 +15802,7 @@
         <v>80</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>79</v>
@@ -15825,10 +15811,10 @@
         <v>102</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>579</v>
+        <v>79</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>79</v>
+        <v>580</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>133</v>
@@ -15842,10 +15828,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15856,62 +15842,58 @@
         <v>80</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I116" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>361</v>
+        <v>195</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="N116" t="s" s="2">
         <v>583</v>
       </c>
+      <c r="N116" s="2"/>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="Q116" t="s" s="2">
+      <c r="Q116" s="2"/>
+      <c r="R116" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S116" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="Y116" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="R116" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S116" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T116" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U116" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V116" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W116" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X116" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y116" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="Z116" t="s" s="2">
-        <v>79</v>
+        <v>585</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>79</v>
@@ -15929,13 +15911,13 @@
         <v>79</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>79</v>
@@ -15947,7 +15929,7 @@
         <v>79</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>585</v>
+        <v>79</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>133</v>
@@ -15987,7 +15969,7 @@
         <v>79</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>195</v>
+        <v>496</v>
       </c>
       <c r="L117" t="s" s="2">
         <v>587</v>
@@ -16020,13 +16002,13 @@
         <v>79</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>288</v>
+        <v>79</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>589</v>
+        <v>79</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>590</v>
+        <v>79</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>79</v>
@@ -16056,7 +16038,7 @@
         <v>79</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>102</v>
+        <v>589</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>79</v>
@@ -16076,10 +16058,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16090,7 +16072,7 @@
         <v>80</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>79</v>
@@ -16102,13 +16084,13 @@
         <v>79</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>501</v>
+        <v>151</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>592</v>
+        <v>152</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>593</v>
+        <v>153</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16159,19 +16141,19 @@
         <v>79</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>591</v>
+        <v>154</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>594</v>
+        <v>79</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>79</v>
@@ -16180,7 +16162,7 @@
         <v>79</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>79</v>
@@ -16191,21 +16173,21 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>79</v>
@@ -16217,15 +16199,17 @@
         <v>79</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N119" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>79</v>
@@ -16274,19 +16258,19 @@
         <v>79</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>79</v>
@@ -16306,14 +16290,14 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>168</v>
+        <v>506</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -16326,24 +16310,26 @@
         <v>79</v>
       </c>
       <c r="I120" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K120" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>169</v>
+        <v>507</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>170</v>
+        <v>508</v>
       </c>
       <c r="N120" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="O120" s="2"/>
+      <c r="O120" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P120" t="s" s="2">
         <v>79</v>
       </c>
@@ -16391,7 +16377,7 @@
         <v>79</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>159</v>
+        <v>509</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -16412,7 +16398,7 @@
         <v>79</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>79</v>
@@ -16423,46 +16409,42 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>511</v>
+        <v>79</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I121" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>512</v>
+        <v>594</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O121" t="s" s="2">
-        <v>264</v>
-      </c>
+        <v>595</v>
+      </c>
+      <c r="N121" s="2"/>
+      <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>79</v>
       </c>
@@ -16510,25 +16492,25 @@
         <v>79</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>514</v>
+        <v>593</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>79</v>
+        <v>596</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>133</v>
@@ -16542,10 +16524,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16568,13 +16550,13 @@
         <v>79</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>151</v>
+        <v>104</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>600</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -16625,7 +16607,7 @@
         <v>79</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -16643,7 +16625,7 @@
         <v>79</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>601</v>
+        <v>79</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>133</v>
@@ -16657,10 +16639,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16683,13 +16665,13 @@
         <v>79</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>104</v>
+        <v>389</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -16740,7 +16722,7 @@
         <v>79</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -16758,7 +16740,7 @@
         <v>79</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>79</v>
+        <v>603</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>133</v>
@@ -16772,10 +16754,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16798,13 +16780,13 @@
         <v>79</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>606</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>607</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -16855,7 +16837,7 @@
         <v>79</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -16873,7 +16855,7 @@
         <v>79</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>133</v>
@@ -16887,10 +16869,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16901,7 +16883,7 @@
         <v>80</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>79</v>
@@ -16913,13 +16895,13 @@
         <v>79</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>394</v>
+        <v>195</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -16946,13 +16928,13 @@
         <v>79</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>79</v>
+        <v>283</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>79</v>
+        <v>611</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>79</v>
+        <v>612</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>79</v>
@@ -16970,13 +16952,13 @@
         <v>79</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>79</v>
@@ -16988,7 +16970,7 @@
         <v>79</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>133</v>
@@ -17002,10 +16984,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17016,7 +16998,7 @@
         <v>80</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>79</v>
@@ -17031,10 +17013,10 @@
         <v>195</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -17061,13 +17043,13 @@
         <v>79</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>79</v>
@@ -17085,13 +17067,13 @@
         <v>79</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI126" t="s" s="2">
         <v>79</v>
@@ -17103,7 +17085,7 @@
         <v>79</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>618</v>
+        <v>79</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>133</v>
@@ -17131,7 +17113,7 @@
         <v>80</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>79</v>
@@ -17143,7 +17125,7 @@
         <v>79</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>195</v>
+        <v>496</v>
       </c>
       <c r="L127" t="s" s="2">
         <v>620</v>
@@ -17151,7 +17133,9 @@
       <c r="M127" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="N127" s="2"/>
+      <c r="N127" t="s" s="2">
+        <v>622</v>
+      </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>79</v>
@@ -17176,13 +17160,13 @@
         <v>79</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>288</v>
+        <v>79</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>622</v>
+        <v>79</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>623</v>
+        <v>79</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>79</v>
@@ -17206,7 +17190,7 @@
         <v>80</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI127" t="s" s="2">
         <v>79</v>
@@ -17218,10 +17202,10 @@
         <v>79</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>79</v>
+        <v>623</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>133</v>
+        <v>624</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>79</v>
@@ -17232,10 +17216,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17246,7 +17230,7 @@
         <v>80</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>79</v>
@@ -17258,17 +17242,15 @@
         <v>79</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>501</v>
+        <v>151</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>625</v>
+        <v>152</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>627</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N128" s="2"/>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
         <v>79</v>
@@ -17317,28 +17299,28 @@
         <v>79</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>624</v>
+        <v>154</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK128" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>628</v>
+        <v>79</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>629</v>
+        <v>155</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>79</v>
@@ -17349,21 +17331,21 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>79</v>
@@ -17375,15 +17357,17 @@
         <v>79</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N129" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
         <v>79</v>
@@ -17432,19 +17416,19 @@
         <v>79</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>79</v>
@@ -17464,14 +17448,14 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>168</v>
+        <v>506</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
@@ -17484,24 +17468,26 @@
         <v>79</v>
       </c>
       <c r="I130" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J130" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K130" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>169</v>
+        <v>507</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>170</v>
+        <v>508</v>
       </c>
       <c r="N130" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="O130" s="2"/>
+      <c r="O130" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P130" t="s" s="2">
         <v>79</v>
       </c>
@@ -17549,7 +17535,7 @@
         <v>79</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>159</v>
+        <v>509</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -17570,7 +17556,7 @@
         <v>79</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>79</v>
@@ -17581,46 +17567,42 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>511</v>
+        <v>79</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I131" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>135</v>
+        <v>389</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>512</v>
+        <v>629</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>264</v>
-      </c>
+        <v>630</v>
+      </c>
+      <c r="N131" s="2"/>
+      <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>79</v>
       </c>
@@ -17668,28 +17650,28 @@
         <v>79</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>514</v>
+        <v>628</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK131" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>79</v>
+        <v>631</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>133</v>
+        <v>397</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>79</v>
@@ -17700,10 +17682,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17726,7 +17708,7 @@
         <v>79</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>394</v>
+        <v>633</v>
       </c>
       <c r="L132" t="s" s="2">
         <v>634</v>
@@ -17783,7 +17765,7 @@
         <v>79</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -17804,7 +17786,7 @@
         <v>636</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>402</v>
+        <v>637</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>79</v>
@@ -17815,10 +17797,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17841,7 +17823,7 @@
         <v>79</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>638</v>
+        <v>356</v>
       </c>
       <c r="L133" t="s" s="2">
         <v>639</v>
@@ -17898,7 +17880,7 @@
         <v>79</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -17944,7 +17926,7 @@
         <v>80</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H134" t="s" s="2">
         <v>79</v>
@@ -17956,7 +17938,7 @@
         <v>79</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>361</v>
+        <v>496</v>
       </c>
       <c r="L134" t="s" s="2">
         <v>644</v>
@@ -18019,7 +18001,7 @@
         <v>80</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>79</v>
@@ -18031,10 +18013,10 @@
         <v>79</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>646</v>
+        <v>79</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>647</v>
+        <v>133</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>79</v>
@@ -18045,10 +18027,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18059,7 +18041,7 @@
         <v>80</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H135" t="s" s="2">
         <v>79</v>
@@ -18071,13 +18053,13 @@
         <v>79</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>501</v>
+        <v>151</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>649</v>
+        <v>152</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>650</v>
+        <v>153</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -18128,19 +18110,19 @@
         <v>79</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>648</v>
+        <v>154</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH135" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI135" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK135" t="s" s="2">
         <v>79</v>
@@ -18149,7 +18131,7 @@
         <v>79</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>79</v>
@@ -18160,21 +18142,21 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H136" t="s" s="2">
         <v>79</v>
@@ -18186,15 +18168,17 @@
         <v>79</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N136" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N136" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
         <v>79</v>
@@ -18243,19 +18227,19 @@
         <v>79</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="AK136" t="s" s="2">
         <v>79</v>
@@ -18275,14 +18259,14 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
-        <v>168</v>
+        <v>506</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
@@ -18295,24 +18279,26 @@
         <v>79</v>
       </c>
       <c r="I137" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J137" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K137" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>169</v>
+        <v>507</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>170</v>
+        <v>508</v>
       </c>
       <c r="N137" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="O137" s="2"/>
+      <c r="O137" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P137" t="s" s="2">
         <v>79</v>
       </c>
@@ -18360,7 +18346,7 @@
         <v>79</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>159</v>
+        <v>509</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -18381,7 +18367,7 @@
         <v>79</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>79</v>
@@ -18392,46 +18378,42 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>511</v>
+        <v>79</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I138" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J138" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>512</v>
+        <v>650</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O138" t="s" s="2">
-        <v>264</v>
-      </c>
+        <v>651</v>
+      </c>
+      <c r="N138" s="2"/>
+      <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
         <v>79</v>
       </c>
@@ -18455,13 +18437,11 @@
         <v>79</v>
       </c>
       <c r="X138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y138" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="Y138" s="2"/>
       <c r="Z138" t="s" s="2">
-        <v>79</v>
+        <v>652</v>
       </c>
       <c r="AA138" t="s" s="2">
         <v>79</v>
@@ -18479,19 +18459,19 @@
         <v>79</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>514</v>
+        <v>649</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI138" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>79</v>
@@ -18511,10 +18491,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18537,13 +18517,13 @@
         <v>79</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>151</v>
+        <v>457</v>
       </c>
       <c r="L139" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="M139" t="s" s="2">
         <v>655</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>656</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -18570,11 +18550,13 @@
         <v>79</v>
       </c>
       <c r="X139" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="Y139" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y139" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z139" t="s" s="2">
-        <v>657</v>
+        <v>79</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>79</v>
@@ -18592,7 +18574,7 @@
         <v>79</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -18624,10 +18606,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18638,7 +18620,7 @@
         <v>80</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H140" t="s" s="2">
         <v>79</v>
@@ -18650,13 +18632,13 @@
         <v>79</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>462</v>
+        <v>195</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -18683,13 +18665,13 @@
         <v>79</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>79</v>
+        <v>659</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>79</v>
+        <v>660</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>79</v>
@@ -18707,13 +18689,13 @@
         <v>79</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI140" t="s" s="2">
         <v>79</v>
@@ -18750,10 +18732,10 @@
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>79</v>
@@ -18765,15 +18747,17 @@
         <v>79</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>195</v>
+        <v>662</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="N141" s="2"/>
+        <v>664</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>665</v>
+      </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>79</v>
@@ -18798,37 +18782,35 @@
         <v>79</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>664</v>
+        <v>79</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>665</v>
+        <v>79</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC141" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="AC141" s="2"/>
       <c r="AD141" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE141" t="s" s="2">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="AF141" t="s" s="2">
         <v>661</v>
       </c>
       <c r="AG141" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI141" t="s" s="2">
         <v>79</v>
@@ -18857,15 +18839,17 @@
         <v>666</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="C142" s="2"/>
+        <v>661</v>
+      </c>
+      <c r="C142" t="s" s="2">
+        <v>667</v>
+      </c>
       <c r="D142" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G142" t="s" s="2">
         <v>90</v>
@@ -18880,16 +18864,16 @@
         <v>79</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -18927,17 +18911,19 @@
         <v>79</v>
       </c>
       <c r="AB142" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="AC142" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC142" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD142" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE142" t="s" s="2">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>90</v>
@@ -18969,14 +18955,12 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="C143" t="s" s="2">
-        <v>672</v>
-      </c>
+        <v>670</v>
+      </c>
+      <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
         <v>79</v>
       </c>
@@ -18997,16 +18981,16 @@
         <v>79</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>673</v>
+        <v>662</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -19056,10 +19040,10 @@
         <v>79</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="AG143" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH143" t="s" s="2">
         <v>90</v>
@@ -19083,123 +19067,6 @@
         <v>79</v>
       </c>
       <c r="AO143" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="B144" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="C144" s="2"/>
-      <c r="D144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E144" s="2"/>
-      <c r="F144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G144" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K144" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="L144" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="M144" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="N144" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="O144" s="2"/>
-      <c r="P144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q144" s="2"/>
-      <c r="R144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF144" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="AG144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH144" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ144" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM144" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AN144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO144" t="s" s="2">
         <v>79</v>
       </c>
     </row>

--- a/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
+++ b/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T14:04:21+00:00</t>
+    <t>2026-06-22T14:24:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
+++ b/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T14:24:08+00:00</t>
+    <t>2026-06-22T14:26:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -85,8 +85,7 @@
   </si>
   <si>
     <t>FRCoreImmunizationProfile permet de décrire l'administration d'un vaccin.
- - Il permet également de décrire pourquoi un vaccin n'a pas été réalisé.
- - Ce profil hérite de la structuration, des contraintes et des vocabulaires définis dans le profil FRMedicationAdministrationDocument sauf mentions précisées ci-après.</t>
+ - Il permet également de décrire pourquoi un vaccin n'a pas été réalisé.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
+++ b/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T14:26:05+00:00</t>
+    <t>2026-06-22T14:28:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,8 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>FRCoreImmunizationProfile permet de décrire l'administration d'un vaccin.
- - Il permet également de décrire pourquoi un vaccin n'a pas été réalisé.</t>
+    <t>FRCoreImmunizationProfile permet de décrire l'administration d'un vaccin. Il permet également de décrire pourquoi un vaccin n'a pas été réalisé.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
+++ b/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T14:28:00+00:00</t>
+    <t>2026-06-22T14:39:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
+++ b/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T14:39:52+00:00</t>
+    <t>2026-06-29T10:03:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
+++ b/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5274" uniqueCount="673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4788" uniqueCount="599">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:03:57+00:00</t>
+    <t>2026-06-29T10:21:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -920,10 +920,7 @@
     <t>Vaccine that was administered or was to be administered.</t>
   </si>
   <si>
-    <t>The type of vaccine for particular disease or diseases against which the patient has been immunised, or a code for absent/unknown immunization.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/uv/ips/ValueSet/vaccines-uv-ips|1.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-vaccine-code-cis|2.2.0</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -941,426 +938,205 @@
     <t>ClinicalDocument/component/StructuredBody/component/section/entry/substanceAdministration/consumable/manfacturedProduct/manufacturedMaterial/realmCode/code</t>
   </si>
   <si>
-    <t>Immunization.vaccineCode.id</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.extension</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
+    <t>Immunization.patient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://hl7.eu/fhir/base/StructureDefinition/patient-eu-core|2.0.0)
 </t>
   </si>
   <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:system}
+    <t>Who was immunized</t>
+  </si>
+  <si>
+    <t>The patient who either received or did not receive the immunization.</t>
+  </si>
+  <si>
+    <t>Event.subject</t>
+  </si>
+  <si>
+    <t>PID-3</t>
+  </si>
+  <si>
+    <t>.partipication[ttypeCode=].role</t>
+  </si>
+  <si>
+    <t>FiveWs.subject</t>
+  </si>
+  <si>
+    <t>Immunization.encounter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
-    <t>Slice CIS et autres codifications</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.coding:cis</t>
-  </si>
-  <si>
-    <t>cis</t>
-  </si>
-  <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-vaccine-code-cis|2.2.0</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.coding:translation</t>
-  </si>
-  <si>
-    <t>translation</t>
-  </si>
-  <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-medication-translation|2.2.0</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.coding:translation.id</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.coding.id</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.coding:translation.extension</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.coding.extension</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.coding:translation.system</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.coding:translation.version</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.coding:translation.code</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.coding:translation.display</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.coding:translation.userSelected</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.coding.userSelected</t>
+    <t>Encounter immunization was part of</t>
+  </si>
+  <si>
+    <t>The visit or admission or other contact between patient and health care provider the immunization was performed as part of.</t>
+  </si>
+  <si>
+    <t>Event.context</t>
+  </si>
+  <si>
+    <t>PV1-19</t>
+  </si>
+  <si>
+    <t>component-&gt;EncounterEvent</t>
+  </si>
+  <si>
+    <t>FiveWs.context</t>
+  </si>
+  <si>
+    <t>Immunization.occurrence[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Date de la vaccination</t>
+  </si>
+  <si>
+    <t>Si la date de la vaccination est inconnue, utiliser l'extension data-absent-reason précisant pourquoi elle n'est pas connue.</t>
+  </si>
+  <si>
+    <t>When immunizations are given a specific date and time should always be known.   When immunizations are patient reported, a specific date might not be known.  Although partial dates are allowed, an adult patient might not be able to recall the year a childhood immunization was given. An exact date is always preferable, but the use of the String data type is acceptable when an exact date is not known. A small number of vaccines (e.g. live oral typhoid vaccine) are given as a series of patient self-administered dose over a span of time. In cases like this, often, only the first dose (typically a provider supervised dose) is recorded with the occurrence indicating the date/time of the first dose.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
+    <t>Event.occurrence[x]</t>
+  </si>
+  <si>
+    <t>RXA-3</t>
+  </si>
+  <si>
+    <t>.effectiveTime</t>
+  </si>
+  <si>
+    <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/StructuredBody/component/section/entry/substanceAdministration/effectiveTime/value</t>
+  </si>
+  <si>
+    <t>Immunization.occurrence[x]:occurrenceDateTime</t>
+  </si>
+  <si>
+    <t>occurrenceDateTime</t>
+  </si>
+  <si>
+    <t>Vaccine administration date</t>
+  </si>
+  <si>
+    <t>Date vaccine administered or was to be administered.</t>
+  </si>
+  <si>
+    <t>Immunization.occurrence[x]:occurrenceDateTime.id</t>
+  </si>
+  <si>
+    <t>Immunization.occurrence[x].id</t>
+  </si>
+  <si>
+    <t>xml:id (or equivalent in JSON)</t>
+  </si>
+  <si>
+    <t>unique id for the element within a resource (for internal references)</t>
+  </si>
+  <si>
+    <t>Immunization.occurrence[x]:occurrenceDateTime.extension</t>
+  </si>
+  <si>
+    <t>Immunization.occurrence[x].extension</t>
+  </si>
+  <si>
+    <t>Immunization.occurrence[x]:occurrenceDateTime.extension:periodOfLife</t>
+  </si>
+  <si>
+    <t>periodOfLife</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.eu/fhir/extensions/StructureDefinition/periods-of-life|1.3.0}
+</t>
+  </si>
+  <si>
+    <t>Many: Periods of Life</t>
+  </si>
+  <si>
+    <t>Extensions used to indicate a time period in a person's life as a reference to a coded value for that life period.</t>
+  </si>
+  <si>
+    <t>Immunization.occurrence[x]:occurrenceDateTime.extension:periodOfLife.id</t>
+  </si>
+  <si>
+    <t>Immunization.occurrence[x].extension.id</t>
+  </si>
+  <si>
+    <t>Immunization.occurrence[x]:occurrenceDateTime.extension:periodOfLife.extension</t>
+  </si>
+  <si>
+    <t>Immunization.occurrence[x].extension.extension</t>
+  </si>
+  <si>
+    <t>Immunization.occurrence[x]:occurrenceDateTime.extension:periodOfLife.url</t>
+  </si>
+  <si>
+    <t>Immunization.occurrence[x].extension.url</t>
+  </si>
+  <si>
+    <t>http://hl7.eu/fhir/extensions/StructureDefinition/periods-of-life</t>
+  </si>
+  <si>
+    <t>Immunization.occurrence[x]:occurrenceDateTime.extension:periodOfLife.value[x]</t>
+  </si>
+  <si>
+    <t>Immunization.occurrence[x].extension.value[x]</t>
+  </si>
+  <si>
+    <t>http://hl7.eu/fhir/base/ValueSet/periodsOfLife-eu|2.0.0</t>
+  </si>
+  <si>
+    <t>Immunization.occurrence[x]:occurrenceDateTime.value</t>
+  </si>
+  <si>
+    <t>Immunization.occurrence[x].value</t>
+  </si>
+  <si>
+    <t>Primitive value for dateTime</t>
+  </si>
+  <si>
+    <t>The actual value</t>
+  </si>
+  <si>
+    <t>dateTime.value</t>
+  </si>
+  <si>
+    <t>Immunization.recorded</t>
+  </si>
+  <si>
+    <t>When the immunization was first captured in the subject's record</t>
+  </si>
+  <si>
+    <t>The date the occurrence of the immunization was first captured in the record - potentially significantly after the occurrence of the event.</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=AUT].time</t>
+  </si>
+  <si>
+    <t>FiveWs.recorded</t>
+  </si>
+  <si>
+    <t>Immunization.primarySource</t>
   </si>
   <si>
     <t xml:space="preserve">boolean
 </t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>Immunization.patient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://hl7.eu/fhir/base/StructureDefinition/patient-eu-core|2.0.0)
-</t>
-  </si>
-  <si>
-    <t>Who was immunized</t>
-  </si>
-  <si>
-    <t>The patient who either received or did not receive the immunization.</t>
-  </si>
-  <si>
-    <t>Event.subject</t>
-  </si>
-  <si>
-    <t>PID-3</t>
-  </si>
-  <si>
-    <t>.partipication[ttypeCode=].role</t>
-  </si>
-  <si>
-    <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>Immunization.encounter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Encounter|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Encounter immunization was part of</t>
-  </si>
-  <si>
-    <t>The visit or admission or other contact between patient and health care provider the immunization was performed as part of.</t>
-  </si>
-  <si>
-    <t>Event.context</t>
-  </si>
-  <si>
-    <t>PV1-19</t>
-  </si>
-  <si>
-    <t>component-&gt;EncounterEvent</t>
-  </si>
-  <si>
-    <t>FiveWs.context</t>
-  </si>
-  <si>
-    <t>Immunization.occurrence[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>Date de la vaccination</t>
-  </si>
-  <si>
-    <t>Si la date de la vaccination est inconnue, utiliser l'extension data-absent-reason précisant pourquoi elle n'est pas connue.</t>
-  </si>
-  <si>
-    <t>When immunizations are given a specific date and time should always be known.   When immunizations are patient reported, a specific date might not be known.  Although partial dates are allowed, an adult patient might not be able to recall the year a childhood immunization was given. An exact date is always preferable, but the use of the String data type is acceptable when an exact date is not known. A small number of vaccines (e.g. live oral typhoid vaccine) are given as a series of patient self-administered dose over a span of time. In cases like this, often, only the first dose (typically a provider supervised dose) is recorded with the occurrence indicating the date/time of the first dose.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
-    <t>Event.occurrence[x]</t>
-  </si>
-  <si>
-    <t>RXA-3</t>
-  </si>
-  <si>
-    <t>.effectiveTime</t>
-  </si>
-  <si>
-    <t>FiveWs.done[x]</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/StructuredBody/component/section/entry/substanceAdministration/effectiveTime/value</t>
-  </si>
-  <si>
-    <t>Immunization.occurrence[x]:occurrenceDateTime</t>
-  </si>
-  <si>
-    <t>occurrenceDateTime</t>
-  </si>
-  <si>
-    <t>Vaccine administration date</t>
-  </si>
-  <si>
-    <t>Date vaccine administered or was to be administered.</t>
-  </si>
-  <si>
-    <t>Immunization.occurrence[x]:occurrenceDateTime.id</t>
-  </si>
-  <si>
-    <t>Immunization.occurrence[x].id</t>
-  </si>
-  <si>
-    <t>xml:id (or equivalent in JSON)</t>
-  </si>
-  <si>
-    <t>unique id for the element within a resource (for internal references)</t>
-  </si>
-  <si>
-    <t>Immunization.occurrence[x]:occurrenceDateTime.extension</t>
-  </si>
-  <si>
-    <t>Immunization.occurrence[x].extension</t>
-  </si>
-  <si>
-    <t>Immunization.occurrence[x]:occurrenceDateTime.extension:periodOfLife</t>
-  </si>
-  <si>
-    <t>periodOfLife</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://hl7.eu/fhir/extensions/StructureDefinition/periods-of-life|1.3.0}
-</t>
-  </si>
-  <si>
-    <t>Many: Periods of Life</t>
-  </si>
-  <si>
-    <t>Extensions used to indicate a time period in a person's life as a reference to a coded value for that life period.</t>
-  </si>
-  <si>
-    <t>Immunization.occurrence[x]:occurrenceDateTime.extension:periodOfLife.id</t>
-  </si>
-  <si>
-    <t>Immunization.occurrence[x].extension.id</t>
-  </si>
-  <si>
-    <t>Immunization.occurrence[x]:occurrenceDateTime.extension:periodOfLife.extension</t>
-  </si>
-  <si>
-    <t>Immunization.occurrence[x].extension.extension</t>
-  </si>
-  <si>
-    <t>Immunization.occurrence[x]:occurrenceDateTime.extension:periodOfLife.url</t>
-  </si>
-  <si>
-    <t>Immunization.occurrence[x].extension.url</t>
-  </si>
-  <si>
-    <t>http://hl7.eu/fhir/extensions/StructureDefinition/periods-of-life</t>
-  </si>
-  <si>
-    <t>Immunization.occurrence[x]:occurrenceDateTime.extension:periodOfLife.value[x]</t>
-  </si>
-  <si>
-    <t>Immunization.occurrence[x].extension.value[x]</t>
-  </si>
-  <si>
-    <t>http://hl7.eu/fhir/base/ValueSet/periodsOfLife-eu|2.0.0</t>
-  </si>
-  <si>
-    <t>Immunization.occurrence[x]:occurrenceDateTime.value</t>
-  </si>
-  <si>
-    <t>Immunization.occurrence[x].value</t>
-  </si>
-  <si>
-    <t>Primitive value for dateTime</t>
-  </si>
-  <si>
-    <t>The actual value</t>
-  </si>
-  <si>
-    <t>dateTime.value</t>
-  </si>
-  <si>
-    <t>Immunization.recorded</t>
-  </si>
-  <si>
-    <t>When the immunization was first captured in the subject's record</t>
-  </si>
-  <si>
-    <t>The date the occurrence of the immunization was first captured in the record - potentially significantly after the occurrence of the event.</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=AUT].time</t>
-  </si>
-  <si>
-    <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>Immunization.primarySource</t>
   </si>
   <si>
     <t>Indicates context the data was recorded in</t>
@@ -2404,7 +2180,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO143"/>
+  <dimension ref="A1:AO130"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="66.5703125" customWidth="true" bestFit="true"/>
@@ -2431,7 +2207,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="116.69140625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="57.20703125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="96.62890625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -9268,13 +9044,11 @@
         <v>79</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="Y59" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="Y59" s="2"/>
+      <c r="Z59" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>79</v>
@@ -9307,27 +9081,27 @@
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AL59" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AL59" t="s" s="2">
+      <c r="AM59" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AN59" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="AN59" t="s" s="2">
+      <c r="AO59" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>297</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9335,7 +9109,7 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>90</v>
@@ -9347,16 +9121,16 @@
         <v>79</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>151</v>
+        <v>298</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>152</v>
+        <v>299</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>153</v>
+        <v>300</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9407,10 +9181,10 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>154</v>
+        <v>297</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>90</v>
@@ -9419,19 +9193,19 @@
         <v>79</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>79</v>
+        <v>301</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>79</v>
+        <v>302</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>155</v>
+        <v>303</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>79</v>
+        <v>304</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>79</v>
@@ -9439,21 +9213,21 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>79</v>
@@ -9465,17 +9239,15 @@
         <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>135</v>
+        <v>306</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>169</v>
+        <v>307</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>79</v>
@@ -9512,43 +9284,43 @@
         <v>79</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>159</v>
+        <v>305</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>79</v>
+        <v>309</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>79</v>
+        <v>310</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>155</v>
+        <v>311</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>79</v>
+        <v>312</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>79</v>
@@ -9556,10 +9328,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9570,7 +9342,7 @@
         <v>90</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>79</v>
@@ -9582,20 +9354,18 @@
         <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>79</v>
       </c>
@@ -9631,25 +9401,23 @@
         <v>79</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>307</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="AC62" s="2"/>
       <c r="AD62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>139</v>
+        <v>319</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>79</v>
@@ -9658,37 +9426,37 @@
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>79</v>
+        <v>320</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>79</v>
+        <v>323</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>79</v>
+        <v>324</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>90</v>
@@ -9703,20 +9471,18 @@
         <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>302</v>
+        <v>327</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>303</v>
+        <v>328</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>79</v>
       </c>
@@ -9740,35 +9506,37 @@
         <v>79</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="Y63" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF63" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="AA63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>308</v>
-      </c>
       <c r="AG63" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>79</v>
@@ -9777,31 +9545,29 @@
         <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>79</v>
+        <v>320</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>79</v>
+        <v>323</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>79</v>
+        <v>324</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="C64" t="s" s="2">
-        <v>315</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>79</v>
       </c>
@@ -9810,7 +9576,7 @@
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>79</v>
@@ -9819,23 +9585,19 @@
         <v>79</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>301</v>
+        <v>151</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>302</v>
+        <v>331</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>79</v>
       </c>
@@ -9859,11 +9621,13 @@
         <v>79</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="Y64" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z64" t="s" s="2">
-        <v>316</v>
+        <v>79</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>79</v>
@@ -9881,28 +9645,28 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>308</v>
+        <v>154</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>309</v>
+        <v>79</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>310</v>
+        <v>79</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>79</v>
@@ -9913,10 +9677,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>318</v>
+        <v>334</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9927,7 +9691,7 @@
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>79</v>
@@ -9939,13 +9703,13 @@
         <v>79</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9984,31 +9748,29 @@
         <v>79</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AC65" s="2"/>
       <c r="AD65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>79</v>
@@ -10017,7 +9779,7 @@
         <v>79</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>155</v>
+        <v>79</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>79</v>
@@ -10028,21 +9790,23 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="C66" s="2"/>
+        <v>334</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>336</v>
+      </c>
       <c r="D66" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>79</v>
@@ -10054,17 +9818,15 @@
         <v>79</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>135</v>
+        <v>337</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>169</v>
+        <v>338</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>79</v>
@@ -10101,16 +9863,16 @@
         <v>79</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
         <v>159</v>
@@ -10122,7 +9884,7 @@
         <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>79</v>
+        <v>148</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>141</v>
@@ -10134,7 +9896,7 @@
         <v>79</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>155</v>
+        <v>79</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>79</v>
@@ -10145,10 +9907,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>321</v>
+        <v>340</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>322</v>
+        <v>341</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10156,7 +9918,7 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>90</v>
@@ -10168,23 +9930,19 @@
         <v>79</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>104</v>
+        <v>151</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>323</v>
+        <v>152</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>326</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>79</v>
       </c>
@@ -10232,7 +9990,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>327</v>
+        <v>154</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10244,16 +10002,16 @@
         <v>79</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>328</v>
+        <v>79</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>329</v>
+        <v>155</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>79</v>
@@ -10264,10 +10022,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10278,7 +10036,7 @@
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>79</v>
@@ -10287,20 +10045,18 @@
         <v>79</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>332</v>
+        <v>136</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>334</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>79</v>
@@ -10337,40 +10093,40 @@
         <v>79</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>335</v>
+        <v>159</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>336</v>
+        <v>79</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>337</v>
+        <v>79</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>79</v>
@@ -10381,10 +10137,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10392,7 +10148,7 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>90</v>
@@ -10404,27 +10160,27 @@
         <v>79</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>340</v>
+        <v>174</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" t="s" s="2">
-        <v>342</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
-        <v>79</v>
+        <v>346</v>
       </c>
       <c r="S69" t="s" s="2">
         <v>79</v>
@@ -10466,10 +10222,10 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>343</v>
+        <v>178</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>90</v>
@@ -10478,16 +10234,16 @@
         <v>79</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>344</v>
+        <v>79</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>345</v>
+        <v>133</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>79</v>
@@ -10498,10 +10254,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10521,21 +10277,19 @@
         <v>79</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>348</v>
+        <v>181</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>349</v>
+        <v>182</v>
       </c>
       <c r="N70" s="2"/>
-      <c r="O70" t="s" s="2">
-        <v>350</v>
-      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>79</v>
       </c>
@@ -10559,13 +10313,11 @@
         <v>79</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>79</v>
+        <v>349</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>79</v>
@@ -10583,7 +10335,7 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>351</v>
+        <v>185</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10601,10 +10353,10 @@
         <v>79</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>352</v>
+        <v>79</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>353</v>
+        <v>133</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>79</v>
@@ -10615,10 +10367,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10638,23 +10390,19 @@
         <v>79</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>356</v>
+        <v>314</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>360</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>79</v>
       </c>
@@ -10702,7 +10450,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10714,16 +10462,16 @@
         <v>79</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>362</v>
+        <v>79</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>363</v>
+        <v>79</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>79</v>
@@ -10734,10 +10482,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10757,23 +10505,19 @@
         <v>79</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>151</v>
+        <v>314</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>368</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>79</v>
       </c>
@@ -10821,7 +10565,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10839,13 +10583,13 @@
         <v>79</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>370</v>
+        <v>79</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>79</v>
+        <v>359</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>79</v>
@@ -10853,10 +10597,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10864,7 +10608,7 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>90</v>
@@ -10879,15 +10623,17 @@
         <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>363</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>79</v>
@@ -10936,10 +10682,10 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>90</v>
@@ -10951,16 +10697,16 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>376</v>
+        <v>79</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>79</v>
@@ -10968,10 +10714,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10994,15 +10740,17 @@
         <v>79</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>381</v>
+        <v>195</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>382</v>
+        <v>369</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N74" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>371</v>
+      </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>79</v>
@@ -11027,13 +10775,13 @@
         <v>79</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>79</v>
+        <v>283</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>79</v>
+        <v>372</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>79</v>
+        <v>231</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>79</v>
@@ -11051,7 +10799,7 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11066,16 +10814,16 @@
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>384</v>
+        <v>79</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>386</v>
+        <v>373</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>387</v>
+        <v>367</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>79</v>
@@ -11083,10 +10831,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11094,7 +10842,7 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>90</v>
@@ -11106,20 +10854,18 @@
         <v>79</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>389</v>
+        <v>375</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>390</v>
+        <v>376</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>392</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>79</v>
@@ -11156,20 +10902,22 @@
         <v>79</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AC75" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>394</v>
+        <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>90</v>
@@ -11181,31 +10929,29 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>395</v>
+        <v>378</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>396</v>
+        <v>379</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>397</v>
+        <v>380</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>398</v>
+        <v>381</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>399</v>
+        <v>79</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="C76" t="s" s="2">
-        <v>401</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
         <v>79</v>
       </c>
@@ -11223,20 +10969,18 @@
         <v>79</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>402</v>
+        <v>384</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>392</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>79</v>
@@ -11285,10 +11029,10 @@
         <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>90</v>
@@ -11300,27 +11044,27 @@
         <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>395</v>
+        <v>79</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>398</v>
+        <v>79</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>399</v>
+        <v>388</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>404</v>
+        <v>389</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>405</v>
+        <v>389</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11346,10 +11090,10 @@
         <v>151</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>406</v>
+        <v>390</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>407</v>
+        <v>391</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11400,7 +11144,7 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>154</v>
+        <v>389</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11412,30 +11156,30 @@
         <v>79</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>79</v>
+        <v>392</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>79</v>
+        <v>393</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>79</v>
+        <v>394</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>408</v>
+        <v>395</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>409</v>
+        <v>395</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11446,7 +11190,7 @@
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>79</v>
@@ -11458,13 +11202,13 @@
         <v>79</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>135</v>
+        <v>396</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>136</v>
+        <v>397</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>137</v>
+        <v>398</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11503,38 +11247,40 @@
         <v>79</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AC78" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>159</v>
+        <v>395</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>79</v>
+        <v>399</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>79</v>
+        <v>400</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>79</v>
@@ -11545,14 +11291,12 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>411</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
         <v>79</v>
       </c>
@@ -11573,13 +11317,13 @@
         <v>79</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>412</v>
+        <v>195</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11606,13 +11350,11 @@
         <v>79</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>79</v>
+        <v>404</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>79</v>
@@ -11630,42 +11372,42 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>159</v>
+        <v>401</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>79</v>
+        <v>405</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>79</v>
+        <v>406</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>79</v>
+        <v>407</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11688,13 +11430,13 @@
         <v>79</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>152</v>
+        <v>409</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>153</v>
+        <v>410</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11721,13 +11463,11 @@
         <v>79</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
-        <v>79</v>
+        <v>411</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>79</v>
@@ -11745,7 +11485,7 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>154</v>
+        <v>408</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11757,30 +11497,30 @@
         <v>79</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>79</v>
+        <v>412</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>155</v>
+        <v>413</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>79</v>
+        <v>414</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11791,7 +11531,7 @@
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>79</v>
@@ -11803,13 +11543,13 @@
         <v>79</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>135</v>
+        <v>416</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>136</v>
+        <v>417</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>137</v>
+        <v>418</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11848,40 +11588,40 @@
         <v>79</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>159</v>
+        <v>415</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>79</v>
+        <v>419</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>79</v>
+        <v>420</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>79</v>
@@ -11892,10 +11632,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11903,10 +11643,10 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>79</v>
@@ -11915,90 +11655,86 @@
         <v>79</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>104</v>
+        <v>422</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>174</v>
+        <v>423</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q82" s="2"/>
       <c r="R82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AC82" s="2"/>
+      <c r="AD82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AF82" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="S82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>178</v>
-      </c>
       <c r="AG82" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>79</v>
+        <v>426</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>79</v>
+        <v>427</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>133</v>
+        <v>428</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>79</v>
@@ -12009,10 +11745,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12035,13 +11771,13 @@
         <v>79</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>195</v>
+        <v>151</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>181</v>
+        <v>152</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12068,11 +11804,13 @@
         <v>79</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="Y83" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z83" t="s" s="2">
-        <v>424</v>
+        <v>79</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>79</v>
@@ -12090,7 +11828,7 @@
         <v>79</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12102,7 +11840,7 @@
         <v>79</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>79</v>
@@ -12111,7 +11849,7 @@
         <v>79</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>79</v>
@@ -12122,21 +11860,21 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>79</v>
@@ -12148,15 +11886,17 @@
         <v>79</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>389</v>
+        <v>135</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>427</v>
+        <v>169</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>79</v>
@@ -12205,19 +11945,19 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>429</v>
+        <v>159</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>79</v>
@@ -12226,7 +11966,7 @@
         <v>79</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>79</v>
+        <v>155</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>79</v>
@@ -12237,42 +11977,46 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>79</v>
+        <v>432</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>389</v>
+        <v>135</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
+        <v>434</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>79</v>
       </c>
@@ -12320,19 +12064,19 @@
         <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>79</v>
@@ -12341,10 +12085,10 @@
         <v>79</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>433</v>
+        <v>133</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>434</v>
+        <v>79</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>79</v>
@@ -12352,10 +12096,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12378,17 +12122,15 @@
         <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>356</v>
+        <v>195</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N86" t="s" s="2">
         <v>438</v>
       </c>
+      <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>79</v>
@@ -12413,13 +12155,13 @@
         <v>79</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>79</v>
+        <v>439</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>79</v>
+        <v>440</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>79</v>
+        <v>441</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>79</v>
@@ -12437,7 +12179,7 @@
         <v>79</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12452,16 +12194,16 @@
         <v>102</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>79</v>
+        <v>442</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>439</v>
+        <v>79</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>441</v>
+        <v>79</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>79</v>
@@ -12469,10 +12211,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12480,7 +12222,7 @@
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G87" t="s" s="2">
         <v>90</v>
@@ -12492,19 +12234,19 @@
         <v>79</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>195</v>
+        <v>445</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12530,13 +12272,13 @@
         <v>79</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>283</v>
+        <v>79</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>446</v>
+        <v>79</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>231</v>
+        <v>79</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>79</v>
@@ -12554,10 +12296,10 @@
         <v>79</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>90</v>
@@ -12569,16 +12311,16 @@
         <v>102</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>79</v>
+        <v>449</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>439</v>
+        <v>79</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>79</v>
@@ -12586,12 +12328,14 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="C88" s="2"/>
+        <v>421</v>
+      </c>
+      <c r="C88" t="s" s="2">
+        <v>453</v>
+      </c>
       <c r="D88" t="s" s="2">
         <v>79</v>
       </c>
@@ -12600,7 +12344,7 @@
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>79</v>
@@ -12609,16 +12353,16 @@
         <v>79</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>449</v>
+        <v>422</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>451</v>
+        <v>424</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12669,13 +12413,13 @@
         <v>79</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>448</v>
+        <v>421</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>79</v>
@@ -12684,16 +12428,16 @@
         <v>102</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>452</v>
+        <v>426</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>453</v>
+        <v>427</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>454</v>
+        <v>428</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>455</v>
+        <v>79</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>79</v>
@@ -12701,10 +12445,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>456</v>
+        <v>429</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12727,13 +12471,13 @@
         <v>79</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>457</v>
+        <v>151</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>458</v>
+        <v>152</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>459</v>
+        <v>153</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12784,7 +12528,7 @@
         <v>79</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>456</v>
+        <v>154</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12796,41 +12540,41 @@
         <v>79</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>460</v>
+        <v>79</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>461</v>
+        <v>155</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>462</v>
+        <v>79</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>463</v>
+        <v>430</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>79</v>
@@ -12842,15 +12586,17 @@
         <v>79</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>464</v>
+        <v>169</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="N90" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>79</v>
@@ -12899,74 +12645,78 @@
         <v>79</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>463</v>
+        <v>159</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>466</v>
+        <v>79</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>467</v>
+        <v>155</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>468</v>
+        <v>79</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>469</v>
+        <v>431</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>79</v>
+        <v>432</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>470</v>
+        <v>135</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>471</v>
+        <v>433</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
+        <v>434</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>79</v>
       </c>
@@ -13014,28 +12764,28 @@
         <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>469</v>
+        <v>435</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>473</v>
+        <v>79</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>474</v>
+        <v>133</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>79</v>
@@ -13046,10 +12796,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>475</v>
+        <v>458</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>475</v>
+        <v>436</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13069,16 +12819,16 @@
         <v>79</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K92" t="s" s="2">
         <v>195</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>476</v>
+        <v>437</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>477</v>
+        <v>438</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13090,7 +12840,7 @@
         <v>79</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>79</v>
+        <v>459</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>79</v>
@@ -13105,11 +12855,13 @@
         <v>79</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="Y92" s="2"/>
+        <v>439</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>440</v>
+      </c>
       <c r="Z92" t="s" s="2">
-        <v>478</v>
+        <v>441</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>79</v>
@@ -13127,7 +12879,7 @@
         <v>79</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>475</v>
+        <v>436</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13142,27 +12894,27 @@
         <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>79</v>
+        <v>442</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>479</v>
+        <v>79</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>480</v>
+        <v>443</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>481</v>
+        <v>79</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>482</v>
+        <v>460</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>482</v>
+        <v>444</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13170,7 +12922,7 @@
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G93" t="s" s="2">
         <v>90</v>
@@ -13182,18 +12934,20 @@
         <v>79</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>195</v>
+        <v>461</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>483</v>
+        <v>446</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="N93" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>448</v>
+      </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>79</v>
@@ -13218,11 +12972,13 @@
         <v>79</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="Y93" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z93" t="s" s="2">
-        <v>485</v>
+        <v>79</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>79</v>
@@ -13240,10 +12996,10 @@
         <v>79</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>482</v>
+        <v>444</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>90</v>
@@ -13255,27 +13011,27 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>79</v>
+        <v>449</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>486</v>
+        <v>79</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>487</v>
+        <v>450</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>79</v>
+        <v>451</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>488</v>
+        <v>79</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>489</v>
+        <v>462</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>489</v>
+        <v>462</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13295,16 +13051,16 @@
         <v>79</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>490</v>
+        <v>463</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>491</v>
+        <v>464</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>492</v>
+        <v>465</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13355,13 +13111,13 @@
         <v>79</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>489</v>
+        <v>462</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>79</v>
@@ -13370,13 +13126,13 @@
         <v>102</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>79</v>
+        <v>466</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>493</v>
+        <v>467</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>494</v>
+        <v>468</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>79</v>
@@ -13387,10 +13143,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>495</v>
+        <v>469</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>495</v>
+        <v>469</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13401,7 +13157,7 @@
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>79</v>
@@ -13410,16 +13166,16 @@
         <v>79</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>496</v>
+        <v>151</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>497</v>
+        <v>152</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>498</v>
+        <v>153</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13458,38 +13214,40 @@
         <v>79</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="AC95" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>495</v>
+        <v>154</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>500</v>
+        <v>79</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>501</v>
+        <v>79</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>502</v>
+        <v>155</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>79</v>
@@ -13500,21 +13258,21 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>79</v>
@@ -13526,15 +13284,17 @@
         <v>79</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N96" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>79</v>
@@ -13571,31 +13331,31 @@
         <v>79</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>79</v>
@@ -13615,21 +13375,21 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>79</v>
@@ -13638,19 +13398,19 @@
         <v>79</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>135</v>
+        <v>472</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>169</v>
+        <v>473</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>170</v>
+        <v>474</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>171</v>
+        <v>475</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13700,28 +13460,28 @@
         <v>79</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>159</v>
+        <v>476</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>155</v>
+        <v>477</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>79</v>
@@ -13732,46 +13492,42 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>505</v>
+        <v>478</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>505</v>
+        <v>478</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>506</v>
+        <v>79</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J98" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>135</v>
+        <v>314</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>507</v>
+        <v>479</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>79</v>
       </c>
@@ -13819,28 +13575,28 @@
         <v>79</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>509</v>
+        <v>481</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>133</v>
+        <v>482</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>79</v>
@@ -13851,10 +13607,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>510</v>
+        <v>483</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>510</v>
+        <v>483</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13862,7 +13618,7 @@
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G99" t="s" s="2">
         <v>90</v>
@@ -13877,13 +13633,13 @@
         <v>91</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>195</v>
+        <v>484</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>511</v>
+        <v>485</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>512</v>
+        <v>486</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13910,13 +13666,13 @@
         <v>79</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>513</v>
+        <v>79</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>514</v>
+        <v>79</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>515</v>
+        <v>79</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>79</v>
@@ -13934,10 +13690,10 @@
         <v>79</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>510</v>
+        <v>487</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH99" t="s" s="2">
         <v>90</v>
@@ -13949,13 +13705,13 @@
         <v>102</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>516</v>
+        <v>79</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>517</v>
+        <v>488</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>79</v>
@@ -13966,10 +13722,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>518</v>
+        <v>489</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>518</v>
+        <v>489</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13977,10 +13733,10 @@
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>79</v>
@@ -13989,20 +13745,18 @@
         <v>79</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>519</v>
+        <v>195</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>520</v>
+        <v>490</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>522</v>
-      </c>
+        <v>491</v>
+      </c>
+      <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>79</v>
@@ -14027,13 +13781,13 @@
         <v>79</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>79</v>
+        <v>283</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>79</v>
+        <v>492</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>79</v>
+        <v>493</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>79</v>
@@ -14051,13 +13805,13 @@
         <v>79</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>518</v>
+        <v>489</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>79</v>
@@ -14066,16 +13820,16 @@
         <v>102</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>523</v>
+        <v>494</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>524</v>
+        <v>495</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>525</v>
+        <v>79</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>79</v>
@@ -14083,14 +13837,12 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>526</v>
+        <v>496</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="C101" t="s" s="2">
-        <v>527</v>
-      </c>
+        <v>496</v>
+      </c>
+      <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
         <v>79</v>
       </c>
@@ -14108,16 +13860,16 @@
         <v>79</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>528</v>
+        <v>498</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -14168,7 +13920,7 @@
         <v>79</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14186,10 +13938,10 @@
         <v>500</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>501</v>
+        <v>79</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>502</v>
+        <v>133</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>79</v>
@@ -14200,10 +13952,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>529</v>
+        <v>501</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14220,26 +13972,30 @@
         <v>79</v>
       </c>
       <c r="I102" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>151</v>
+        <v>361</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>152</v>
+        <v>502</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N102" s="2"/>
+        <v>503</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>504</v>
+      </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="Q102" s="2"/>
+      <c r="Q102" t="s" s="2">
+        <v>505</v>
+      </c>
       <c r="R102" t="s" s="2">
         <v>79</v>
       </c>
@@ -14283,7 +14039,7 @@
         <v>79</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>154</v>
+        <v>501</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14295,16 +14051,16 @@
         <v>79</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>79</v>
+        <v>506</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>79</v>
@@ -14315,14 +14071,14 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>530</v>
+        <v>507</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -14341,17 +14097,15 @@
         <v>79</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>135</v>
+        <v>195</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>169</v>
+        <v>508</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>509</v>
+      </c>
+      <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>79</v>
@@ -14376,13 +14130,13 @@
         <v>79</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>79</v>
+        <v>283</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>79</v>
+        <v>510</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>79</v>
+        <v>511</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>79</v>
@@ -14400,7 +14154,7 @@
         <v>79</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>159</v>
+        <v>507</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14412,7 +14166,7 @@
         <v>79</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>79</v>
@@ -14421,7 +14175,7 @@
         <v>79</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>79</v>
@@ -14432,14 +14186,14 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>531</v>
+        <v>512</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>506</v>
+        <v>79</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -14452,26 +14206,22 @@
         <v>79</v>
       </c>
       <c r="I104" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>135</v>
+        <v>422</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>514</v>
+      </c>
+      <c r="N104" s="2"/>
+      <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>79</v>
       </c>
@@ -14519,7 +14269,7 @@
         <v>79</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14531,7 +14281,7 @@
         <v>79</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>141</v>
+        <v>515</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>79</v>
@@ -14551,10 +14301,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>532</v>
+        <v>516</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14574,16 +14324,16 @@
         <v>79</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>195</v>
+        <v>151</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>511</v>
+        <v>152</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>512</v>
+        <v>153</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14595,7 +14345,7 @@
         <v>79</v>
       </c>
       <c r="S105" t="s" s="2">
-        <v>533</v>
+        <v>79</v>
       </c>
       <c r="T105" t="s" s="2">
         <v>79</v>
@@ -14610,13 +14360,13 @@
         <v>79</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>513</v>
+        <v>79</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>514</v>
+        <v>79</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>515</v>
+        <v>79</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>79</v>
@@ -14634,7 +14384,7 @@
         <v>79</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>510</v>
+        <v>154</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14646,16 +14396,16 @@
         <v>79</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>516</v>
+        <v>79</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>517</v>
+        <v>155</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>79</v>
@@ -14666,21 +14416,21 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>534</v>
+        <v>517</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>79</v>
@@ -14689,19 +14439,19 @@
         <v>79</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>535</v>
+        <v>135</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>520</v>
+        <v>169</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>521</v>
+        <v>170</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>522</v>
+        <v>171</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14751,31 +14501,31 @@
         <v>79</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>518</v>
+        <v>159</v>
       </c>
       <c r="AG106" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>523</v>
+        <v>79</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>524</v>
+        <v>155</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>525</v>
+        <v>79</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>79</v>
@@ -14783,42 +14533,46 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>536</v>
+        <v>518</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>536</v>
+        <v>518</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>79</v>
+        <v>432</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I107" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J107" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>537</v>
+        <v>135</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>538</v>
+        <v>433</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="N107" s="2"/>
-      <c r="O107" s="2"/>
+        <v>434</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P107" t="s" s="2">
         <v>79</v>
       </c>
@@ -14866,7 +14620,7 @@
         <v>79</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>536</v>
+        <v>435</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -14878,16 +14632,16 @@
         <v>79</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>540</v>
+        <v>79</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>541</v>
+        <v>79</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>542</v>
+        <v>133</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>79</v>
@@ -14898,10 +14652,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>543</v>
+        <v>519</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>543</v>
+        <v>519</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14927,10 +14681,10 @@
         <v>151</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>152</v>
+        <v>520</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>153</v>
+        <v>521</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -14981,7 +14735,7 @@
         <v>79</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>154</v>
+        <v>519</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -14993,16 +14747,16 @@
         <v>79</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>79</v>
+        <v>522</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>79</v>
@@ -15013,21 +14767,21 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>544</v>
+        <v>523</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>544</v>
+        <v>523</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>79</v>
@@ -15039,17 +14793,15 @@
         <v>79</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>169</v>
+        <v>524</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>525</v>
+      </c>
+      <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>79</v>
@@ -15086,31 +14838,31 @@
         <v>79</v>
       </c>
       <c r="AB109" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AC109" t="s" s="2">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="AD109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE109" t="s" s="2">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>159</v>
+        <v>523</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>79</v>
@@ -15119,7 +14871,7 @@
         <v>79</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>79</v>
@@ -15130,10 +14882,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>545</v>
+        <v>526</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>545</v>
+        <v>526</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15153,20 +14905,18 @@
         <v>79</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>546</v>
+        <v>314</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>547</v>
+        <v>527</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>549</v>
-      </c>
+        <v>528</v>
+      </c>
+      <c r="N110" s="2"/>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>79</v>
@@ -15215,7 +14965,7 @@
         <v>79</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>550</v>
+        <v>526</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15233,10 +14983,10 @@
         <v>79</v>
       </c>
       <c r="AL110" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AM110" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM110" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>79</v>
@@ -15247,10 +14997,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>552</v>
+        <v>530</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>552</v>
+        <v>530</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15270,16 +15020,16 @@
         <v>79</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>389</v>
+        <v>314</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>553</v>
+        <v>531</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>554</v>
+        <v>532</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -15330,7 +15080,7 @@
         <v>79</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>555</v>
+        <v>530</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15348,10 +15098,10 @@
         <v>79</v>
       </c>
       <c r="AL111" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AM111" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM111" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>79</v>
@@ -15362,10 +15112,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>557</v>
+        <v>534</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>557</v>
+        <v>534</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15373,10 +15123,10 @@
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>79</v>
@@ -15385,16 +15135,16 @@
         <v>79</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>558</v>
+        <v>195</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>559</v>
+        <v>535</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>560</v>
+        <v>536</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -15421,13 +15171,13 @@
         <v>79</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>79</v>
+        <v>283</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>79</v>
+        <v>537</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>79</v>
+        <v>538</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>79</v>
@@ -15445,13 +15195,13 @@
         <v>79</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>561</v>
+        <v>534</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>79</v>
@@ -15463,10 +15213,10 @@
         <v>79</v>
       </c>
       <c r="AL112" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AM112" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM112" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>79</v>
@@ -15477,10 +15227,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>563</v>
+        <v>540</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>563</v>
+        <v>540</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15491,7 +15241,7 @@
         <v>80</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>79</v>
@@ -15506,10 +15256,10 @@
         <v>195</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>564</v>
+        <v>541</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>565</v>
+        <v>542</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -15539,10 +15289,10 @@
         <v>283</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>566</v>
+        <v>543</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>567</v>
+        <v>544</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>79</v>
@@ -15560,13 +15310,13 @@
         <v>79</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>563</v>
+        <v>540</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>79</v>
@@ -15575,13 +15325,13 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>568</v>
+        <v>79</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>569</v>
+        <v>133</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>79</v>
@@ -15592,10 +15342,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>570</v>
+        <v>545</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>570</v>
+        <v>545</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15618,15 +15368,17 @@
         <v>79</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>571</v>
+        <v>422</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>572</v>
+        <v>546</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="N114" s="2"/>
+        <v>547</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>548</v>
+      </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>79</v>
@@ -15675,7 +15427,7 @@
         <v>79</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>570</v>
+        <v>545</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -15690,13 +15442,13 @@
         <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>574</v>
+        <v>79</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>79</v>
+        <v>549</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>133</v>
+        <v>550</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>79</v>
@@ -15707,10 +15459,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>575</v>
+        <v>551</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>575</v>
+        <v>551</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15727,30 +15479,26 @@
         <v>79</v>
       </c>
       <c r="I115" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>356</v>
+        <v>151</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>576</v>
+        <v>152</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>578</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N115" s="2"/>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="Q115" t="s" s="2">
-        <v>579</v>
-      </c>
+      <c r="Q115" s="2"/>
       <c r="R115" t="s" s="2">
         <v>79</v>
       </c>
@@ -15794,7 +15542,7 @@
         <v>79</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>575</v>
+        <v>154</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -15806,16 +15554,16 @@
         <v>79</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>580</v>
+        <v>79</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>79</v>
@@ -15826,14 +15574,14 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>581</v>
+        <v>552</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>581</v>
+        <v>552</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -15852,15 +15600,17 @@
         <v>79</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>195</v>
+        <v>135</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>582</v>
+        <v>169</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="N116" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>79</v>
@@ -15885,13 +15635,13 @@
         <v>79</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>283</v>
+        <v>79</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>584</v>
+        <v>79</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>585</v>
+        <v>79</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>79</v>
@@ -15909,7 +15659,7 @@
         <v>79</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>581</v>
+        <v>159</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -15921,7 +15671,7 @@
         <v>79</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>79</v>
@@ -15930,7 +15680,7 @@
         <v>79</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>79</v>
@@ -15941,14 +15691,14 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>586</v>
+        <v>553</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>586</v>
+        <v>553</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>79</v>
+        <v>432</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -15961,22 +15711,26 @@
         <v>79</v>
       </c>
       <c r="I117" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>496</v>
+        <v>135</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>587</v>
+        <v>433</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N117" s="2"/>
-      <c r="O117" s="2"/>
+        <v>434</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P117" t="s" s="2">
         <v>79</v>
       </c>
@@ -16024,7 +15778,7 @@
         <v>79</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>586</v>
+        <v>435</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16036,7 +15790,7 @@
         <v>79</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>589</v>
+        <v>141</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>79</v>
@@ -16056,10 +15810,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>590</v>
+        <v>554</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>590</v>
+        <v>554</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16082,13 +15836,13 @@
         <v>79</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>151</v>
+        <v>314</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>152</v>
+        <v>555</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>153</v>
+        <v>556</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16139,7 +15893,7 @@
         <v>79</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>154</v>
+        <v>554</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16151,16 +15905,16 @@
         <v>79</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>79</v>
+        <v>557</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>155</v>
+        <v>322</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>79</v>
@@ -16171,21 +15925,21 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>591</v>
+        <v>558</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>591</v>
+        <v>558</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>79</v>
@@ -16197,17 +15951,15 @@
         <v>79</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>135</v>
+        <v>559</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>169</v>
+        <v>560</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>79</v>
@@ -16256,28 +16008,28 @@
         <v>79</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>159</v>
+        <v>558</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>79</v>
+        <v>562</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>155</v>
+        <v>563</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>79</v>
@@ -16288,46 +16040,42 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>592</v>
+        <v>564</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>592</v>
+        <v>564</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>506</v>
+        <v>79</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I120" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>135</v>
+        <v>361</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>507</v>
+        <v>565</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>566</v>
+      </c>
+      <c r="N120" s="2"/>
+      <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
         <v>79</v>
       </c>
@@ -16375,28 +16123,28 @@
         <v>79</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>509</v>
+        <v>564</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK120" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>79</v>
+        <v>567</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>133</v>
+        <v>568</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>79</v>
@@ -16407,10 +16155,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>593</v>
+        <v>569</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>593</v>
+        <v>569</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16421,7 +16169,7 @@
         <v>80</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>79</v>
@@ -16433,13 +16181,13 @@
         <v>79</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>151</v>
+        <v>422</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>594</v>
+        <v>570</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>595</v>
+        <v>571</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -16490,13 +16238,13 @@
         <v>79</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>593</v>
+        <v>569</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>79</v>
@@ -16508,7 +16256,7 @@
         <v>79</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>596</v>
+        <v>79</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>133</v>
@@ -16522,10 +16270,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>597</v>
+        <v>572</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>597</v>
+        <v>572</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16548,13 +16296,13 @@
         <v>79</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>104</v>
+        <v>151</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>598</v>
+        <v>152</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>599</v>
+        <v>153</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -16605,7 +16353,7 @@
         <v>79</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>597</v>
+        <v>154</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -16617,7 +16365,7 @@
         <v>79</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>79</v>
@@ -16626,7 +16374,7 @@
         <v>79</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>79</v>
@@ -16637,21 +16385,21 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>600</v>
+        <v>573</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>600</v>
+        <v>573</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>79</v>
@@ -16663,15 +16411,17 @@
         <v>79</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>389</v>
+        <v>135</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>601</v>
+        <v>169</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="N123" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>79</v>
@@ -16720,28 +16470,28 @@
         <v>79</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>600</v>
+        <v>159</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>603</v>
+        <v>79</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>79</v>
@@ -16752,42 +16502,46 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>604</v>
+        <v>574</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>604</v>
+        <v>574</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>79</v>
+        <v>432</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I124" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>389</v>
+        <v>135</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>605</v>
+        <v>433</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="N124" s="2"/>
-      <c r="O124" s="2"/>
+        <v>434</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="O124" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P124" t="s" s="2">
         <v>79</v>
       </c>
@@ -16835,25 +16589,25 @@
         <v>79</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>604</v>
+        <v>435</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>607</v>
+        <v>79</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>133</v>
@@ -16867,10 +16621,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>608</v>
+        <v>575</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>608</v>
+        <v>575</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16881,7 +16635,7 @@
         <v>80</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>79</v>
@@ -16893,13 +16647,13 @@
         <v>79</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>195</v>
+        <v>151</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>609</v>
+        <v>576</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>610</v>
+        <v>577</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -16926,13 +16680,11 @@
         <v>79</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="Y125" t="s" s="2">
-        <v>611</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="Y125" s="2"/>
       <c r="Z125" t="s" s="2">
-        <v>612</v>
+        <v>578</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>79</v>
@@ -16950,13 +16702,13 @@
         <v>79</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>608</v>
+        <v>575</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>79</v>
@@ -16968,7 +16720,7 @@
         <v>79</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>613</v>
+        <v>79</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>133</v>
@@ -16982,10 +16734,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>614</v>
+        <v>579</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>614</v>
+        <v>579</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17008,13 +16760,13 @@
         <v>79</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>195</v>
+        <v>383</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>615</v>
+        <v>580</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>616</v>
+        <v>581</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -17041,13 +16793,13 @@
         <v>79</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>283</v>
+        <v>79</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>617</v>
+        <v>79</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>618</v>
+        <v>79</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>79</v>
@@ -17065,7 +16817,7 @@
         <v>79</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>614</v>
+        <v>579</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17097,10 +16849,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>619</v>
+        <v>582</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>619</v>
+        <v>582</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17123,17 +16875,15 @@
         <v>79</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>496</v>
+        <v>195</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>620</v>
+        <v>583</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>622</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="N127" s="2"/>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>79</v>
@@ -17158,13 +16908,13 @@
         <v>79</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>79</v>
+        <v>585</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>79</v>
+        <v>586</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>79</v>
@@ -17182,7 +16932,7 @@
         <v>79</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>619</v>
+        <v>582</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17200,10 +16950,10 @@
         <v>79</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>623</v>
+        <v>79</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>624</v>
+        <v>133</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>79</v>
@@ -17214,10 +16964,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>625</v>
+        <v>587</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>625</v>
+        <v>587</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17225,7 +16975,7 @@
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G128" t="s" s="2">
         <v>90</v>
@@ -17240,15 +16990,17 @@
         <v>79</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>151</v>
+        <v>588</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>152</v>
+        <v>589</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N128" s="2"/>
+        <v>590</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>591</v>
+      </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
         <v>79</v>
@@ -17285,22 +17037,20 @@
         <v>79</v>
       </c>
       <c r="AB128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC128" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="AC128" s="2"/>
       <c r="AD128" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE128" t="s" s="2">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>154</v>
+        <v>587</v>
       </c>
       <c r="AG128" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH128" t="s" s="2">
         <v>90</v>
@@ -17309,7 +17059,7 @@
         <v>79</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
         <v>79</v>
@@ -17318,7 +17068,7 @@
         <v>79</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>79</v>
@@ -17329,21 +17079,23 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>626</v>
+        <v>592</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="C129" s="2"/>
+        <v>587</v>
+      </c>
+      <c r="C129" t="s" s="2">
+        <v>593</v>
+      </c>
       <c r="D129" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>79</v>
@@ -17355,16 +17107,16 @@
         <v>79</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>135</v>
+        <v>594</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>169</v>
+        <v>595</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>170</v>
+        <v>590</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>171</v>
+        <v>591</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -17414,19 +17166,19 @@
         <v>79</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>159</v>
+        <v>587</v>
       </c>
       <c r="AG129" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>79</v>
@@ -17435,7 +17187,7 @@
         <v>79</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>79</v>
@@ -17446,46 +17198,44 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>627</v>
+        <v>596</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>627</v>
+        <v>596</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>506</v>
+        <v>79</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I130" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J130" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>135</v>
+        <v>588</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>507</v>
+        <v>597</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>508</v>
+        <v>598</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O130" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>591</v>
+      </c>
+      <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
         <v>79</v>
       </c>
@@ -17533,19 +17283,19 @@
         <v>79</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>509</v>
+        <v>596</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK130" t="s" s="2">
         <v>79</v>
@@ -17560,1511 +17310,6 @@
         <v>79</v>
       </c>
       <c r="AO130" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="B131" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="C131" s="2"/>
-      <c r="D131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E131" s="2"/>
-      <c r="F131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G131" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K131" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="L131" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="N131" s="2"/>
-      <c r="O131" s="2"/>
-      <c r="P131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q131" s="2"/>
-      <c r="R131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF131" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="AG131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH131" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ131" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL131" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="AM131" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="AN131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO131" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="B132" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="C132" s="2"/>
-      <c r="D132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E132" s="2"/>
-      <c r="F132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G132" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K132" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="L132" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="N132" s="2"/>
-      <c r="O132" s="2"/>
-      <c r="P132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q132" s="2"/>
-      <c r="R132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF132" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="AG132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH132" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ132" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL132" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="AM132" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="AN132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO132" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="B133" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="C133" s="2"/>
-      <c r="D133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E133" s="2"/>
-      <c r="F133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G133" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K133" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="L133" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="N133" s="2"/>
-      <c r="O133" s="2"/>
-      <c r="P133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q133" s="2"/>
-      <c r="R133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF133" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="AG133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH133" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ133" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL133" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="AM133" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="AN133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO133" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="B134" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="C134" s="2"/>
-      <c r="D134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E134" s="2"/>
-      <c r="F134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G134" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K134" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="L134" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="N134" s="2"/>
-      <c r="O134" s="2"/>
-      <c r="P134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q134" s="2"/>
-      <c r="R134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF134" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="AG134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH134" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ134" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM134" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AN134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO134" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="B135" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="C135" s="2"/>
-      <c r="D135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E135" s="2"/>
-      <c r="F135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G135" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K135" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="L135" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N135" s="2"/>
-      <c r="O135" s="2"/>
-      <c r="P135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q135" s="2"/>
-      <c r="R135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF135" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AG135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH135" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM135" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AN135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO135" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="B136" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="C136" s="2"/>
-      <c r="D136" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="E136" s="2"/>
-      <c r="F136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G136" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K136" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L136" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="M136" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O136" s="2"/>
-      <c r="P136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q136" s="2"/>
-      <c r="R136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF136" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="AG136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH136" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ136" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM136" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AN136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO136" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="B137" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="C137" s="2"/>
-      <c r="D137" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="E137" s="2"/>
-      <c r="F137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G137" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I137" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="J137" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K137" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L137" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="M137" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="P137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q137" s="2"/>
-      <c r="R137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF137" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="AG137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH137" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ137" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM137" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AN137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO137" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="B138" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="C138" s="2"/>
-      <c r="D138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E138" s="2"/>
-      <c r="F138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G138" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K138" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="L138" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="M138" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="N138" s="2"/>
-      <c r="O138" s="2"/>
-      <c r="P138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q138" s="2"/>
-      <c r="R138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X138" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="Y138" s="2"/>
-      <c r="Z138" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="AA138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF138" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="AG138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH138" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ138" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM138" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AN138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO138" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="B139" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="C139" s="2"/>
-      <c r="D139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E139" s="2"/>
-      <c r="F139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G139" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K139" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="L139" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="N139" s="2"/>
-      <c r="O139" s="2"/>
-      <c r="P139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q139" s="2"/>
-      <c r="R139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF139" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="AG139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH139" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ139" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM139" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AN139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO139" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="B140" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="C140" s="2"/>
-      <c r="D140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E140" s="2"/>
-      <c r="F140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G140" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K140" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="L140" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="M140" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="N140" s="2"/>
-      <c r="O140" s="2"/>
-      <c r="P140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q140" s="2"/>
-      <c r="R140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X140" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="Y140" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="Z140" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="AA140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF140" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="AG140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH140" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ140" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM140" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AN140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO140" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="B141" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="C141" s="2"/>
-      <c r="D141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E141" s="2"/>
-      <c r="F141" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G141" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K141" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="L141" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="O141" s="2"/>
-      <c r="P141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q141" s="2"/>
-      <c r="R141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB141" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AC141" s="2"/>
-      <c r="AD141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE141" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AF141" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="AG141" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH141" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ141" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM141" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AN141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO141" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="B142" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="C142" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="D142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E142" s="2"/>
-      <c r="F142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G142" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K142" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="L142" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="O142" s="2"/>
-      <c r="P142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q142" s="2"/>
-      <c r="R142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF142" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="AG142" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH142" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ142" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM142" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AN142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO142" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="B143" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="C143" s="2"/>
-      <c r="D143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E143" s="2"/>
-      <c r="F143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G143" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K143" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="L143" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="M143" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="O143" s="2"/>
-      <c r="P143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q143" s="2"/>
-      <c r="R143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF143" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="AG143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH143" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ143" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM143" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AN143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO143" t="s" s="2">
         <v>79</v>
       </c>
     </row>

--- a/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
+++ b/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4788" uniqueCount="599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4975" uniqueCount="623">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:21:29+00:00</t>
+    <t>2026-06-29T10:25:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -920,22 +920,96 @@
     <t>Vaccine that was administered or was to be administered.</t>
   </si>
   <si>
+    <t>The type of vaccine for particular disease or diseases against which the patient has been immunised, or a code for absent/unknown immunization.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/uv/ips/ValueSet/vaccines-uv-ips|1.1.0</t>
+  </si>
+  <si>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>RXA-5</t>
+  </si>
+  <si>
+    <t>.code</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/StructuredBody/component/section/entry/substanceAdministration/consumable/manfacturedProduct/manufacturedMaterial/realmCode/code</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.id</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.extension</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:system}
+</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding:cis</t>
+  </si>
+  <si>
+    <t>cis</t>
+  </si>
+  <si>
     <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-vaccine-code-cis|2.2.0</t>
   </si>
   <si>
-    <t>Event.code</t>
-  </si>
-  <si>
-    <t>RXA-5</t>
-  </si>
-  <si>
-    <t>.code</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/StructuredBody/component/section/entry/substanceAdministration/consumable/manfacturedProduct/manufacturedMaterial/realmCode/code</t>
+    <t>Immunization.vaccineCode.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>Immunization.patient</t>
@@ -2180,7 +2254,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO130"/>
+  <dimension ref="A1:AO135"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="66.5703125" customWidth="true" bestFit="true"/>
@@ -2207,7 +2281,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="57.20703125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="116.69140625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="96.62890625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -9044,11 +9118,13 @@
         <v>79</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="Y59" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="Z59" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>79</v>
@@ -9081,27 +9157,27 @@
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9109,7 +9185,7 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>90</v>
@@ -9121,16 +9197,16 @@
         <v>79</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>298</v>
+        <v>151</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>299</v>
+        <v>152</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>300</v>
+        <v>153</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9181,10 +9257,10 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>297</v>
+        <v>154</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>90</v>
@@ -9193,19 +9269,19 @@
         <v>79</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>301</v>
+        <v>79</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>302</v>
+        <v>79</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>303</v>
+        <v>155</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>304</v>
+        <v>79</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>79</v>
@@ -9213,21 +9289,21 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>79</v>
@@ -9239,15 +9315,17 @@
         <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>306</v>
+        <v>135</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>307</v>
+        <v>169</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>79</v>
@@ -9284,43 +9362,43 @@
         <v>79</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>305</v>
+        <v>159</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>309</v>
+        <v>79</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>310</v>
+        <v>79</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>311</v>
+        <v>155</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>312</v>
+        <v>79</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>79</v>
@@ -9328,10 +9406,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9342,7 +9420,7 @@
         <v>90</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>79</v>
@@ -9354,18 +9432,20 @@
         <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>315</v>
+        <v>302</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>316</v>
+        <v>303</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>79</v>
       </c>
@@ -9401,23 +9481,23 @@
         <v>79</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="AC62" s="2"/>
       <c r="AD62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>319</v>
+        <v>139</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>79</v>
@@ -9426,37 +9506,37 @@
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>320</v>
+        <v>79</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>323</v>
+        <v>79</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>324</v>
+        <v>79</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>90</v>
@@ -9471,18 +9551,20 @@
         <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>327</v>
+        <v>302</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>328</v>
+        <v>303</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>79</v>
       </c>
@@ -9506,13 +9588,11 @@
         <v>79</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>79</v>
+        <v>312</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>79</v>
@@ -9530,13 +9610,13 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>79</v>
@@ -9545,27 +9625,27 @@
         <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>320</v>
+        <v>79</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>323</v>
+        <v>79</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>324</v>
+        <v>79</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9585,19 +9665,23 @@
         <v>79</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K64" t="s" s="2">
         <v>151</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+        <v>315</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>79</v>
       </c>
@@ -9645,7 +9729,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>154</v>
+        <v>318</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9657,16 +9741,16 @@
         <v>79</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>79</v>
+        <v>319</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>79</v>
+        <v>320</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>79</v>
@@ -9677,10 +9761,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>334</v>
+        <v>321</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9688,10 +9772,10 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>79</v>
@@ -9700,16 +9784,16 @@
         <v>79</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>135</v>
+        <v>322</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>136</v>
+        <v>323</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>137</v>
+        <v>324</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9748,41 +9832,43 @@
         <v>79</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AC65" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>159</v>
+        <v>321</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>79</v>
+        <v>325</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>79</v>
+        <v>326</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>79</v>
+        <v>327</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>79</v>
+        <v>328</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>79</v>
@@ -9790,14 +9876,12 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="C66" t="s" s="2">
-        <v>336</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
         <v>79</v>
       </c>
@@ -9818,13 +9902,13 @@
         <v>79</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9875,31 +9959,31 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>159</v>
+        <v>329</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>79</v>
+        <v>333</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>79</v>
+        <v>334</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>79</v>
+        <v>335</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>79</v>
+        <v>336</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>79</v>
@@ -9907,10 +9991,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9918,7 +10002,7 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>90</v>
@@ -9930,18 +10014,20 @@
         <v>79</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>151</v>
+        <v>338</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>152</v>
+        <v>339</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>340</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>79</v>
@@ -9978,22 +10064,20 @@
         <v>79</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="AC67" s="2"/>
       <c r="AD67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>79</v>
+        <v>343</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>154</v>
+        <v>337</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>90</v>
@@ -10002,32 +10086,34 @@
         <v>79</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>79</v>
+        <v>344</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>79</v>
+        <v>345</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>155</v>
+        <v>346</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>79</v>
+        <v>347</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>79</v>
+        <v>348</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="C68" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="C68" t="s" s="2">
+        <v>350</v>
+      </c>
       <c r="D68" t="s" s="2">
         <v>79</v>
       </c>
@@ -10036,7 +10122,7 @@
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>79</v>
@@ -10045,18 +10131,20 @@
         <v>79</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>135</v>
+        <v>338</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>136</v>
+        <v>351</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>79</v>
@@ -10093,54 +10181,54 @@
         <v>79</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>159</v>
+        <v>337</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>79</v>
+        <v>344</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>79</v>
+        <v>345</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>79</v>
+        <v>346</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>79</v>
+        <v>347</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>79</v>
+        <v>348</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10148,7 +10236,7 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>90</v>
@@ -10163,24 +10251,22 @@
         <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>104</v>
+        <v>151</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>174</v>
+        <v>355</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
-        <v>346</v>
+        <v>79</v>
       </c>
       <c r="S69" t="s" s="2">
         <v>79</v>
@@ -10222,10 +10308,10 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>90</v>
@@ -10243,7 +10329,7 @@
         <v>79</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>79</v>
@@ -10254,10 +10340,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10268,7 +10354,7 @@
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>79</v>
@@ -10280,13 +10366,13 @@
         <v>79</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>195</v>
+        <v>135</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>181</v>
+        <v>136</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10313,41 +10399,41 @@
         <v>79</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="Y70" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z70" t="s" s="2">
-        <v>349</v>
+        <v>79</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AC70" s="2"/>
       <c r="AD70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>79</v>
@@ -10356,7 +10442,7 @@
         <v>79</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>79</v>
@@ -10367,12 +10453,14 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="C71" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="C71" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="D71" t="s" s="2">
         <v>79</v>
       </c>
@@ -10393,13 +10481,13 @@
         <v>79</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>314</v>
+        <v>361</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10450,19 +10538,19 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>354</v>
+        <v>159</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>79</v>
+        <v>148</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>79</v>
@@ -10482,10 +10570,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10508,13 +10596,13 @@
         <v>79</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>314</v>
+        <v>151</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>356</v>
+        <v>152</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>357</v>
+        <v>153</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10565,7 +10653,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>355</v>
+        <v>154</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10577,7 +10665,7 @@
         <v>79</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>79</v>
@@ -10586,10 +10674,10 @@
         <v>79</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>358</v>
+        <v>155</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>359</v>
+        <v>79</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>79</v>
@@ -10597,10 +10685,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10611,7 +10699,7 @@
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>79</v>
@@ -10620,20 +10708,18 @@
         <v>79</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>361</v>
+        <v>135</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>362</v>
+        <v>136</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>79</v>
@@ -10670,43 +10756,43 @@
         <v>79</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>360</v>
+        <v>159</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>365</v>
+        <v>79</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>366</v>
+        <v>79</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>367</v>
+        <v>79</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>79</v>
@@ -10717,7 +10803,7 @@
         <v>368</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10725,7 +10811,7 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>90</v>
@@ -10740,16 +10826,16 @@
         <v>79</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>195</v>
+        <v>104</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>369</v>
+        <v>174</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>370</v>
+        <v>175</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>371</v>
+        <v>176</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10757,7 +10843,7 @@
       </c>
       <c r="Q74" s="2"/>
       <c r="R74" t="s" s="2">
-        <v>79</v>
+        <v>370</v>
       </c>
       <c r="S74" t="s" s="2">
         <v>79</v>
@@ -10775,13 +10861,13 @@
         <v>79</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>283</v>
+        <v>79</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>372</v>
+        <v>79</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>231</v>
+        <v>79</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>79</v>
@@ -10799,10 +10885,10 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>368</v>
+        <v>178</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>90</v>
@@ -10811,19 +10897,19 @@
         <v>79</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>365</v>
+        <v>79</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>373</v>
+        <v>133</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>367</v>
+        <v>79</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>79</v>
@@ -10831,10 +10917,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10857,13 +10943,13 @@
         <v>79</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>375</v>
+        <v>195</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>376</v>
+        <v>181</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>377</v>
+        <v>182</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10890,13 +10976,11 @@
         <v>79</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>79</v>
+        <v>373</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>79</v>
@@ -10914,7 +10998,7 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>374</v>
+        <v>185</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -10929,16 +11013,16 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>378</v>
+        <v>79</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>379</v>
+        <v>79</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>380</v>
+        <v>133</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>381</v>
+        <v>79</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>79</v>
@@ -10946,10 +11030,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10972,13 +11056,13 @@
         <v>79</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>383</v>
+        <v>338</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11029,7 +11113,7 @@
         <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11041,30 +11125,30 @@
         <v>79</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>386</v>
+        <v>79</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>387</v>
+        <v>79</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>388</v>
+        <v>79</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11087,13 +11171,13 @@
         <v>79</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>151</v>
+        <v>338</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11144,7 +11228,7 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11162,24 +11246,24 @@
         <v>79</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>392</v>
+        <v>79</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>79</v>
+        <v>383</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>394</v>
+        <v>79</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11199,18 +11283,20 @@
         <v>79</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>79</v>
@@ -11259,7 +11345,7 @@
         <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11277,13 +11363,13 @@
         <v>79</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>79</v>
+        <v>391</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>79</v>
@@ -11291,10 +11377,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11320,12 +11406,14 @@
         <v>195</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N79" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>395</v>
+      </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>79</v>
@@ -11350,11 +11438,13 @@
         <v>79</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="Y79" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>396</v>
+      </c>
       <c r="Z79" t="s" s="2">
-        <v>404</v>
+        <v>231</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>79</v>
@@ -11372,7 +11462,7 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11390,24 +11480,24 @@
         <v>79</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>405</v>
+        <v>389</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>79</v>
+        <v>391</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>407</v>
+        <v>79</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11430,13 +11520,13 @@
         <v>79</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>195</v>
+        <v>399</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11463,11 +11553,13 @@
         <v>79</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="Y80" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z80" t="s" s="2">
-        <v>411</v>
+        <v>79</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>79</v>
@@ -11485,7 +11577,7 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11500,27 +11592,27 @@
         <v>102</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>79</v>
+        <v>402</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>79</v>
+        <v>405</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>414</v>
+        <v>79</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11543,13 +11635,13 @@
         <v>79</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11600,7 +11692,7 @@
         <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11618,24 +11710,24 @@
         <v>79</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>79</v>
+        <v>412</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11646,7 +11738,7 @@
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>79</v>
@@ -11655,16 +11747,16 @@
         <v>79</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>422</v>
+        <v>151</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11703,23 +11795,25 @@
         <v>79</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="AC82" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>79</v>
@@ -11728,27 +11822,27 @@
         <v>102</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>426</v>
+        <v>79</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>79</v>
+        <v>418</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11771,13 +11865,13 @@
         <v>79</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>151</v>
+        <v>420</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>152</v>
+        <v>421</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>153</v>
+        <v>422</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11828,7 +11922,7 @@
         <v>79</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>154</v>
+        <v>419</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -11840,16 +11934,16 @@
         <v>79</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>79</v>
+        <v>423</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>155</v>
+        <v>424</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>79</v>
@@ -11860,21 +11954,21 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>79</v>
@@ -11886,17 +11980,15 @@
         <v>79</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>135</v>
+        <v>195</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>169</v>
+        <v>426</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>427</v>
+      </c>
+      <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>79</v>
@@ -11921,13 +12013,11 @@
         <v>79</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
-        <v>79</v>
+        <v>428</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>79</v>
@@ -11945,65 +12035,65 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>159</v>
+        <v>425</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>79</v>
+        <v>429</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>155</v>
+        <v>430</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>79</v>
+        <v>431</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>432</v>
+        <v>79</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>135</v>
+        <v>195</v>
       </c>
       <c r="L85" t="s" s="2">
         <v>433</v>
@@ -12011,12 +12101,8 @@
       <c r="M85" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="N85" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>259</v>
-      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>79</v>
       </c>
@@ -12040,13 +12126,11 @@
         <v>79</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="Y85" s="2"/>
       <c r="Z85" t="s" s="2">
-        <v>79</v>
+        <v>435</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>79</v>
@@ -12064,42 +12148,42 @@
         <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>79</v>
+        <v>436</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>133</v>
+        <v>437</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>79</v>
+        <v>438</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12119,16 +12203,16 @@
         <v>79</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>195</v>
+        <v>440</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12155,31 +12239,31 @@
         <v>79</v>
       </c>
       <c r="X86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF86" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12194,13 +12278,13 @@
         <v>102</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>442</v>
+        <v>79</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>79</v>
+        <v>443</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>79</v>
@@ -12211,10 +12295,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12222,10 +12306,10 @@
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>79</v>
@@ -12237,17 +12321,15 @@
         <v>91</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N87" t="s" s="2">
         <v>448</v>
       </c>
+      <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>79</v>
@@ -12284,25 +12366,23 @@
         <v>79</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>449</v>
+      </c>
+      <c r="AC87" s="2"/>
       <c r="AD87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>79</v>
@@ -12311,16 +12391,16 @@
         <v>102</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>79</v>
+        <v>451</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>451</v>
+        <v>79</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>79</v>
@@ -12328,14 +12408,12 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="C88" t="s" s="2">
         <v>453</v>
       </c>
+      <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>79</v>
       </c>
@@ -12344,7 +12422,7 @@
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>79</v>
@@ -12353,16 +12431,16 @@
         <v>79</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>422</v>
+        <v>151</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>454</v>
+        <v>152</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>424</v>
+        <v>153</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12413,28 +12491,28 @@
         <v>79</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>421</v>
+        <v>154</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>426</v>
+        <v>79</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>427</v>
+        <v>79</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>428</v>
+        <v>155</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>79</v>
@@ -12445,21 +12523,21 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>429</v>
+        <v>454</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>79</v>
@@ -12471,15 +12549,17 @@
         <v>79</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N89" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>79</v>
@@ -12528,19 +12608,19 @@
         <v>79</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>79</v>
@@ -12560,14 +12640,14 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>430</v>
+        <v>455</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>168</v>
+        <v>456</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -12580,24 +12660,26 @@
         <v>79</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K90" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>169</v>
+        <v>457</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>170</v>
+        <v>458</v>
       </c>
       <c r="N90" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="O90" s="2"/>
+      <c r="O90" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>79</v>
       </c>
@@ -12645,7 +12727,7 @@
         <v>79</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>159</v>
+        <v>459</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12666,7 +12748,7 @@
         <v>79</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>79</v>
@@ -12677,46 +12759,42 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>431</v>
+        <v>460</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>432</v>
+        <v>79</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J91" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>135</v>
+        <v>195</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>433</v>
+        <v>461</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>79</v>
       </c>
@@ -12740,13 +12818,13 @@
         <v>79</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>79</v>
+        <v>463</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>79</v>
+        <v>464</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>79</v>
+        <v>465</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>79</v>
@@ -12764,28 +12842,28 @@
         <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>435</v>
+        <v>460</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>79</v>
+        <v>466</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>133</v>
+        <v>467</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>79</v>
@@ -12796,10 +12874,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>436</v>
+        <v>468</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12807,7 +12885,7 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>90</v>
@@ -12822,15 +12900,17 @@
         <v>91</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>195</v>
+        <v>469</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>437</v>
+        <v>470</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N92" s="2"/>
+        <v>471</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>472</v>
+      </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>79</v>
@@ -12840,7 +12920,7 @@
         <v>79</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>459</v>
+        <v>79</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>79</v>
@@ -12855,13 +12935,13 @@
         <v>79</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>439</v>
+        <v>79</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>440</v>
+        <v>79</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>441</v>
+        <v>79</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>79</v>
@@ -12879,10 +12959,10 @@
         <v>79</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>436</v>
+        <v>468</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>90</v>
@@ -12894,16 +12974,16 @@
         <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>442</v>
+        <v>473</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>443</v>
+        <v>474</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>79</v>
+        <v>475</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>79</v>
@@ -12911,21 +12991,23 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>460</v>
+        <v>476</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="C93" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="C93" t="s" s="2">
+        <v>477</v>
+      </c>
       <c r="D93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>79</v>
@@ -12937,17 +13019,15 @@
         <v>91</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>461</v>
+        <v>446</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>446</v>
+        <v>478</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N93" t="s" s="2">
         <v>448</v>
       </c>
+      <c r="N93" s="2"/>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>79</v>
@@ -12996,13 +13076,13 @@
         <v>79</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>79</v>
@@ -13011,16 +13091,16 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>79</v>
+        <v>451</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>451</v>
+        <v>79</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>79</v>
@@ -13028,10 +13108,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>462</v>
+        <v>479</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13051,16 +13131,16 @@
         <v>79</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>463</v>
+        <v>151</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>464</v>
+        <v>152</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>465</v>
+        <v>153</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13111,28 +13191,28 @@
         <v>79</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>462</v>
+        <v>154</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>466</v>
+        <v>79</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>467</v>
+        <v>79</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>468</v>
+        <v>155</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>79</v>
@@ -13143,21 +13223,21 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>469</v>
+        <v>454</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>79</v>
@@ -13169,15 +13249,17 @@
         <v>79</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N95" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>79</v>
@@ -13226,19 +13308,19 @@
         <v>79</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>79</v>
@@ -13258,14 +13340,14 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>470</v>
+        <v>455</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>168</v>
+        <v>456</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -13278,24 +13360,26 @@
         <v>79</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K96" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>169</v>
+        <v>457</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>170</v>
+        <v>458</v>
       </c>
       <c r="N96" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="O96" s="2"/>
+      <c r="O96" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>79</v>
       </c>
@@ -13331,19 +13415,19 @@
         <v>79</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>159</v>
+        <v>459</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13364,7 +13448,7 @@
         <v>79</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>79</v>
@@ -13375,10 +13459,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13401,17 +13485,15 @@
         <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>472</v>
+        <v>195</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>475</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="N97" s="2"/>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>79</v>
@@ -13421,7 +13503,7 @@
         <v>79</v>
       </c>
       <c r="S97" t="s" s="2">
-        <v>79</v>
+        <v>483</v>
       </c>
       <c r="T97" t="s" s="2">
         <v>79</v>
@@ -13436,13 +13518,13 @@
         <v>79</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>79</v>
+        <v>463</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>79</v>
+        <v>464</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>79</v>
+        <v>465</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>79</v>
@@ -13460,7 +13542,7 @@
         <v>79</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>476</v>
+        <v>460</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13475,13 +13557,13 @@
         <v>102</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>79</v>
+        <v>466</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>79</v>
@@ -13492,10 +13574,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13503,7 +13585,7 @@
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G98" t="s" s="2">
         <v>90</v>
@@ -13518,15 +13600,17 @@
         <v>91</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>314</v>
+        <v>485</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N98" s="2"/>
+        <v>471</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>472</v>
+      </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>79</v>
@@ -13575,10 +13659,10 @@
         <v>79</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>481</v>
+        <v>468</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>90</v>
@@ -13590,16 +13674,16 @@
         <v>102</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>79</v>
+        <v>473</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>79</v>
+        <v>475</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>79</v>
@@ -13607,10 +13691,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13618,7 +13702,7 @@
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G99" t="s" s="2">
         <v>90</v>
@@ -13633,13 +13717,13 @@
         <v>91</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13690,13 +13774,13 @@
         <v>79</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>79</v>
@@ -13705,13 +13789,13 @@
         <v>102</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>79</v>
+        <v>490</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>133</v>
+        <v>491</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>79</v>
@@ -13722,10 +13806,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13736,7 +13820,7 @@
         <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>79</v>
@@ -13748,13 +13832,13 @@
         <v>79</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>195</v>
+        <v>151</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>490</v>
+        <v>152</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>491</v>
+        <v>153</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13781,13 +13865,13 @@
         <v>79</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>283</v>
+        <v>79</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>492</v>
+        <v>79</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>493</v>
+        <v>79</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>79</v>
@@ -13805,28 +13889,28 @@
         <v>79</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>489</v>
+        <v>154</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>494</v>
+        <v>79</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>495</v>
+        <v>155</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>79</v>
@@ -13837,14 +13921,14 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -13863,15 +13947,17 @@
         <v>79</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>497</v>
+        <v>135</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>498</v>
+        <v>169</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="N101" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>79</v>
@@ -13908,19 +13994,19 @@
         <v>79</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>496</v>
+        <v>159</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -13932,16 +14018,16 @@
         <v>79</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>500</v>
+        <v>79</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>79</v>
@@ -13952,10 +14038,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13972,30 +14058,28 @@
         <v>79</v>
       </c>
       <c r="I102" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J102" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>361</v>
+        <v>496</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="Q102" t="s" s="2">
-        <v>505</v>
-      </c>
+      <c r="Q102" s="2"/>
       <c r="R102" t="s" s="2">
         <v>79</v>
       </c>
@@ -14039,7 +14123,7 @@
         <v>79</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14057,10 +14141,10 @@
         <v>79</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>506</v>
+        <v>133</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>133</v>
+        <v>501</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>79</v>
@@ -14071,10 +14155,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14085,7 +14169,7 @@
         <v>80</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>79</v>
@@ -14094,16 +14178,16 @@
         <v>79</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>195</v>
+        <v>338</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14130,13 +14214,13 @@
         <v>79</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>283</v>
+        <v>79</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>510</v>
+        <v>79</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>511</v>
+        <v>79</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>79</v>
@@ -14154,13 +14238,13 @@
         <v>79</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>79</v>
@@ -14172,10 +14256,10 @@
         <v>79</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>133</v>
+        <v>506</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>79</v>
@@ -14186,10 +14270,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14197,10 +14281,10 @@
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>79</v>
@@ -14209,16 +14293,16 @@
         <v>79</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>422</v>
+        <v>508</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14269,28 +14353,28 @@
         <v>79</v>
       </c>
       <c r="AF104" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AM104" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="AG104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ104" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="AK104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM104" t="s" s="2">
-        <v>133</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>79</v>
@@ -14301,10 +14385,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14315,7 +14399,7 @@
         <v>80</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>79</v>
@@ -14327,13 +14411,13 @@
         <v>79</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>152</v>
+        <v>514</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>153</v>
+        <v>515</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14360,13 +14444,13 @@
         <v>79</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>79</v>
+        <v>283</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>79</v>
+        <v>516</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>79</v>
+        <v>517</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>79</v>
@@ -14384,28 +14468,28 @@
         <v>79</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>154</v>
+        <v>513</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>79</v>
+        <v>518</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>155</v>
+        <v>519</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>79</v>
@@ -14416,14 +14500,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -14442,17 +14526,15 @@
         <v>79</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>135</v>
+        <v>521</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>169</v>
+        <v>522</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>523</v>
+      </c>
+      <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>79</v>
@@ -14501,7 +14583,7 @@
         <v>79</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>159</v>
+        <v>520</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -14513,16 +14595,16 @@
         <v>79</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>79</v>
+        <v>524</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>79</v>
@@ -14533,21 +14615,21 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>432</v>
+        <v>79</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>79</v>
@@ -14559,24 +14641,24 @@
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>135</v>
+        <v>385</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>433</v>
+        <v>526</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>434</v>
+        <v>527</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>528</v>
+      </c>
+      <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="Q107" s="2"/>
+      <c r="Q107" t="s" s="2">
+        <v>529</v>
+      </c>
       <c r="R107" t="s" s="2">
         <v>79</v>
       </c>
@@ -14620,25 +14702,25 @@
         <v>79</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>435</v>
+        <v>525</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>79</v>
+        <v>530</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>133</v>
@@ -14652,10 +14734,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14666,7 +14748,7 @@
         <v>80</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>79</v>
@@ -14678,13 +14760,13 @@
         <v>79</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -14711,13 +14793,13 @@
         <v>79</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>79</v>
+        <v>283</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>79</v>
+        <v>534</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>79</v>
+        <v>535</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>79</v>
@@ -14735,13 +14817,13 @@
         <v>79</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>79</v>
@@ -14753,7 +14835,7 @@
         <v>79</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>522</v>
+        <v>79</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>133</v>
@@ -14767,10 +14849,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>523</v>
+        <v>536</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>523</v>
+        <v>536</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14781,7 +14863,7 @@
         <v>80</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>79</v>
@@ -14793,13 +14875,13 @@
         <v>79</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>104</v>
+        <v>446</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>524</v>
+        <v>537</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>525</v>
+        <v>538</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -14850,19 +14932,19 @@
         <v>79</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>523</v>
+        <v>536</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>102</v>
+        <v>539</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>79</v>
@@ -14882,10 +14964,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>526</v>
+        <v>540</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>526</v>
+        <v>540</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14908,13 +14990,13 @@
         <v>79</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>314</v>
+        <v>151</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>527</v>
+        <v>152</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>528</v>
+        <v>153</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -14965,7 +15047,7 @@
         <v>79</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>526</v>
+        <v>154</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -14977,16 +15059,16 @@
         <v>79</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>529</v>
+        <v>79</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>79</v>
@@ -14997,21 +15079,21 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>79</v>
@@ -15023,15 +15105,17 @@
         <v>79</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>314</v>
+        <v>135</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>531</v>
+        <v>169</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="N111" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>79</v>
@@ -15080,28 +15164,28 @@
         <v>79</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>530</v>
+        <v>159</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>533</v>
+        <v>79</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>79</v>
@@ -15112,14 +15196,14 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>79</v>
+        <v>456</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -15132,22 +15216,26 @@
         <v>79</v>
       </c>
       <c r="I112" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>195</v>
+        <v>135</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>535</v>
+        <v>457</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="N112" s="2"/>
-      <c r="O112" s="2"/>
+        <v>458</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="O112" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P112" t="s" s="2">
         <v>79</v>
       </c>
@@ -15171,13 +15259,13 @@
         <v>79</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>283</v>
+        <v>79</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>537</v>
+        <v>79</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>538</v>
+        <v>79</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>79</v>
@@ -15195,7 +15283,7 @@
         <v>79</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>534</v>
+        <v>459</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -15207,13 +15295,13 @@
         <v>79</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>539</v>
+        <v>79</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>133</v>
@@ -15227,10 +15315,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15253,13 +15341,13 @@
         <v>79</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>195</v>
+        <v>151</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -15286,31 +15374,31 @@
         <v>79</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>283</v>
+        <v>79</v>
       </c>
       <c r="Y113" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF113" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="Z113" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="AA113" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF113" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -15328,7 +15416,7 @@
         <v>79</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>79</v>
+        <v>546</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>133</v>
@@ -15342,10 +15430,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15356,7 +15444,7 @@
         <v>80</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>79</v>
@@ -15368,17 +15456,15 @@
         <v>79</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>422</v>
+        <v>104</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>548</v>
-      </c>
+        <v>549</v>
+      </c>
+      <c r="N114" s="2"/>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>79</v>
@@ -15427,13 +15513,13 @@
         <v>79</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>79</v>
@@ -15445,10 +15531,10 @@
         <v>79</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>549</v>
+        <v>79</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>550</v>
+        <v>133</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>79</v>
@@ -15459,10 +15545,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15485,13 +15571,13 @@
         <v>79</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>151</v>
+        <v>338</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>152</v>
+        <v>551</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>153</v>
+        <v>552</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -15542,7 +15628,7 @@
         <v>79</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>154</v>
+        <v>550</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -15554,16 +15640,16 @@
         <v>79</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>79</v>
+        <v>553</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>79</v>
@@ -15574,21 +15660,21 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>79</v>
@@ -15600,17 +15686,15 @@
         <v>79</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>135</v>
+        <v>338</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>169</v>
+        <v>555</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>556</v>
+      </c>
+      <c r="N116" s="2"/>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>79</v>
@@ -15659,28 +15743,28 @@
         <v>79</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>159</v>
+        <v>554</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>79</v>
+        <v>557</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>79</v>
@@ -15691,14 +15775,14 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>432</v>
+        <v>79</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -15711,26 +15795,22 @@
         <v>79</v>
       </c>
       <c r="I117" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>135</v>
+        <v>195</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>433</v>
+        <v>559</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O117" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>560</v>
+      </c>
+      <c r="N117" s="2"/>
+      <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>79</v>
       </c>
@@ -15754,13 +15834,13 @@
         <v>79</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>79</v>
+        <v>283</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>79</v>
+        <v>561</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>79</v>
+        <v>562</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>79</v>
@@ -15778,7 +15858,7 @@
         <v>79</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>435</v>
+        <v>558</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -15790,13 +15870,13 @@
         <v>79</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>79</v>
+        <v>563</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>133</v>
@@ -15810,10 +15890,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>554</v>
+        <v>564</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>554</v>
+        <v>564</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15836,13 +15916,13 @@
         <v>79</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>314</v>
+        <v>195</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>555</v>
+        <v>565</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>556</v>
+        <v>566</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -15869,13 +15949,13 @@
         <v>79</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>79</v>
+        <v>283</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>79</v>
+        <v>567</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>79</v>
+        <v>568</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>79</v>
@@ -15893,7 +15973,7 @@
         <v>79</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>554</v>
+        <v>564</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -15911,10 +15991,10 @@
         <v>79</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>557</v>
+        <v>79</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>322</v>
+        <v>133</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>79</v>
@@ -15925,10 +16005,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>558</v>
+        <v>569</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>558</v>
+        <v>569</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15939,7 +16019,7 @@
         <v>80</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>79</v>
@@ -15951,15 +16031,17 @@
         <v>79</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>559</v>
+        <v>446</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>560</v>
+        <v>570</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="N119" s="2"/>
+        <v>571</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>572</v>
+      </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>79</v>
@@ -16008,13 +16090,13 @@
         <v>79</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>558</v>
+        <v>569</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>79</v>
@@ -16026,10 +16108,10 @@
         <v>79</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>562</v>
+        <v>573</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>563</v>
+        <v>574</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>79</v>
@@ -16040,10 +16122,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>564</v>
+        <v>575</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>564</v>
+        <v>575</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16066,13 +16148,13 @@
         <v>79</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>361</v>
+        <v>151</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>565</v>
+        <v>152</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>566</v>
+        <v>153</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -16123,7 +16205,7 @@
         <v>79</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>564</v>
+        <v>154</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -16135,16 +16217,16 @@
         <v>79</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK120" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>567</v>
+        <v>79</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>568</v>
+        <v>155</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>79</v>
@@ -16155,14 +16237,14 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
@@ -16181,15 +16263,17 @@
         <v>79</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>422</v>
+        <v>135</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>570</v>
+        <v>169</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="N121" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>79</v>
@@ -16238,7 +16322,7 @@
         <v>79</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>569</v>
+        <v>159</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -16250,7 +16334,7 @@
         <v>79</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>79</v>
@@ -16259,7 +16343,7 @@
         <v>79</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>79</v>
@@ -16270,42 +16354,46 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>79</v>
+        <v>456</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I122" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J122" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>152</v>
+        <v>457</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N122" s="2"/>
-      <c r="O122" s="2"/>
+        <v>458</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="O122" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P122" t="s" s="2">
         <v>79</v>
       </c>
@@ -16353,19 +16441,19 @@
         <v>79</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>154</v>
+        <v>459</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>79</v>
@@ -16374,7 +16462,7 @@
         <v>79</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>79</v>
@@ -16385,21 +16473,21 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>79</v>
@@ -16411,17 +16499,15 @@
         <v>79</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>135</v>
+        <v>338</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>169</v>
+        <v>579</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="N123" s="2"/>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>79</v>
@@ -16470,28 +16556,28 @@
         <v>79</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>159</v>
+        <v>578</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>79</v>
+        <v>581</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>155</v>
+        <v>346</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>79</v>
@@ -16502,46 +16588,42 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>432</v>
+        <v>79</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I124" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>135</v>
+        <v>583</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>433</v>
+        <v>584</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>585</v>
+      </c>
+      <c r="N124" s="2"/>
+      <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>79</v>
       </c>
@@ -16589,28 +16671,28 @@
         <v>79</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>435</v>
+        <v>582</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>79</v>
+        <v>586</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>133</v>
+        <v>587</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>79</v>
@@ -16621,10 +16703,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>575</v>
+        <v>588</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>575</v>
+        <v>588</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16647,13 +16729,13 @@
         <v>79</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>151</v>
+        <v>385</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>576</v>
+        <v>589</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>577</v>
+        <v>590</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -16680,11 +16762,13 @@
         <v>79</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="Y125" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z125" t="s" s="2">
-        <v>578</v>
+        <v>79</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>79</v>
@@ -16702,7 +16786,7 @@
         <v>79</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>575</v>
+        <v>588</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -16720,10 +16804,10 @@
         <v>79</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>79</v>
+        <v>591</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>133</v>
+        <v>592</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>79</v>
@@ -16734,10 +16818,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>579</v>
+        <v>593</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>579</v>
+        <v>593</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16748,7 +16832,7 @@
         <v>80</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>79</v>
@@ -16760,13 +16844,13 @@
         <v>79</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>383</v>
+        <v>446</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>580</v>
+        <v>594</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>581</v>
+        <v>595</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -16817,13 +16901,13 @@
         <v>79</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>579</v>
+        <v>593</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI126" t="s" s="2">
         <v>79</v>
@@ -16849,10 +16933,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>582</v>
+        <v>596</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>582</v>
+        <v>596</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16863,7 +16947,7 @@
         <v>80</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>79</v>
@@ -16875,13 +16959,13 @@
         <v>79</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>195</v>
+        <v>151</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>583</v>
+        <v>152</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>584</v>
+        <v>153</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -16908,13 +16992,13 @@
         <v>79</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>585</v>
+        <v>79</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>586</v>
+        <v>79</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>79</v>
@@ -16932,19 +17016,19 @@
         <v>79</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>582</v>
+        <v>154</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI127" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>79</v>
@@ -16953,7 +17037,7 @@
         <v>79</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>79</v>
@@ -16964,21 +17048,21 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>587</v>
+        <v>597</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>587</v>
+        <v>597</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>79</v>
@@ -16990,16 +17074,16 @@
         <v>79</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>588</v>
+        <v>135</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>589</v>
+        <v>169</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>590</v>
+        <v>170</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>591</v>
+        <v>171</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -17037,29 +17121,31 @@
         <v>79</v>
       </c>
       <c r="AB128" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="AC128" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD128" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE128" t="s" s="2">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>587</v>
+        <v>159</v>
       </c>
       <c r="AG128" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK128" t="s" s="2">
         <v>79</v>
@@ -17068,7 +17154,7 @@
         <v>79</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>79</v>
@@ -17079,46 +17165,46 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="C129" t="s" s="2">
-        <v>593</v>
-      </c>
+        <v>598</v>
+      </c>
+      <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>79</v>
+        <v>456</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I129" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>594</v>
+        <v>135</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>595</v>
+        <v>457</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>590</v>
+        <v>458</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="O129" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="O129" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P129" t="s" s="2">
         <v>79</v>
       </c>
@@ -17166,19 +17252,19 @@
         <v>79</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>587</v>
+        <v>459</v>
       </c>
       <c r="AG129" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>79</v>
@@ -17198,10 +17284,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17224,17 +17310,15 @@
         <v>79</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>588</v>
+        <v>151</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>591</v>
-      </c>
+        <v>601</v>
+      </c>
+      <c r="N130" s="2"/>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
         <v>79</v>
@@ -17259,13 +17343,11 @@
         <v>79</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y130" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="Y130" s="2"/>
       <c r="Z130" t="s" s="2">
-        <v>79</v>
+        <v>602</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>79</v>
@@ -17283,7 +17365,7 @@
         <v>79</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -17310,6 +17392,587 @@
         <v>79</v>
       </c>
       <c r="AO130" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E131" s="2"/>
+      <c r="F131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G131" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K131" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="L131" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="N131" s="2"/>
+      <c r="O131" s="2"/>
+      <c r="P131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q131" s="2"/>
+      <c r="R131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF131" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AG131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ131" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM131" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO131" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="C132" s="2"/>
+      <c r="D132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E132" s="2"/>
+      <c r="F132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K132" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L132" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="M132" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="N132" s="2"/>
+      <c r="O132" s="2"/>
+      <c r="P132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q132" s="2"/>
+      <c r="R132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X132" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="Y132" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="Z132" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AA132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF132" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="AG132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ132" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM132" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO132" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E133" s="2"/>
+      <c r="F133" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G133" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K133" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="L133" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="O133" s="2"/>
+      <c r="P133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q133" s="2"/>
+      <c r="R133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB133" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AC133" s="2"/>
+      <c r="AD133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE133" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AF133" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ133" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM133" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO133" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="C134" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="D134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E134" s="2"/>
+      <c r="F134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G134" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K134" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="L134" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="N134" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="O134" s="2"/>
+      <c r="P134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q134" s="2"/>
+      <c r="R134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF134" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="AG134" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH134" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ134" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM134" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO134" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="C135" s="2"/>
+      <c r="D135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E135" s="2"/>
+      <c r="F135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G135" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K135" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="L135" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="M135" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="N135" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="O135" s="2"/>
+      <c r="P135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q135" s="2"/>
+      <c r="R135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF135" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AG135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH135" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ135" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM135" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO135" t="s" s="2">
         <v>79</v>
       </c>
     </row>

--- a/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
+++ b/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4975" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4975" uniqueCount="622">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:25:23+00:00</t>
+    <t>2026-06-29T15:19:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1072,7 +1072,7 @@
     <t>Date de la vaccination</t>
   </si>
   <si>
-    <t>Si la date de la vaccination est inconnue, utiliser l'extension data-absent-reason précisant pourquoi elle n'est pas connue.</t>
+    <t>Date vaccine administered or was to be administered.</t>
   </si>
   <si>
     <t>When immunizations are given a specific date and time should always be known.   When immunizations are patient reported, a specific date might not be known.  Although partial dates are allowed, an adult patient might not be able to recall the year a childhood immunization was given. An exact date is always preferable, but the use of the String data type is acceptable when an exact date is not known. A small number of vaccines (e.g. live oral typhoid vaccine) are given as a series of patient self-administered dose over a span of time. In cases like this, often, only the first dose (typically a provider supervised dose) is recorded with the occurrence indicating the date/time of the first dose.</t>
@@ -1107,9 +1107,6 @@
   </si>
   <si>
     <t>Vaccine administration date</t>
-  </si>
-  <si>
-    <t>Date vaccine administered or was to be administered.</t>
   </si>
   <si>
     <t>Immunization.occurrence[x]:occurrenceDateTime.id</t>
@@ -10140,7 +10137,7 @@
         <v>351</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>341</v>
@@ -10225,10 +10222,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="B69" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10254,10 +10251,10 @@
         <v>151</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10340,10 +10337,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="B70" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10453,13 +10450,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="C71" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="C71" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>79</v>
@@ -10481,13 +10478,13 @@
         <v>79</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="M71" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10570,10 +10567,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="B72" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10685,10 +10682,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="B73" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10800,10 +10797,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="B74" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10843,7 +10840,7 @@
       </c>
       <c r="Q74" s="2"/>
       <c r="R74" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="S74" t="s" s="2">
         <v>79</v>
@@ -10917,10 +10914,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="B75" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10980,7 +10977,7 @@
       </c>
       <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>79</v>
@@ -11030,10 +11027,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="B76" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11059,10 +11056,10 @@
         <v>338</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11113,7 +11110,7 @@
         <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11145,10 +11142,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11174,10 +11171,10 @@
         <v>338</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11228,7 +11225,7 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11249,10 +11246,10 @@
         <v>79</v>
       </c>
       <c r="AM77" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AN77" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>79</v>
@@ -11260,10 +11257,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11286,16 +11283,16 @@
         <v>91</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11345,7 +11342,7 @@
         <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11363,13 +11360,13 @@
         <v>79</v>
       </c>
       <c r="AL78" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AM78" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="AM78" t="s" s="2">
+      <c r="AN78" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>79</v>
@@ -11377,10 +11374,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11406,13 +11403,13 @@
         <v>195</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11441,7 +11438,7 @@
         <v>283</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="Z79" t="s" s="2">
         <v>231</v>
@@ -11462,7 +11459,7 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11480,13 +11477,13 @@
         <v>79</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>79</v>
@@ -11494,10 +11491,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11520,13 +11517,13 @@
         <v>79</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="L80" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="L80" t="s" s="2">
+      <c r="M80" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11577,7 +11574,7 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11592,16 +11589,16 @@
         <v>102</v>
       </c>
       <c r="AK80" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AL80" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AL80" t="s" s="2">
+      <c r="AM80" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="AM80" t="s" s="2">
+      <c r="AN80" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>79</v>
@@ -11609,10 +11606,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11635,13 +11632,13 @@
         <v>79</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="L81" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="L81" t="s" s="2">
+      <c r="M81" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11692,7 +11689,7 @@
         <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11710,24 +11707,24 @@
         <v>79</v>
       </c>
       <c r="AL81" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AM81" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="AM81" t="s" s="2">
+      <c r="AN81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO81" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>412</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11753,10 +11750,10 @@
         <v>151</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11807,7 +11804,7 @@
         <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -11825,24 +11822,24 @@
         <v>79</v>
       </c>
       <c r="AL82" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AM82" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="AM82" t="s" s="2">
+      <c r="AN82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO82" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>418</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11865,13 +11862,13 @@
         <v>79</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="L83" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="M83" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11922,7 +11919,7 @@
         <v>79</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -11940,10 +11937,10 @@
         <v>79</v>
       </c>
       <c r="AL83" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AM83" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>79</v>
@@ -11954,10 +11951,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11983,10 +11980,10 @@
         <v>195</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12017,7 +12014,7 @@
       </c>
       <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>79</v>
@@ -12035,7 +12032,7 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12053,24 +12050,24 @@
         <v>79</v>
       </c>
       <c r="AL84" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AM84" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="AM84" t="s" s="2">
+      <c r="AN84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO84" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>431</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12096,10 +12093,10 @@
         <v>195</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12130,7 +12127,7 @@
       </c>
       <c r="Y85" s="2"/>
       <c r="Z85" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>79</v>
@@ -12148,7 +12145,7 @@
         <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12166,24 +12163,24 @@
         <v>79</v>
       </c>
       <c r="AL85" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AM85" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="AM85" t="s" s="2">
+      <c r="AN85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO85" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>438</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12206,13 +12203,13 @@
         <v>79</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="L86" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="L86" t="s" s="2">
+      <c r="M86" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12263,7 +12260,7 @@
         <v>79</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12281,10 +12278,10 @@
         <v>79</v>
       </c>
       <c r="AL86" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AM86" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>79</v>
@@ -12295,10 +12292,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12321,13 +12318,13 @@
         <v>91</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="L87" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="M87" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12366,7 +12363,7 @@
         <v>79</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AC87" s="2"/>
       <c r="AD87" t="s" s="2">
@@ -12376,7 +12373,7 @@
         <v>139</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12391,13 +12388,13 @@
         <v>102</v>
       </c>
       <c r="AK87" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AL87" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="AL87" t="s" s="2">
+      <c r="AM87" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>79</v>
@@ -12408,10 +12405,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12523,10 +12520,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12640,14 +12637,14 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -12669,10 +12666,10 @@
         <v>135</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="N90" t="s" s="2">
         <v>171</v>
@@ -12727,7 +12724,7 @@
         <v>79</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12759,10 +12756,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12788,10 +12785,10 @@
         <v>195</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12818,14 +12815,14 @@
         <v>79</v>
       </c>
       <c r="X91" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="Y91" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="Y91" t="s" s="2">
+      <c r="Z91" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="Z91" t="s" s="2">
-        <v>465</v>
-      </c>
       <c r="AA91" t="s" s="2">
         <v>79</v>
       </c>
@@ -12842,7 +12839,7 @@
         <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -12857,13 +12854,13 @@
         <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM91" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="AL91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>79</v>
@@ -12874,10 +12871,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12900,16 +12897,16 @@
         <v>91</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="L92" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="L92" t="s" s="2">
+      <c r="M92" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12959,7 +12956,7 @@
         <v>79</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>90</v>
@@ -12974,16 +12971,16 @@
         <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM92" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="AL92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM92" t="s" s="2">
+      <c r="AN92" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>79</v>
@@ -12991,13 +12988,13 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="C93" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="C93" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="D93" t="s" s="2">
         <v>79</v>
@@ -13019,13 +13016,13 @@
         <v>91</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13076,7 +13073,7 @@
         <v>79</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13091,13 +13088,13 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AL93" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="AL93" t="s" s="2">
+      <c r="AM93" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="AM93" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>79</v>
@@ -13108,10 +13105,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13223,10 +13220,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13340,14 +13337,14 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -13369,10 +13366,10 @@
         <v>135</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="N96" t="s" s="2">
         <v>171</v>
@@ -13427,7 +13424,7 @@
         <v>79</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13459,10 +13456,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13488,10 +13485,10 @@
         <v>195</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13503,7 +13500,7 @@
         <v>79</v>
       </c>
       <c r="S97" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="T97" t="s" s="2">
         <v>79</v>
@@ -13518,14 +13515,14 @@
         <v>79</v>
       </c>
       <c r="X97" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="Y97" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="Y97" t="s" s="2">
+      <c r="Z97" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="Z97" t="s" s="2">
-        <v>465</v>
-      </c>
       <c r="AA97" t="s" s="2">
         <v>79</v>
       </c>
@@ -13542,7 +13539,7 @@
         <v>79</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13557,13 +13554,13 @@
         <v>102</v>
       </c>
       <c r="AK97" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM97" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>79</v>
@@ -13574,10 +13571,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13600,16 +13597,16 @@
         <v>91</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="M98" t="s" s="2">
+      <c r="N98" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13659,7 +13656,7 @@
         <v>79</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>90</v>
@@ -13674,16 +13671,16 @@
         <v>102</v>
       </c>
       <c r="AK98" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM98" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="AL98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM98" t="s" s="2">
+      <c r="AN98" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>79</v>
@@ -13691,10 +13688,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13717,13 +13714,13 @@
         <v>91</v>
       </c>
       <c r="K99" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="L99" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="L99" t="s" s="2">
+      <c r="M99" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13774,7 +13771,7 @@
         <v>79</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -13789,13 +13786,13 @@
         <v>102</v>
       </c>
       <c r="AK99" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AL99" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="AL99" t="s" s="2">
+      <c r="AM99" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>79</v>
@@ -13806,10 +13803,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13921,10 +13918,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14038,10 +14035,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14064,16 +14061,16 @@
         <v>91</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="L102" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="M102" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14123,7 +14120,7 @@
         <v>79</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14144,7 +14141,7 @@
         <v>133</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>79</v>
@@ -14155,10 +14152,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14184,10 +14181,10 @@
         <v>338</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14238,7 +14235,7 @@
         <v>79</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14259,7 +14256,7 @@
         <v>133</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>79</v>
@@ -14270,10 +14267,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14296,13 +14293,13 @@
         <v>91</v>
       </c>
       <c r="K104" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="L104" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="L104" t="s" s="2">
+      <c r="M104" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14353,7 +14350,7 @@
         <v>79</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>90</v>
@@ -14374,7 +14371,7 @@
         <v>133</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>79</v>
@@ -14385,10 +14382,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14414,10 +14411,10 @@
         <v>195</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14447,11 +14444,11 @@
         <v>283</v>
       </c>
       <c r="Y105" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="Z105" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="Z105" t="s" s="2">
-        <v>517</v>
-      </c>
       <c r="AA105" t="s" s="2">
         <v>79</v>
       </c>
@@ -14468,7 +14465,7 @@
         <v>79</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14483,13 +14480,13 @@
         <v>102</v>
       </c>
       <c r="AK105" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM105" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="AL105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>79</v>
@@ -14500,10 +14497,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14526,13 +14523,13 @@
         <v>79</v>
       </c>
       <c r="K106" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="L106" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="L106" t="s" s="2">
+      <c r="M106" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14583,7 +14580,7 @@
         <v>79</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -14598,7 +14595,7 @@
         <v>102</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>79</v>
@@ -14615,10 +14612,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14641,23 +14638,23 @@
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="N107" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q107" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="R107" t="s" s="2">
         <v>79</v>
@@ -14702,7 +14699,7 @@
         <v>79</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -14720,7 +14717,7 @@
         <v>79</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>133</v>
@@ -14734,10 +14731,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14763,10 +14760,10 @@
         <v>195</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -14796,11 +14793,11 @@
         <v>283</v>
       </c>
       <c r="Y108" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="Z108" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="Z108" t="s" s="2">
-        <v>535</v>
-      </c>
       <c r="AA108" t="s" s="2">
         <v>79</v>
       </c>
@@ -14817,7 +14814,7 @@
         <v>79</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -14849,10 +14846,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14875,13 +14872,13 @@
         <v>79</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="L109" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M109" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -14932,7 +14929,7 @@
         <v>79</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -14944,7 +14941,7 @@
         <v>79</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>79</v>
@@ -14964,10 +14961,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15079,10 +15076,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15196,14 +15193,14 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -15225,10 +15222,10 @@
         <v>135</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="N112" t="s" s="2">
         <v>171</v>
@@ -15283,7 +15280,7 @@
         <v>79</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -15315,10 +15312,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15344,10 +15341,10 @@
         <v>151</v>
       </c>
       <c r="L113" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -15398,7 +15395,7 @@
         <v>79</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -15416,7 +15413,7 @@
         <v>79</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>133</v>
@@ -15430,10 +15427,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15459,10 +15456,10 @@
         <v>104</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -15513,7 +15510,7 @@
         <v>79</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -15545,10 +15542,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15574,10 +15571,10 @@
         <v>338</v>
       </c>
       <c r="L115" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="M115" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -15628,7 +15625,7 @@
         <v>79</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -15646,7 +15643,7 @@
         <v>79</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>133</v>
@@ -15660,10 +15657,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15689,10 +15686,10 @@
         <v>338</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -15743,7 +15740,7 @@
         <v>79</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -15761,7 +15758,7 @@
         <v>79</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>133</v>
@@ -15775,10 +15772,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15804,10 +15801,10 @@
         <v>195</v>
       </c>
       <c r="L117" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M117" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -15837,11 +15834,11 @@
         <v>283</v>
       </c>
       <c r="Y117" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="Z117" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="Z117" t="s" s="2">
-        <v>562</v>
-      </c>
       <c r="AA117" t="s" s="2">
         <v>79</v>
       </c>
@@ -15858,7 +15855,7 @@
         <v>79</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -15876,7 +15873,7 @@
         <v>79</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>133</v>
@@ -15890,10 +15887,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15919,10 +15916,10 @@
         <v>195</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -15952,11 +15949,11 @@
         <v>283</v>
       </c>
       <c r="Y118" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="Z118" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="Z118" t="s" s="2">
-        <v>568</v>
-      </c>
       <c r="AA118" t="s" s="2">
         <v>79</v>
       </c>
@@ -15973,7 +15970,7 @@
         <v>79</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16005,10 +16002,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16031,16 +16028,16 @@
         <v>79</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="M119" t="s" s="2">
+      <c r="N119" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -16090,7 +16087,7 @@
         <v>79</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -16108,10 +16105,10 @@
         <v>79</v>
       </c>
       <c r="AL119" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AM119" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="AM119" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>79</v>
@@ -16122,10 +16119,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16237,10 +16234,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16354,14 +16351,14 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -16383,10 +16380,10 @@
         <v>135</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="N122" t="s" s="2">
         <v>171</v>
@@ -16441,7 +16438,7 @@
         <v>79</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -16473,10 +16470,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16502,10 +16499,10 @@
         <v>338</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -16556,7 +16553,7 @@
         <v>79</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -16574,7 +16571,7 @@
         <v>79</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>346</v>
@@ -16588,10 +16585,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16614,13 +16611,13 @@
         <v>79</v>
       </c>
       <c r="K124" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="L124" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="L124" t="s" s="2">
+      <c r="M124" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -16671,7 +16668,7 @@
         <v>79</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -16689,10 +16686,10 @@
         <v>79</v>
       </c>
       <c r="AL124" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AM124" t="s" s="2">
         <v>586</v>
-      </c>
-      <c r="AM124" t="s" s="2">
-        <v>587</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>79</v>
@@ -16703,10 +16700,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16729,13 +16726,13 @@
         <v>79</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>589</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>590</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -16786,7 +16783,7 @@
         <v>79</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -16804,10 +16801,10 @@
         <v>79</v>
       </c>
       <c r="AL125" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="AM125" t="s" s="2">
         <v>591</v>
-      </c>
-      <c r="AM125" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>79</v>
@@ -16818,10 +16815,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16844,13 +16841,13 @@
         <v>79</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -16901,7 +16898,7 @@
         <v>79</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -16933,10 +16930,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17048,10 +17045,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17165,14 +17162,14 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
@@ -17194,10 +17191,10 @@
         <v>135</v>
       </c>
       <c r="L129" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M129" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M129" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="N129" t="s" s="2">
         <v>171</v>
@@ -17252,7 +17249,7 @@
         <v>79</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -17284,10 +17281,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17313,10 +17310,10 @@
         <v>151</v>
       </c>
       <c r="L130" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M130" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -17347,7 +17344,7 @@
       </c>
       <c r="Y130" s="2"/>
       <c r="Z130" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>79</v>
@@ -17365,7 +17362,7 @@
         <v>79</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -17397,10 +17394,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17423,13 +17420,13 @@
         <v>79</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="M131" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>605</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -17480,7 +17477,7 @@
         <v>79</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -17512,10 +17509,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17541,10 +17538,10 @@
         <v>195</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="M132" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -17574,11 +17571,11 @@
         <v>114</v>
       </c>
       <c r="Y132" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="Z132" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="Z132" t="s" s="2">
-        <v>610</v>
-      </c>
       <c r="AA132" t="s" s="2">
         <v>79</v>
       </c>
@@ -17595,7 +17592,7 @@
         <v>79</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -17627,10 +17624,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17653,16 +17650,16 @@
         <v>79</v>
       </c>
       <c r="K133" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="L133" t="s" s="2">
         <v>612</v>
       </c>
-      <c r="L133" t="s" s="2">
+      <c r="M133" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="M133" t="s" s="2">
+      <c r="N133" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>615</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -17710,7 +17707,7 @@
         <v>139</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>90</v>
@@ -17742,13 +17739,13 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="C134" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="B134" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="C134" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="D134" t="s" s="2">
         <v>79</v>
@@ -17770,16 +17767,16 @@
         <v>79</v>
       </c>
       <c r="K134" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="L134" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="L134" t="s" s="2">
-        <v>619</v>
-      </c>
       <c r="M134" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="N134" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>615</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -17829,7 +17826,7 @@
         <v>79</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>90</v>
@@ -17861,10 +17858,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17887,16 +17884,16 @@
         <v>79</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="M135" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="M135" t="s" s="2">
-        <v>622</v>
-      </c>
       <c r="N135" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -17946,7 +17943,7 @@
         <v>79</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>

--- a/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
+++ b/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:19:05+00:00</t>
+    <t>2026-07-20T14:29:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1339,7 +1339,7 @@
     <t>Body site where vaccine was administered.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-immunization-approach-site-code-cisis|20260420150249</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-immunization-approach-site-code-cisis|20260619134041</t>
   </si>
   <si>
     <t>RXR-2</t>
@@ -1360,7 +1360,7 @@
     <t>The path by which the vaccine product is taken into the body.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-immunization-route-code-cisis|20260420150250</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-immunization-route-code-cisis|20260619134042</t>
   </si>
   <si>
     <t>RXR-1</t>
@@ -1532,7 +1532,7 @@
 </t>
   </si>
   <si>
-    <t>Commentaire</t>
+    <t>Additional immunization notes</t>
   </si>
   <si>
     <t>Extra information about the immunization that is not conveyed by the other attributes.</t>
@@ -1879,7 +1879,7 @@
     <t>One possible path to achieve presumed immunity against a disease - within the context of an authority.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActSubstanceAdministrationImmunizationCode-cisis|20260420150251</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActSubstanceAdministrationImmunizationCode-cisis|20260619134043</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.authority</t>
@@ -13702,7 +13702,7 @@
         <v>80</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>79</v>

--- a/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
+++ b/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T14:29:12+00:00</t>
+    <t>2026-07-21T07:29:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
+++ b/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4975" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5709" uniqueCount="645">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T07:29:40+00:00</t>
+    <t>2026-07-21T07:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -811,6 +811,76 @@
   </si>
   <si>
     <t>Allows tracing of an authorization for the Immunization.</t>
+  </si>
+  <si>
+    <t>Immunization.extension:ImmunizationAdministeredProductR5</t>
+  </si>
+  <si>
+    <t>ImmunizationAdministeredProductR5</t>
+  </si>
+  <si>
+    <t>Dose d'antigène administrée</t>
+  </si>
+  <si>
+    <t>Immunization.extension:ImmunizationAdministeredProductR5.id</t>
+  </si>
+  <si>
+    <t>Immunization.extension:ImmunizationAdministeredProductR5.extension</t>
+  </si>
+  <si>
+    <t>Immunization.extension:ImmunizationAdministeredProductR5.extension:_datatype</t>
+  </si>
+  <si>
+    <t>Immunization.extension:ImmunizationAdministeredProductR5.extension:_datatype.id</t>
+  </si>
+  <si>
+    <t>Immunization.extension:ImmunizationAdministeredProductR5.extension:_datatype.extension</t>
+  </si>
+  <si>
+    <t>Immunization.extension:ImmunizationAdministeredProductR5.extension:_datatype.url</t>
+  </si>
+  <si>
+    <t>Immunization.extension:ImmunizationAdministeredProductR5.extension:_datatype.value[x]</t>
+  </si>
+  <si>
+    <t>Immunization.extension:ImmunizationAdministeredProductR5.extension:concept</t>
+  </si>
+  <si>
+    <t>Immunization.extension:ImmunizationAdministeredProductR5.extension:concept.id</t>
+  </si>
+  <si>
+    <t>Immunization.extension:ImmunizationAdministeredProductR5.extension:concept.extension</t>
+  </si>
+  <si>
+    <t>Immunization.extension:ImmunizationAdministeredProductR5.extension:concept.url</t>
+  </si>
+  <si>
+    <t>Immunization.extension:ImmunizationAdministeredProductR5.extension:concept.value[x]</t>
+  </si>
+  <si>
+    <t>Immunization.extension:ImmunizationAdministeredProductR5.extension:reference</t>
+  </si>
+  <si>
+    <t>Immunization.extension:ImmunizationAdministeredProductR5.extension:reference.id</t>
+  </si>
+  <si>
+    <t>Immunization.extension:ImmunizationAdministeredProductR5.extension:reference.extension</t>
+  </si>
+  <si>
+    <t>Immunization.extension:ImmunizationAdministeredProductR5.extension:reference.url</t>
+  </si>
+  <si>
+    <t>Immunization.extension:ImmunizationAdministeredProductR5.extension:reference.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Medication|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Immunization.extension:ImmunizationAdministeredProductR5.url</t>
+  </si>
+  <si>
+    <t>Immunization.extension:ImmunizationAdministeredProductR5.value[x]</t>
   </si>
   <si>
     <t>Immunization.modifierExtension</t>
@@ -2251,12 +2321,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO135"/>
+  <dimension ref="A1:AO155"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="66.5703125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="74.4765625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="39.45703125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="21.08984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="30.2578125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -8591,43 +8661,43 @@
         <v>256</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="C55" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="C55" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="D55" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>258</v>
+        <v>146</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>79</v>
       </c>
@@ -8675,7 +8745,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>260</v>
+        <v>140</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8696,7 +8766,7 @@
         <v>79</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>79</v>
@@ -8707,10 +8777,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>261</v>
+        <v>150</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8721,7 +8791,7 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>79</v>
@@ -8733,13 +8803,13 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>262</v>
+        <v>151</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>263</v>
+        <v>152</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>264</v>
+        <v>153</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8790,42 +8860,42 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>261</v>
+        <v>154</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>265</v>
+        <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>266</v>
+        <v>155</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>267</v>
+        <v>79</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>268</v>
+        <v>79</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>269</v>
+        <v>157</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8836,29 +8906,27 @@
         <v>90</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>270</v>
+        <v>136</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>79</v>
@@ -8883,55 +8951,55 @@
         <v>79</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>273</v>
+        <v>79</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>274</v>
+        <v>79</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>275</v>
+        <v>79</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>269</v>
+        <v>159</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>276</v>
+        <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>277</v>
+        <v>79</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>278</v>
+        <v>79</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>79</v>
@@ -8939,18 +9007,20 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="C58" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="C58" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="D58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>90</v>
@@ -8965,17 +9035,15 @@
         <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>195</v>
+        <v>135</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>280</v>
+        <v>162</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>79</v>
@@ -9000,13 +9068,13 @@
         <v>79</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>283</v>
+        <v>79</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>284</v>
+        <v>79</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>285</v>
+        <v>79</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>79</v>
@@ -9024,28 +9092,28 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>279</v>
+        <v>159</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>286</v>
+        <v>79</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>287</v>
+        <v>79</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>79</v>
@@ -9056,10 +9124,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>288</v>
+        <v>262</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>288</v>
+        <v>165</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9067,7 +9135,7 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>90</v>
@@ -9079,16 +9147,16 @@
         <v>79</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>195</v>
+        <v>151</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>289</v>
+        <v>152</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>290</v>
+        <v>153</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9115,13 +9183,13 @@
         <v>79</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>291</v>
+        <v>79</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>292</v>
+        <v>79</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>79</v>
@@ -9139,10 +9207,10 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>288</v>
+        <v>154</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>90</v>
@@ -9151,41 +9219,41 @@
         <v>79</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>293</v>
+        <v>79</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>294</v>
+        <v>79</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>295</v>
+        <v>155</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>296</v>
+        <v>79</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>297</v>
+        <v>79</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>298</v>
+        <v>263</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>298</v>
+        <v>167</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>79</v>
@@ -9197,15 +9265,17 @@
         <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>79</v>
@@ -9242,31 +9312,31 @@
         <v>79</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>79</v>
@@ -9286,21 +9356,21 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>299</v>
+        <v>264</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>299</v>
+        <v>173</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>79</v>
@@ -9312,16 +9382,16 @@
         <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9329,7 +9399,7 @@
       </c>
       <c r="Q61" s="2"/>
       <c r="R61" t="s" s="2">
-        <v>79</v>
+        <v>177</v>
       </c>
       <c r="S61" t="s" s="2">
         <v>79</v>
@@ -9359,31 +9429,31 @@
         <v>79</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>141</v>
+        <v>79</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>79</v>
@@ -9392,7 +9462,7 @@
         <v>79</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>79</v>
@@ -9403,10 +9473,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>300</v>
+        <v>265</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>300</v>
+        <v>180</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9417,7 +9487,7 @@
         <v>90</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>79</v>
@@ -9426,29 +9496,27 @@
         <v>79</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>301</v>
+        <v>151</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>302</v>
+        <v>181</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>303</v>
+        <v>182</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
-        <v>79</v>
+        <v>184</v>
       </c>
       <c r="S62" t="s" s="2">
         <v>79</v>
@@ -9478,23 +9546,25 @@
         <v>79</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AC62" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>307</v>
+        <v>185</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>79</v>
@@ -9506,10 +9576,10 @@
         <v>79</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>308</v>
+        <v>79</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>309</v>
+        <v>133</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>79</v>
@@ -9520,20 +9590,20 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>310</v>
+        <v>266</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>300</v>
+        <v>157</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>311</v>
+        <v>187</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>90</v>
@@ -9545,22 +9615,22 @@
         <v>79</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>301</v>
+        <v>135</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>302</v>
+        <v>188</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>303</v>
+        <v>189</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>304</v>
+        <v>190</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>305</v>
+        <v>190</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>79</v>
@@ -9585,11 +9655,13 @@
         <v>79</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="Y63" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z63" t="s" s="2">
-        <v>312</v>
+        <v>79</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>79</v>
@@ -9607,7 +9679,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>307</v>
+        <v>159</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9619,16 +9691,16 @@
         <v>79</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>308</v>
+        <v>79</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>309</v>
+        <v>79</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>79</v>
@@ -9639,10 +9711,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>313</v>
+        <v>267</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>313</v>
+        <v>165</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9662,23 +9734,19 @@
         <v>79</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K64" t="s" s="2">
         <v>151</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>314</v>
+        <v>152</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>79</v>
       </c>
@@ -9726,7 +9794,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>318</v>
+        <v>154</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9738,16 +9806,16 @@
         <v>79</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>319</v>
+        <v>79</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>320</v>
+        <v>155</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>79</v>
@@ -9758,21 +9826,21 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>321</v>
+        <v>268</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>321</v>
+        <v>167</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>79</v>
@@ -9781,18 +9849,20 @@
         <v>79</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>322</v>
+        <v>135</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>323</v>
+        <v>169</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>79</v>
@@ -9829,43 +9899,43 @@
         <v>79</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>321</v>
+        <v>159</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>325</v>
+        <v>79</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>326</v>
+        <v>79</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>327</v>
+        <v>155</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>328</v>
+        <v>79</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>79</v>
@@ -9873,10 +9943,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>329</v>
+        <v>269</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>329</v>
+        <v>173</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9884,7 +9954,7 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>90</v>
@@ -9899,22 +9969,24 @@
         <v>79</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>330</v>
+        <v>104</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>331</v>
+        <v>174</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
-        <v>79</v>
+        <v>187</v>
       </c>
       <c r="S66" t="s" s="2">
         <v>79</v>
@@ -9956,10 +10028,10 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>329</v>
+        <v>178</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>90</v>
@@ -9968,19 +10040,19 @@
         <v>79</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>333</v>
+        <v>79</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>334</v>
+        <v>79</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>335</v>
+        <v>133</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>336</v>
+        <v>79</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>79</v>
@@ -9988,10 +10060,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>337</v>
+        <v>270</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>337</v>
+        <v>180</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9999,7 +10071,7 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>90</v>
@@ -10011,20 +10083,18 @@
         <v>79</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>338</v>
+        <v>195</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>339</v>
+        <v>196</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>79</v>
@@ -10061,20 +10131,22 @@
         <v>79</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="AC67" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>343</v>
+        <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>337</v>
+        <v>185</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>90</v>
@@ -10086,30 +10158,30 @@
         <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>344</v>
+        <v>79</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>345</v>
+        <v>79</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>346</v>
+        <v>133</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>347</v>
+        <v>79</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>348</v>
+        <v>79</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>349</v>
+        <v>271</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>337</v>
+        <v>157</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>350</v>
+        <v>199</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>79</v>
@@ -10128,20 +10200,18 @@
         <v>79</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>338</v>
+        <v>135</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>351</v>
+        <v>136</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>79</v>
@@ -10190,42 +10260,42 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>337</v>
+        <v>159</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>344</v>
+        <v>79</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>345</v>
+        <v>79</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>346</v>
+        <v>79</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>347</v>
+        <v>79</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>348</v>
+        <v>79</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>352</v>
+        <v>272</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>353</v>
+        <v>165</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10251,10 +10321,10 @@
         <v>151</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>354</v>
+        <v>152</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>355</v>
+        <v>153</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10326,7 +10396,7 @@
         <v>79</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>79</v>
+        <v>155</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>79</v>
@@ -10337,10 +10407,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>356</v>
+        <v>273</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>357</v>
+        <v>167</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10351,7 +10421,7 @@
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>79</v>
@@ -10410,7 +10480,9 @@
       <c r="AB70" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="AC70" s="2"/>
+      <c r="AC70" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="AD70" t="s" s="2">
         <v>79</v>
       </c>
@@ -10450,20 +10522,18 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>358</v>
+        <v>274</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="C71" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>90</v>
@@ -10478,22 +10548,24 @@
         <v>79</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>360</v>
+        <v>104</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>361</v>
+        <v>174</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
-        <v>79</v>
+        <v>199</v>
       </c>
       <c r="S71" t="s" s="2">
         <v>79</v>
@@ -10535,19 +10607,19 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>141</v>
+        <v>79</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>79</v>
@@ -10556,7 +10628,7 @@
         <v>79</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>79</v>
@@ -10567,10 +10639,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>363</v>
+        <v>275</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>364</v>
+        <v>180</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10593,13 +10665,13 @@
         <v>79</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>151</v>
+        <v>276</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>152</v>
+        <v>205</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>153</v>
+        <v>206</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10650,7 +10722,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10662,7 +10734,7 @@
         <v>79</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>79</v>
@@ -10671,7 +10743,7 @@
         <v>79</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>79</v>
@@ -10682,10 +10754,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>365</v>
+        <v>277</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>366</v>
+        <v>208</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10693,10 +10765,10 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>79</v>
@@ -10708,22 +10780,24 @@
         <v>79</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q73" s="2"/>
       <c r="R73" t="s" s="2">
-        <v>79</v>
+        <v>209</v>
       </c>
       <c r="S73" t="s" s="2">
         <v>79</v>
@@ -10753,31 +10827,31 @@
         <v>79</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>141</v>
+        <v>79</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>79</v>
@@ -10786,7 +10860,7 @@
         <v>79</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>79</v>
@@ -10797,10 +10871,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>367</v>
+        <v>278</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>368</v>
+        <v>211</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10808,10 +10882,10 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>79</v>
@@ -10823,24 +10897,22 @@
         <v>79</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>104</v>
+        <v>212</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q74" s="2"/>
       <c r="R74" t="s" s="2">
-        <v>369</v>
+        <v>79</v>
       </c>
       <c r="S74" t="s" s="2">
         <v>79</v>
@@ -10882,10 +10954,10 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>90</v>
@@ -10894,7 +10966,7 @@
         <v>79</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>79</v>
@@ -10914,42 +10986,46 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>370</v>
+        <v>279</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>371</v>
+        <v>279</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>195</v>
+        <v>135</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>181</v>
+        <v>280</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>79</v>
       </c>
@@ -10973,11 +11049,13 @@
         <v>79</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="Y75" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z75" t="s" s="2">
-        <v>372</v>
+        <v>79</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>79</v>
@@ -10995,19 +11073,19 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>185</v>
+        <v>283</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>79</v>
@@ -11027,10 +11105,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>373</v>
+        <v>284</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>374</v>
+        <v>284</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11041,7 +11119,7 @@
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>79</v>
@@ -11053,13 +11131,13 @@
         <v>79</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>338</v>
+        <v>285</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>375</v>
+        <v>286</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>376</v>
+        <v>287</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11110,42 +11188,42 @@
         <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>377</v>
+        <v>284</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>79</v>
+        <v>288</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>79</v>
+        <v>289</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>79</v>
+        <v>290</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>79</v>
+        <v>291</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>378</v>
+        <v>292</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>378</v>
+        <v>292</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11153,7 +11231,7 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>90</v>
@@ -11162,21 +11240,23 @@
         <v>79</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>338</v>
+        <v>110</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>379</v>
+        <v>293</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>79</v>
@@ -11201,13 +11281,13 @@
         <v>79</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>79</v>
+        <v>296</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>79</v>
+        <v>297</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>79</v>
+        <v>298</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>79</v>
@@ -11225,10 +11305,10 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>378</v>
+        <v>292</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>90</v>
@@ -11240,16 +11320,16 @@
         <v>102</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>79</v>
+        <v>299</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>381</v>
+        <v>300</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>382</v>
+        <v>301</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>79</v>
@@ -11257,10 +11337,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>383</v>
+        <v>302</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>383</v>
+        <v>302</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11280,19 +11360,19 @@
         <v>79</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>384</v>
+        <v>195</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>385</v>
+        <v>303</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>386</v>
+        <v>304</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>387</v>
+        <v>305</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11318,13 +11398,13 @@
         <v>79</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>79</v>
+        <v>306</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>79</v>
+        <v>307</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>79</v>
+        <v>308</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>79</v>
@@ -11342,7 +11422,7 @@
         <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>383</v>
+        <v>302</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11357,16 +11437,16 @@
         <v>102</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>79</v>
+        <v>309</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>388</v>
+        <v>79</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>389</v>
+        <v>310</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>390</v>
+        <v>79</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>79</v>
@@ -11374,10 +11454,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>391</v>
+        <v>311</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>391</v>
+        <v>311</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11385,7 +11465,7 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G79" t="s" s="2">
         <v>90</v>
@@ -11397,20 +11477,18 @@
         <v>79</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K79" t="s" s="2">
         <v>195</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>392</v>
+        <v>312</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>394</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>79</v>
@@ -11435,13 +11513,13 @@
         <v>79</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>283</v>
+        <v>114</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>395</v>
+        <v>314</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>231</v>
+        <v>315</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>79</v>
@@ -11459,10 +11537,10 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>391</v>
+        <v>311</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>90</v>
@@ -11474,27 +11552,27 @@
         <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>79</v>
+        <v>316</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>388</v>
+        <v>317</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>396</v>
+        <v>318</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>390</v>
+        <v>319</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>79</v>
+        <v>320</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>397</v>
+        <v>321</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>397</v>
+        <v>321</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11517,13 +11595,13 @@
         <v>79</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>398</v>
+        <v>151</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>399</v>
+        <v>152</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>400</v>
+        <v>153</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11574,7 +11652,7 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>397</v>
+        <v>154</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11586,19 +11664,19 @@
         <v>79</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>401</v>
+        <v>79</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>402</v>
+        <v>79</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>403</v>
+        <v>155</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>404</v>
+        <v>79</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>79</v>
@@ -11606,21 +11684,21 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>405</v>
+        <v>322</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>405</v>
+        <v>322</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>79</v>
@@ -11632,15 +11710,17 @@
         <v>79</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>406</v>
+        <v>135</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>407</v>
+        <v>169</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N81" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>79</v>
@@ -11677,54 +11757,54 @@
         <v>79</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>405</v>
+        <v>159</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>409</v>
+        <v>79</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>410</v>
+        <v>155</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>411</v>
+        <v>79</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>412</v>
+        <v>323</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>412</v>
+        <v>323</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11732,10 +11812,10 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>79</v>
@@ -11744,19 +11824,23 @@
         <v>79</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>151</v>
+        <v>324</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>413</v>
+        <v>325</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>79</v>
       </c>
@@ -11792,25 +11876,23 @@
         <v>79</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="AC82" s="2"/>
       <c r="AD82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>412</v>
+        <v>330</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>79</v>
@@ -11822,32 +11904,34 @@
         <v>79</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>415</v>
+        <v>331</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>416</v>
+        <v>332</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>417</v>
+        <v>79</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>418</v>
+        <v>333</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="C83" s="2"/>
+        <v>323</v>
+      </c>
+      <c r="C83" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="D83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G83" t="s" s="2">
         <v>90</v>
@@ -11859,19 +11943,23 @@
         <v>79</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>419</v>
+        <v>324</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>420</v>
+        <v>325</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>79</v>
       </c>
@@ -11895,13 +11983,11 @@
         <v>79</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="Y83" s="2"/>
       <c r="Z83" t="s" s="2">
-        <v>79</v>
+        <v>335</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>79</v>
@@ -11919,13 +12005,13 @@
         <v>79</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>418</v>
+        <v>330</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>79</v>
@@ -11937,10 +12023,10 @@
         <v>79</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>422</v>
+        <v>331</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>423</v>
+        <v>332</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>79</v>
@@ -11951,10 +12037,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>424</v>
+        <v>336</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>424</v>
+        <v>336</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11974,19 +12060,23 @@
         <v>79</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>195</v>
+        <v>151</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>425</v>
+        <v>337</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
+        <v>338</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>79</v>
       </c>
@@ -12010,11 +12100,13 @@
         <v>79</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="Y84" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z84" t="s" s="2">
-        <v>427</v>
+        <v>79</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>79</v>
@@ -12032,7 +12124,7 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>424</v>
+        <v>341</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12050,24 +12142,24 @@
         <v>79</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>428</v>
+        <v>342</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>429</v>
+        <v>343</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>430</v>
+        <v>79</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>431</v>
+        <v>344</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>431</v>
+        <v>344</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12075,7 +12167,7 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G85" t="s" s="2">
         <v>90</v>
@@ -12087,16 +12179,16 @@
         <v>79</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>195</v>
+        <v>345</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>432</v>
+        <v>346</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>433</v>
+        <v>347</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12123,11 +12215,13 @@
         <v>79</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="Y85" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z85" t="s" s="2">
-        <v>434</v>
+        <v>79</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>79</v>
@@ -12145,10 +12239,10 @@
         <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>431</v>
+        <v>344</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>90</v>
@@ -12160,27 +12254,27 @@
         <v>102</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>79</v>
+        <v>348</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>435</v>
+        <v>349</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>436</v>
+        <v>350</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>79</v>
+        <v>351</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>437</v>
+        <v>79</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>438</v>
+        <v>352</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>438</v>
+        <v>352</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12203,13 +12297,13 @@
         <v>79</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>439</v>
+        <v>353</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>440</v>
+        <v>354</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>441</v>
+        <v>355</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12260,7 +12354,7 @@
         <v>79</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>438</v>
+        <v>352</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12275,16 +12369,16 @@
         <v>102</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>79</v>
+        <v>356</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>442</v>
+        <v>357</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>443</v>
+        <v>358</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>79</v>
+        <v>359</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>79</v>
@@ -12292,10 +12386,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>444</v>
+        <v>360</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>444</v>
+        <v>360</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12303,10 +12397,10 @@
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>79</v>
@@ -12318,15 +12412,17 @@
         <v>91</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>445</v>
+        <v>361</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>446</v>
+        <v>362</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N87" s="2"/>
+        <v>363</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>79</v>
@@ -12363,23 +12459,23 @@
         <v>79</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>448</v>
+        <v>365</v>
       </c>
       <c r="AC87" s="2"/>
       <c r="AD87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>139</v>
+        <v>366</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>444</v>
+        <v>360</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>79</v>
@@ -12388,29 +12484,31 @@
         <v>102</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>449</v>
+        <v>367</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>450</v>
+        <v>368</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>451</v>
+        <v>369</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>79</v>
+        <v>370</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>79</v>
+        <v>371</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>452</v>
+        <v>372</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="C88" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="C88" t="s" s="2">
+        <v>373</v>
+      </c>
       <c r="D88" t="s" s="2">
         <v>79</v>
       </c>
@@ -12428,18 +12526,20 @@
         <v>79</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>151</v>
+        <v>361</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>152</v>
+        <v>374</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N88" s="2"/>
+        <v>363</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>79</v>
@@ -12488,10 +12588,10 @@
         <v>79</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>154</v>
+        <v>360</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>90</v>
@@ -12500,41 +12600,41 @@
         <v>79</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>79</v>
+        <v>367</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>79</v>
+        <v>368</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>155</v>
+        <v>369</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>79</v>
+        <v>370</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>79</v>
+        <v>371</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>453</v>
+        <v>375</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>453</v>
+        <v>376</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>79</v>
@@ -12546,17 +12646,15 @@
         <v>79</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>169</v>
+        <v>377</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>79</v>
@@ -12605,19 +12703,19 @@
         <v>79</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>141</v>
+        <v>79</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>79</v>
@@ -12626,7 +12724,7 @@
         <v>79</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>155</v>
+        <v>79</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>79</v>
@@ -12637,14 +12735,14 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>454</v>
+        <v>379</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>454</v>
+        <v>380</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>455</v>
+        <v>79</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -12657,26 +12755,22 @@
         <v>79</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K90" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>456</v>
+        <v>136</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>79</v>
       </c>
@@ -12712,19 +12806,17 @@
         <v>79</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AC90" s="2"/>
       <c r="AD90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>458</v>
+        <v>159</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12745,7 +12837,7 @@
         <v>79</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>79</v>
@@ -12756,12 +12848,14 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>459</v>
+        <v>381</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="C91" s="2"/>
+        <v>380</v>
+      </c>
+      <c r="C91" t="s" s="2">
+        <v>382</v>
+      </c>
       <c r="D91" t="s" s="2">
         <v>79</v>
       </c>
@@ -12779,16 +12873,16 @@
         <v>79</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>195</v>
+        <v>383</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>460</v>
+        <v>384</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>461</v>
+        <v>385</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12815,13 +12909,13 @@
         <v>79</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>462</v>
+        <v>79</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>463</v>
+        <v>79</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>464</v>
+        <v>79</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>79</v>
@@ -12839,28 +12933,28 @@
         <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>459</v>
+        <v>159</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>79</v>
+        <v>148</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>465</v>
+        <v>79</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>466</v>
+        <v>79</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>79</v>
@@ -12871,10 +12965,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>467</v>
+        <v>386</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>467</v>
+        <v>387</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12882,7 +12976,7 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>90</v>
@@ -12894,20 +12988,18 @@
         <v>79</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>468</v>
+        <v>151</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>469</v>
+        <v>152</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>471</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>79</v>
@@ -12956,10 +13048,10 @@
         <v>79</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>467</v>
+        <v>154</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>90</v>
@@ -12968,19 +13060,19 @@
         <v>79</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>472</v>
+        <v>79</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>473</v>
+        <v>155</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>474</v>
+        <v>79</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>79</v>
@@ -12988,14 +13080,12 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>475</v>
+        <v>388</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="C93" t="s" s="2">
-        <v>476</v>
-      </c>
+        <v>389</v>
+      </c>
+      <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
         <v>79</v>
       </c>
@@ -13004,7 +13094,7 @@
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>79</v>
@@ -13013,16 +13103,16 @@
         <v>79</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>445</v>
+        <v>135</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>477</v>
+        <v>136</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>447</v>
+        <v>137</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13061,19 +13151,19 @@
         <v>79</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AC93" t="s" s="2">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="AD93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>444</v>
+        <v>159</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13085,16 +13175,16 @@
         <v>79</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>449</v>
+        <v>79</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>450</v>
+        <v>79</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>451</v>
+        <v>79</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>79</v>
@@ -13105,10 +13195,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>478</v>
+        <v>390</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>452</v>
+        <v>391</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13116,7 +13206,7 @@
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G94" t="s" s="2">
         <v>90</v>
@@ -13131,22 +13221,24 @@
         <v>79</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>151</v>
+        <v>104</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N94" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q94" s="2"/>
       <c r="R94" t="s" s="2">
-        <v>79</v>
+        <v>392</v>
       </c>
       <c r="S94" t="s" s="2">
         <v>79</v>
@@ -13188,10 +13280,10 @@
         <v>79</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>90</v>
@@ -13209,7 +13301,7 @@
         <v>79</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>79</v>
@@ -13220,21 +13312,21 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>479</v>
+        <v>393</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>453</v>
+        <v>394</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>79</v>
@@ -13246,17 +13338,15 @@
         <v>79</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>135</v>
+        <v>195</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>79</v>
@@ -13281,13 +13371,11 @@
         <v>79</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y95" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="Y95" s="2"/>
       <c r="Z95" t="s" s="2">
-        <v>79</v>
+        <v>395</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>79</v>
@@ -13305,19 +13393,19 @@
         <v>79</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>79</v>
@@ -13326,7 +13414,7 @@
         <v>79</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>79</v>
@@ -13337,46 +13425,42 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>480</v>
+        <v>396</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>454</v>
+        <v>397</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>455</v>
+        <v>79</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>135</v>
+        <v>361</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>456</v>
+        <v>398</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>79</v>
       </c>
@@ -13424,19 +13508,19 @@
         <v>79</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>458</v>
+        <v>400</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>141</v>
+        <v>79</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>79</v>
@@ -13445,7 +13529,7 @@
         <v>79</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>79</v>
@@ -13456,10 +13540,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>481</v>
+        <v>401</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>459</v>
+        <v>401</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13479,16 +13563,16 @@
         <v>79</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>195</v>
+        <v>361</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>460</v>
+        <v>402</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>461</v>
+        <v>403</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13500,7 +13584,7 @@
         <v>79</v>
       </c>
       <c r="S97" t="s" s="2">
-        <v>482</v>
+        <v>79</v>
       </c>
       <c r="T97" t="s" s="2">
         <v>79</v>
@@ -13515,13 +13599,13 @@
         <v>79</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>462</v>
+        <v>79</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>463</v>
+        <v>79</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>464</v>
+        <v>79</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>79</v>
@@ -13539,7 +13623,7 @@
         <v>79</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>459</v>
+        <v>401</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13554,16 +13638,16 @@
         <v>102</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>465</v>
+        <v>79</v>
       </c>
       <c r="AL97" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>466</v>
+        <v>404</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>79</v>
+        <v>405</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>79</v>
@@ -13571,10 +13655,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>483</v>
+        <v>406</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>467</v>
+        <v>406</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13582,7 +13666,7 @@
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G98" t="s" s="2">
         <v>90</v>
@@ -13597,16 +13681,16 @@
         <v>91</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>484</v>
+        <v>407</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>469</v>
+        <v>408</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>470</v>
+        <v>409</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>471</v>
+        <v>410</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13656,10 +13740,10 @@
         <v>79</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>467</v>
+        <v>406</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>90</v>
@@ -13671,16 +13755,16 @@
         <v>102</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>472</v>
+        <v>79</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>79</v>
+        <v>411</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>473</v>
+        <v>412</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>474</v>
+        <v>413</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>79</v>
@@ -13688,10 +13772,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>485</v>
+        <v>414</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>485</v>
+        <v>414</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13702,7 +13786,7 @@
         <v>80</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>79</v>
@@ -13711,18 +13795,20 @@
         <v>79</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>486</v>
+        <v>195</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>487</v>
+        <v>415</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N99" s="2"/>
+        <v>416</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>417</v>
+      </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>79</v>
@@ -13747,13 +13833,13 @@
         <v>79</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>79</v>
+        <v>306</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>79</v>
+        <v>418</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>79</v>
+        <v>231</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>79</v>
@@ -13771,13 +13857,13 @@
         <v>79</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>485</v>
+        <v>414</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>79</v>
@@ -13786,16 +13872,16 @@
         <v>102</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>489</v>
+        <v>79</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>490</v>
+        <v>411</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>491</v>
+        <v>419</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>79</v>
+        <v>413</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>79</v>
@@ -13803,10 +13889,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>492</v>
+        <v>420</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>492</v>
+        <v>420</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13829,13 +13915,13 @@
         <v>79</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>151</v>
+        <v>421</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>152</v>
+        <v>422</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>153</v>
+        <v>423</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13886,7 +13972,7 @@
         <v>79</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>154</v>
+        <v>420</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -13898,19 +13984,19 @@
         <v>79</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>79</v>
+        <v>424</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>79</v>
+        <v>425</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>155</v>
+        <v>426</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>79</v>
+        <v>427</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>79</v>
@@ -13918,21 +14004,21 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>493</v>
+        <v>428</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>493</v>
+        <v>428</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>79</v>
@@ -13944,17 +14030,15 @@
         <v>79</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>135</v>
+        <v>429</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>169</v>
+        <v>430</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>79</v>
@@ -13991,54 +14075,54 @@
         <v>79</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>159</v>
+        <v>428</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>79</v>
+        <v>432</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>155</v>
+        <v>433</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>79</v>
+        <v>434</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>494</v>
+        <v>435</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>494</v>
+        <v>435</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14058,20 +14142,18 @@
         <v>79</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>495</v>
+        <v>151</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>496</v>
+        <v>436</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>498</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="N102" s="2"/>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>79</v>
@@ -14120,7 +14202,7 @@
         <v>79</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>499</v>
+        <v>435</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14138,24 +14220,24 @@
         <v>79</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>133</v>
+        <v>438</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>500</v>
+        <v>439</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>79</v>
+        <v>440</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>501</v>
+        <v>441</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>501</v>
+        <v>441</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14175,16 +14257,16 @@
         <v>79</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>338</v>
+        <v>442</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>502</v>
+        <v>443</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>503</v>
+        <v>444</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14235,7 +14317,7 @@
         <v>79</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>504</v>
+        <v>441</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14253,10 +14335,10 @@
         <v>79</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>133</v>
+        <v>445</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>505</v>
+        <v>446</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>79</v>
@@ -14267,10 +14349,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>506</v>
+        <v>447</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>506</v>
+        <v>447</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14278,7 +14360,7 @@
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G104" t="s" s="2">
         <v>90</v>
@@ -14290,16 +14372,16 @@
         <v>79</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>507</v>
+        <v>195</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>508</v>
+        <v>448</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>509</v>
+        <v>449</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14326,13 +14408,11 @@
         <v>79</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="Y104" s="2"/>
       <c r="Z104" t="s" s="2">
-        <v>79</v>
+        <v>450</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>79</v>
@@ -14350,10 +14430,10 @@
         <v>79</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>510</v>
+        <v>447</v>
       </c>
       <c r="AG104" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH104" t="s" s="2">
         <v>90</v>
@@ -14368,24 +14448,24 @@
         <v>79</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>133</v>
+        <v>451</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>511</v>
+        <v>452</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>79</v>
+        <v>453</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>512</v>
+        <v>454</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>512</v>
+        <v>454</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14396,7 +14476,7 @@
         <v>80</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>79</v>
@@ -14411,10 +14491,10 @@
         <v>195</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>513</v>
+        <v>455</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>514</v>
+        <v>456</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14441,13 +14521,11 @@
         <v>79</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="Y105" t="s" s="2">
-        <v>515</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="Y105" s="2"/>
       <c r="Z105" t="s" s="2">
-        <v>516</v>
+        <v>457</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>79</v>
@@ -14465,13 +14543,13 @@
         <v>79</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>512</v>
+        <v>454</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>79</v>
@@ -14480,27 +14558,27 @@
         <v>102</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>517</v>
+        <v>79</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>79</v>
+        <v>458</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>518</v>
+        <v>459</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>79</v>
+        <v>460</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>519</v>
+        <v>461</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>519</v>
+        <v>461</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14511,7 +14589,7 @@
         <v>80</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>79</v>
@@ -14523,13 +14601,13 @@
         <v>79</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>520</v>
+        <v>462</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>521</v>
+        <v>463</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>522</v>
+        <v>464</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14580,13 +14658,13 @@
         <v>79</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>519</v>
+        <v>461</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>79</v>
@@ -14595,13 +14673,13 @@
         <v>102</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>523</v>
+        <v>79</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>79</v>
+        <v>465</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>133</v>
+        <v>466</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>79</v>
@@ -14612,10 +14690,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>524</v>
+        <v>467</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>524</v>
+        <v>467</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14626,36 +14704,32 @@
         <v>80</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I107" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J107" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>384</v>
+        <v>468</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>525</v>
+        <v>469</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>527</v>
-      </c>
+        <v>470</v>
+      </c>
+      <c r="N107" s="2"/>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="Q107" t="s" s="2">
-        <v>528</v>
-      </c>
+      <c r="Q107" s="2"/>
       <c r="R107" t="s" s="2">
         <v>79</v>
       </c>
@@ -14687,25 +14761,23 @@
         <v>79</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC107" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="AC107" s="2"/>
       <c r="AD107" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>524</v>
+        <v>467</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>79</v>
@@ -14714,13 +14786,13 @@
         <v>102</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>79</v>
+        <v>472</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>529</v>
+        <v>473</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>133</v>
+        <v>474</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>79</v>
@@ -14731,10 +14803,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>530</v>
+        <v>475</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>530</v>
+        <v>475</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14745,7 +14817,7 @@
         <v>80</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>79</v>
@@ -14757,13 +14829,13 @@
         <v>79</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>195</v>
+        <v>151</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>531</v>
+        <v>152</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>532</v>
+        <v>153</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -14790,13 +14862,13 @@
         <v>79</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>283</v>
+        <v>79</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>533</v>
+        <v>79</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>534</v>
+        <v>79</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>79</v>
@@ -14814,19 +14886,19 @@
         <v>79</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>530</v>
+        <v>154</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>79</v>
@@ -14835,7 +14907,7 @@
         <v>79</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>79</v>
@@ -14846,14 +14918,14 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>535</v>
+        <v>476</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>535</v>
+        <v>476</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -14872,15 +14944,17 @@
         <v>79</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>445</v>
+        <v>135</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>536</v>
+        <v>169</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N109" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>79</v>
@@ -14929,7 +15003,7 @@
         <v>79</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>535</v>
+        <v>159</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -14941,7 +15015,7 @@
         <v>79</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>538</v>
+        <v>141</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>79</v>
@@ -14950,7 +15024,7 @@
         <v>79</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>79</v>
@@ -14961,42 +15035,46 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>539</v>
+        <v>477</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>539</v>
+        <v>477</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>79</v>
+        <v>478</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I110" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>152</v>
+        <v>479</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N110" s="2"/>
-      <c r="O110" s="2"/>
+        <v>480</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="P110" t="s" s="2">
         <v>79</v>
       </c>
@@ -15044,19 +15122,19 @@
         <v>79</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>154</v>
+        <v>481</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>79</v>
@@ -15065,7 +15143,7 @@
         <v>79</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>79</v>
@@ -15076,21 +15154,21 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>540</v>
+        <v>482</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>540</v>
+        <v>482</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>79</v>
@@ -15099,20 +15177,18 @@
         <v>79</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>135</v>
+        <v>195</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>169</v>
+        <v>483</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>484</v>
+      </c>
+      <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>79</v>
@@ -15137,13 +15213,13 @@
         <v>79</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>79</v>
+        <v>485</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>79</v>
+        <v>486</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>79</v>
+        <v>487</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>79</v>
@@ -15161,28 +15237,28 @@
         <v>79</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>159</v>
+        <v>482</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>79</v>
+        <v>488</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>155</v>
+        <v>489</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>79</v>
@@ -15193,46 +15269,44 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>541</v>
+        <v>490</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>541</v>
+        <v>490</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>455</v>
+        <v>79</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I112" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J112" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>135</v>
+        <v>491</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>456</v>
+        <v>492</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>457</v>
+        <v>493</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>494</v>
+      </c>
+      <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>79</v>
       </c>
@@ -15280,31 +15354,31 @@
         <v>79</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>458</v>
+        <v>490</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>79</v>
+        <v>495</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>133</v>
+        <v>496</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>79</v>
+        <v>497</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>79</v>
@@ -15312,12 +15386,14 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>542</v>
+        <v>498</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="C113" s="2"/>
+        <v>467</v>
+      </c>
+      <c r="C113" t="s" s="2">
+        <v>499</v>
+      </c>
       <c r="D113" t="s" s="2">
         <v>79</v>
       </c>
@@ -15326,7 +15402,7 @@
         <v>80</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>79</v>
@@ -15335,16 +15411,16 @@
         <v>79</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>151</v>
+        <v>468</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>543</v>
+        <v>500</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>544</v>
+        <v>470</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -15395,13 +15471,13 @@
         <v>79</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>542</v>
+        <v>467</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>79</v>
@@ -15410,13 +15486,13 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>79</v>
+        <v>472</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>545</v>
+        <v>473</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>133</v>
+        <v>474</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>79</v>
@@ -15427,10 +15503,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>546</v>
+        <v>501</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>546</v>
+        <v>475</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15453,13 +15529,13 @@
         <v>79</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>104</v>
+        <v>151</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>547</v>
+        <v>152</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>548</v>
+        <v>153</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -15510,7 +15586,7 @@
         <v>79</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>546</v>
+        <v>154</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -15522,7 +15598,7 @@
         <v>79</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>79</v>
@@ -15531,7 +15607,7 @@
         <v>79</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>79</v>
@@ -15542,21 +15618,21 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>549</v>
+        <v>502</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>549</v>
+        <v>476</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>79</v>
@@ -15568,15 +15644,17 @@
         <v>79</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>338</v>
+        <v>135</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>550</v>
+        <v>169</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="N115" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>79</v>
@@ -15625,28 +15703,28 @@
         <v>79</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>549</v>
+        <v>159</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>552</v>
+        <v>79</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>79</v>
@@ -15657,42 +15735,46 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>553</v>
+        <v>503</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>553</v>
+        <v>477</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>79</v>
+        <v>478</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I116" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>338</v>
+        <v>135</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>554</v>
+        <v>479</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="N116" s="2"/>
-      <c r="O116" s="2"/>
+        <v>480</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="O116" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="P116" t="s" s="2">
         <v>79</v>
       </c>
@@ -15740,25 +15822,25 @@
         <v>79</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>553</v>
+        <v>481</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>556</v>
+        <v>79</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>133</v>
@@ -15772,10 +15854,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>557</v>
+        <v>504</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>557</v>
+        <v>482</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15786,7 +15868,7 @@
         <v>80</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>79</v>
@@ -15795,16 +15877,16 @@
         <v>79</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K117" t="s" s="2">
         <v>195</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>558</v>
+        <v>483</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>559</v>
+        <v>484</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -15816,7 +15898,7 @@
         <v>79</v>
       </c>
       <c r="S117" t="s" s="2">
-        <v>79</v>
+        <v>505</v>
       </c>
       <c r="T117" t="s" s="2">
         <v>79</v>
@@ -15831,13 +15913,13 @@
         <v>79</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>283</v>
+        <v>485</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>560</v>
+        <v>486</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>561</v>
+        <v>487</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>79</v>
@@ -15855,13 +15937,13 @@
         <v>79</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>557</v>
+        <v>482</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>79</v>
@@ -15870,13 +15952,13 @@
         <v>102</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>79</v>
+        <v>488</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>562</v>
+        <v>79</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>133</v>
+        <v>489</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>79</v>
@@ -15887,10 +15969,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>563</v>
+        <v>506</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>563</v>
+        <v>490</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15898,7 +15980,7 @@
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G118" t="s" s="2">
         <v>90</v>
@@ -15910,18 +15992,20 @@
         <v>79</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>195</v>
+        <v>507</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>564</v>
+        <v>492</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="N118" s="2"/>
+        <v>493</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>494</v>
+      </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>79</v>
@@ -15946,13 +16030,13 @@
         <v>79</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>283</v>
+        <v>79</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>566</v>
+        <v>79</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>567</v>
+        <v>79</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>79</v>
@@ -15970,10 +16054,10 @@
         <v>79</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>563</v>
+        <v>490</v>
       </c>
       <c r="AG118" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH118" t="s" s="2">
         <v>90</v>
@@ -15985,16 +16069,16 @@
         <v>102</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>79</v>
+        <v>495</v>
       </c>
       <c r="AL118" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>133</v>
+        <v>496</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>79</v>
+        <v>497</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>79</v>
@@ -16002,10 +16086,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>568</v>
+        <v>508</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>568</v>
+        <v>508</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16025,20 +16109,18 @@
         <v>79</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>445</v>
+        <v>509</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>569</v>
+        <v>510</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>571</v>
-      </c>
+        <v>511</v>
+      </c>
+      <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>79</v>
@@ -16087,7 +16169,7 @@
         <v>79</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>568</v>
+        <v>508</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -16102,13 +16184,13 @@
         <v>102</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>79</v>
+        <v>512</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>572</v>
+        <v>513</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>573</v>
+        <v>514</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>79</v>
@@ -16119,10 +16201,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>574</v>
+        <v>515</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>574</v>
+        <v>515</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16234,10 +16316,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>575</v>
+        <v>516</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>575</v>
+        <v>516</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16307,16 +16389,16 @@
         <v>79</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AC121" t="s" s="2">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="AD121" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE121" t="s" s="2">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="AF121" t="s" s="2">
         <v>159</v>
@@ -16351,46 +16433,44 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>576</v>
+        <v>517</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>576</v>
+        <v>517</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>455</v>
+        <v>79</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I122" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J122" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>135</v>
+        <v>518</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>456</v>
+        <v>519</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>457</v>
+        <v>520</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O122" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>521</v>
+      </c>
+      <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
         <v>79</v>
       </c>
@@ -16438,28 +16518,28 @@
         <v>79</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>458</v>
+        <v>522</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>133</v>
+        <v>523</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>79</v>
@@ -16470,10 +16550,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>577</v>
+        <v>524</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>577</v>
+        <v>524</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16493,16 +16573,16 @@
         <v>79</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>338</v>
+        <v>361</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>578</v>
+        <v>525</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>579</v>
+        <v>526</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -16553,7 +16633,7 @@
         <v>79</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>577</v>
+        <v>527</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -16571,10 +16651,10 @@
         <v>79</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>580</v>
+        <v>133</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>346</v>
+        <v>528</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>79</v>
@@ -16585,10 +16665,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>581</v>
+        <v>529</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>581</v>
+        <v>529</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16596,7 +16676,7 @@
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G124" t="s" s="2">
         <v>90</v>
@@ -16608,16 +16688,16 @@
         <v>79</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>582</v>
+        <v>530</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>583</v>
+        <v>531</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>584</v>
+        <v>532</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -16668,10 +16748,10 @@
         <v>79</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>581</v>
+        <v>533</v>
       </c>
       <c r="AG124" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH124" t="s" s="2">
         <v>90</v>
@@ -16686,10 +16766,10 @@
         <v>79</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>585</v>
+        <v>133</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>586</v>
+        <v>534</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>79</v>
@@ -16700,10 +16780,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>587</v>
+        <v>535</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>587</v>
+        <v>535</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16714,7 +16794,7 @@
         <v>80</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>79</v>
@@ -16726,13 +16806,13 @@
         <v>79</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>384</v>
+        <v>195</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>588</v>
+        <v>536</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>589</v>
+        <v>537</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -16759,13 +16839,13 @@
         <v>79</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>79</v>
+        <v>306</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>79</v>
+        <v>538</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>79</v>
+        <v>539</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>79</v>
@@ -16783,13 +16863,13 @@
         <v>79</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>587</v>
+        <v>535</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>79</v>
@@ -16798,13 +16878,13 @@
         <v>102</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>79</v>
+        <v>540</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>590</v>
+        <v>79</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>591</v>
+        <v>541</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>79</v>
@@ -16815,10 +16895,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>592</v>
+        <v>542</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>592</v>
+        <v>542</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16841,13 +16921,13 @@
         <v>79</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>445</v>
+        <v>543</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>593</v>
+        <v>544</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>594</v>
+        <v>545</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -16898,7 +16978,7 @@
         <v>79</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>592</v>
+        <v>542</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -16913,7 +16993,7 @@
         <v>102</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>79</v>
+        <v>546</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>79</v>
@@ -16930,10 +17010,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>595</v>
+        <v>547</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>595</v>
+        <v>547</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16950,26 +17030,30 @@
         <v>79</v>
       </c>
       <c r="I127" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J127" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>151</v>
+        <v>407</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>152</v>
+        <v>548</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N127" s="2"/>
+        <v>549</v>
+      </c>
+      <c r="N127" t="s" s="2">
+        <v>550</v>
+      </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="Q127" s="2"/>
+      <c r="Q127" t="s" s="2">
+        <v>551</v>
+      </c>
       <c r="R127" t="s" s="2">
         <v>79</v>
       </c>
@@ -17013,7 +17097,7 @@
         <v>79</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>154</v>
+        <v>547</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17025,16 +17109,16 @@
         <v>79</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>79</v>
+        <v>552</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>79</v>
@@ -17045,14 +17129,14 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>596</v>
+        <v>553</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>596</v>
+        <v>553</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -17071,17 +17155,15 @@
         <v>79</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>135</v>
+        <v>195</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>169</v>
+        <v>554</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>555</v>
+      </c>
+      <c r="N128" s="2"/>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
         <v>79</v>
@@ -17106,13 +17188,13 @@
         <v>79</v>
       </c>
       <c r="X128" t="s" s="2">
-        <v>79</v>
+        <v>306</v>
       </c>
       <c r="Y128" t="s" s="2">
-        <v>79</v>
+        <v>556</v>
       </c>
       <c r="Z128" t="s" s="2">
-        <v>79</v>
+        <v>557</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>79</v>
@@ -17130,7 +17212,7 @@
         <v>79</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>159</v>
+        <v>553</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -17142,7 +17224,7 @@
         <v>79</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
         <v>79</v>
@@ -17151,7 +17233,7 @@
         <v>79</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>79</v>
@@ -17162,14 +17244,14 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>597</v>
+        <v>558</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>597</v>
+        <v>558</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>455</v>
+        <v>79</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
@@ -17182,26 +17264,22 @@
         <v>79</v>
       </c>
       <c r="I129" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>135</v>
+        <v>468</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>456</v>
+        <v>559</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O129" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>560</v>
+      </c>
+      <c r="N129" s="2"/>
+      <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
         <v>79</v>
       </c>
@@ -17249,7 +17327,7 @@
         <v>79</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>458</v>
+        <v>558</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -17261,7 +17339,7 @@
         <v>79</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>141</v>
+        <v>561</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>79</v>
@@ -17281,10 +17359,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>598</v>
+        <v>562</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>598</v>
+        <v>562</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17310,10 +17388,10 @@
         <v>151</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>599</v>
+        <v>152</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>600</v>
+        <v>153</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -17340,11 +17418,13 @@
         <v>79</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="Y130" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z130" t="s" s="2">
-        <v>601</v>
+        <v>79</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>79</v>
@@ -17362,7 +17442,7 @@
         <v>79</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>598</v>
+        <v>154</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -17374,7 +17454,7 @@
         <v>79</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK130" t="s" s="2">
         <v>79</v>
@@ -17383,7 +17463,7 @@
         <v>79</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>79</v>
@@ -17394,21 +17474,21 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>602</v>
+        <v>563</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>602</v>
+        <v>563</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>79</v>
@@ -17420,15 +17500,17 @@
         <v>79</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>406</v>
+        <v>135</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>603</v>
+        <v>169</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="N131" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>79</v>
@@ -17477,19 +17559,19 @@
         <v>79</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>602</v>
+        <v>159</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK131" t="s" s="2">
         <v>79</v>
@@ -17498,7 +17580,7 @@
         <v>79</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>79</v>
@@ -17509,14 +17591,14 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>605</v>
+        <v>564</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>605</v>
+        <v>564</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>79</v>
+        <v>478</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
@@ -17529,22 +17611,26 @@
         <v>79</v>
       </c>
       <c r="I132" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>195</v>
+        <v>135</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>606</v>
+        <v>479</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="N132" s="2"/>
-      <c r="O132" s="2"/>
+        <v>480</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="O132" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="P132" t="s" s="2">
         <v>79</v>
       </c>
@@ -17568,13 +17654,13 @@
         <v>79</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>608</v>
+        <v>79</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>609</v>
+        <v>79</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>79</v>
@@ -17592,7 +17678,7 @@
         <v>79</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>605</v>
+        <v>481</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -17604,7 +17690,7 @@
         <v>79</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK132" t="s" s="2">
         <v>79</v>
@@ -17624,10 +17710,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>610</v>
+        <v>565</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>610</v>
+        <v>565</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17635,7 +17721,7 @@
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G133" t="s" s="2">
         <v>90</v>
@@ -17650,17 +17736,15 @@
         <v>79</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>611</v>
+        <v>151</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>612</v>
+        <v>566</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>614</v>
-      </c>
+        <v>567</v>
+      </c>
+      <c r="N133" s="2"/>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>79</v>
@@ -17697,20 +17781,22 @@
         <v>79</v>
       </c>
       <c r="AB133" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="AC133" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD133" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE133" t="s" s="2">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>610</v>
+        <v>565</v>
       </c>
       <c r="AG133" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH133" t="s" s="2">
         <v>90</v>
@@ -17725,7 +17811,7 @@
         <v>79</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>79</v>
+        <v>568</v>
       </c>
       <c r="AM133" t="s" s="2">
         <v>133</v>
@@ -17739,14 +17825,12 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>615</v>
+        <v>569</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="C134" t="s" s="2">
-        <v>616</v>
-      </c>
+        <v>569</v>
+      </c>
+      <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
         <v>79</v>
       </c>
@@ -17767,17 +17851,15 @@
         <v>79</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>617</v>
+        <v>104</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>618</v>
+        <v>570</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>614</v>
-      </c>
+        <v>571</v>
+      </c>
+      <c r="N134" s="2"/>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>79</v>
@@ -17826,10 +17908,10 @@
         <v>79</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>610</v>
+        <v>569</v>
       </c>
       <c r="AG134" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH134" t="s" s="2">
         <v>90</v>
@@ -17858,10 +17940,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>619</v>
+        <v>572</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>619</v>
+        <v>572</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17884,17 +17966,15 @@
         <v>79</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>611</v>
+        <v>361</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>620</v>
+        <v>573</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>614</v>
-      </c>
+        <v>574</v>
+      </c>
+      <c r="N135" s="2"/>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
         <v>79</v>
@@ -17943,7 +18023,7 @@
         <v>79</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>619</v>
+        <v>572</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -17961,7 +18041,7 @@
         <v>79</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>79</v>
+        <v>575</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>133</v>
@@ -17970,6 +18050,2324 @@
         <v>79</v>
       </c>
       <c r="AO135" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="C136" s="2"/>
+      <c r="D136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E136" s="2"/>
+      <c r="F136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G136" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K136" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L136" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="M136" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="N136" s="2"/>
+      <c r="O136" s="2"/>
+      <c r="P136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q136" s="2"/>
+      <c r="R136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF136" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AG136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH136" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ136" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL136" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AM136" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO136" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="C137" s="2"/>
+      <c r="D137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E137" s="2"/>
+      <c r="F137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K137" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L137" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="M137" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="N137" s="2"/>
+      <c r="O137" s="2"/>
+      <c r="P137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q137" s="2"/>
+      <c r="R137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X137" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="Y137" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="Z137" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="AA137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF137" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AG137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ137" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL137" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AM137" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO137" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="C138" s="2"/>
+      <c r="D138" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E138" s="2"/>
+      <c r="F138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G138" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H138" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I138" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J138" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K138" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L138" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M138" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="N138" s="2"/>
+      <c r="O138" s="2"/>
+      <c r="P138" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q138" s="2"/>
+      <c r="R138" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S138" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T138" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U138" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V138" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W138" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X138" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="Y138" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="Z138" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="AA138" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB138" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC138" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD138" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE138" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF138" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AG138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH138" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI138" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ138" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK138" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL138" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM138" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN138" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO138" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="C139" s="2"/>
+      <c r="D139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E139" s="2"/>
+      <c r="F139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K139" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="L139" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="M139" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="N139" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="O139" s="2"/>
+      <c r="P139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q139" s="2"/>
+      <c r="R139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF139" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AG139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ139" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL139" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AM139" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AN139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO139" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="B140" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="C140" s="2"/>
+      <c r="D140" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E140" s="2"/>
+      <c r="F140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G140" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H140" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I140" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J140" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K140" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="L140" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="M140" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="N140" s="2"/>
+      <c r="O140" s="2"/>
+      <c r="P140" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q140" s="2"/>
+      <c r="R140" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S140" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T140" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U140" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V140" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W140" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X140" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y140" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z140" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA140" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB140" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC140" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD140" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE140" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF140" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AG140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH140" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI140" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ140" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK140" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL140" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM140" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AN140" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO140" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="C141" s="2"/>
+      <c r="D141" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="E141" s="2"/>
+      <c r="F141" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H141" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I141" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J141" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K141" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L141" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="M141" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="O141" s="2"/>
+      <c r="P141" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q141" s="2"/>
+      <c r="R141" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S141" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T141" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U141" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V141" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W141" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X141" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y141" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z141" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA141" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB141" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC141" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD141" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE141" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF141" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AG141" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI141" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ141" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK141" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL141" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM141" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AN141" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO141" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="B142" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="C142" s="2"/>
+      <c r="D142" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="E142" s="2"/>
+      <c r="F142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H142" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I142" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J142" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K142" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L142" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="M142" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="N142" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="O142" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="P142" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q142" s="2"/>
+      <c r="R142" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S142" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T142" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U142" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V142" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W142" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X142" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y142" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z142" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA142" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB142" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC142" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD142" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE142" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF142" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AG142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI142" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ142" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK142" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL142" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM142" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN142" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO142" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="B143" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="C143" s="2"/>
+      <c r="D143" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E143" s="2"/>
+      <c r="F143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G143" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H143" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I143" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J143" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K143" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L143" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="M143" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="N143" s="2"/>
+      <c r="O143" s="2"/>
+      <c r="P143" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q143" s="2"/>
+      <c r="R143" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S143" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T143" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U143" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V143" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W143" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X143" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y143" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z143" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA143" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB143" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC143" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD143" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE143" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF143" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AG143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH143" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI143" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ143" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK143" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL143" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AM143" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AN143" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO143" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="B144" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="C144" s="2"/>
+      <c r="D144" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E144" s="2"/>
+      <c r="F144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G144" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H144" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I144" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J144" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K144" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="L144" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="M144" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="N144" s="2"/>
+      <c r="O144" s="2"/>
+      <c r="P144" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q144" s="2"/>
+      <c r="R144" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S144" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T144" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U144" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V144" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W144" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X144" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y144" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z144" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA144" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB144" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC144" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD144" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE144" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF144" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="AG144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH144" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI144" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ144" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK144" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL144" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AM144" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="AN144" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO144" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="C145" s="2"/>
+      <c r="D145" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E145" s="2"/>
+      <c r="F145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G145" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H145" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I145" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J145" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K145" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="L145" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="M145" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="N145" s="2"/>
+      <c r="O145" s="2"/>
+      <c r="P145" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q145" s="2"/>
+      <c r="R145" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S145" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T145" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U145" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V145" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W145" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X145" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y145" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z145" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA145" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB145" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC145" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD145" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE145" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF145" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AG145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH145" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI145" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ145" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK145" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL145" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="AM145" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="AN145" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO145" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="C146" s="2"/>
+      <c r="D146" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E146" s="2"/>
+      <c r="F146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G146" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H146" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I146" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J146" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K146" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="L146" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="M146" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="N146" s="2"/>
+      <c r="O146" s="2"/>
+      <c r="P146" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q146" s="2"/>
+      <c r="R146" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S146" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T146" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U146" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V146" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W146" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X146" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y146" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z146" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA146" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB146" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC146" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD146" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE146" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF146" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="AG146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH146" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI146" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ146" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK146" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL146" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM146" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN146" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO146" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="B147" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="C147" s="2"/>
+      <c r="D147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E147" s="2"/>
+      <c r="F147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G147" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K147" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="L147" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="M147" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="N147" s="2"/>
+      <c r="O147" s="2"/>
+      <c r="P147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q147" s="2"/>
+      <c r="R147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF147" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AG147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH147" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM147" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AN147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO147" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="B148" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="C148" s="2"/>
+      <c r="D148" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="E148" s="2"/>
+      <c r="F148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G148" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H148" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I148" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J148" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K148" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L148" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="M148" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="N148" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="O148" s="2"/>
+      <c r="P148" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q148" s="2"/>
+      <c r="R148" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S148" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T148" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U148" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V148" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W148" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X148" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y148" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z148" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA148" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB148" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC148" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD148" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE148" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF148" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AG148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH148" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI148" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ148" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK148" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL148" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM148" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AN148" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO148" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="B149" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="C149" s="2"/>
+      <c r="D149" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="E149" s="2"/>
+      <c r="F149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G149" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H149" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I149" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J149" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K149" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L149" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="M149" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="N149" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="O149" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="P149" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q149" s="2"/>
+      <c r="R149" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S149" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T149" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U149" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V149" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W149" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X149" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y149" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z149" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA149" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB149" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC149" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD149" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE149" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF149" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AG149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH149" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI149" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ149" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK149" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL149" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM149" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN149" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO149" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="B150" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="C150" s="2"/>
+      <c r="D150" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E150" s="2"/>
+      <c r="F150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G150" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H150" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I150" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J150" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K150" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="L150" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="M150" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="N150" s="2"/>
+      <c r="O150" s="2"/>
+      <c r="P150" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q150" s="2"/>
+      <c r="R150" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S150" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T150" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U150" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V150" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W150" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X150" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="Y150" s="2"/>
+      <c r="Z150" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AA150" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB150" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC150" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD150" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE150" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF150" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="AG150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH150" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI150" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ150" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK150" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL150" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM150" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN150" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO150" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="B151" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="C151" s="2"/>
+      <c r="D151" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E151" s="2"/>
+      <c r="F151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G151" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H151" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I151" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J151" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K151" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="L151" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="M151" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="N151" s="2"/>
+      <c r="O151" s="2"/>
+      <c r="P151" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q151" s="2"/>
+      <c r="R151" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S151" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T151" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U151" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V151" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W151" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X151" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y151" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z151" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA151" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB151" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC151" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD151" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE151" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF151" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AG151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH151" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI151" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ151" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK151" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL151" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM151" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN151" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO151" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="B152" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="C152" s="2"/>
+      <c r="D152" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E152" s="2"/>
+      <c r="F152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G152" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H152" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I152" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J152" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K152" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L152" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="M152" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="N152" s="2"/>
+      <c r="O152" s="2"/>
+      <c r="P152" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q152" s="2"/>
+      <c r="R152" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S152" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T152" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U152" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V152" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W152" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X152" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="Y152" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="Z152" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AA152" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB152" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC152" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD152" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE152" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF152" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="AG152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH152" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI152" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ152" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK152" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL152" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM152" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN152" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO152" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="B153" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="C153" s="2"/>
+      <c r="D153" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E153" s="2"/>
+      <c r="F153" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G153" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H153" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I153" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J153" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K153" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="L153" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="M153" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="N153" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="O153" s="2"/>
+      <c r="P153" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q153" s="2"/>
+      <c r="R153" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S153" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T153" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U153" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V153" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W153" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X153" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y153" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z153" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA153" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB153" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AC153" s="2"/>
+      <c r="AD153" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE153" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AF153" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="AG153" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH153" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI153" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ153" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK153" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL153" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM153" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN153" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO153" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="B154" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="C154" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="D154" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E154" s="2"/>
+      <c r="F154" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G154" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H154" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I154" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J154" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K154" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="L154" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="M154" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="N154" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="O154" s="2"/>
+      <c r="P154" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q154" s="2"/>
+      <c r="R154" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S154" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T154" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U154" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V154" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W154" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X154" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y154" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z154" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA154" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB154" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC154" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD154" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE154" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF154" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="AG154" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH154" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI154" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ154" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK154" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL154" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM154" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN154" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO154" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="B155" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="C155" s="2"/>
+      <c r="D155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E155" s="2"/>
+      <c r="F155" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G155" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K155" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="L155" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="M155" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="N155" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="O155" s="2"/>
+      <c r="P155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q155" s="2"/>
+      <c r="R155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF155" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="AG155" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH155" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ155" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM155" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO155" t="s" s="2">
         <v>79</v>
       </c>
     </row>

--- a/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
+++ b/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5709" uniqueCount="645">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5969" uniqueCount="692">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T07:54:03+00:00</t>
+    <t>2026-07-31T16:55:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1058,6 +1058,151 @@
     <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-vaccine-code-cis|2.2.0</t>
   </si>
   <si>
+    <t>Immunization.vaccineCode.coding:cis.id</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding.id</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding:cis.extension</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding.extension</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding:cis.system</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/terminologie-bdpm</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding:cis.version</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding:cis.code</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding:cis.display</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding:cis.userSelected</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
     <t>Immunization.vaccineCode.text</t>
   </si>
   <si>
@@ -1274,10 +1419,6 @@
   </si>
   <si>
     <t>Immunization.primarySource</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
   </si>
   <si>
     <t>Indicates context the data was recorded in</t>
@@ -2321,7 +2462,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO155"/>
+  <dimension ref="A1:AO162"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="74.4765625" customWidth="true" bestFit="true"/>
@@ -12040,7 +12181,7 @@
         <v>336</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12060,23 +12201,19 @@
         <v>79</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K84" t="s" s="2">
         <v>151</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>337</v>
+        <v>152</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>79</v>
       </c>
@@ -12124,7 +12261,7 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>341</v>
+        <v>154</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12136,16 +12273,16 @@
         <v>79</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>342</v>
+        <v>79</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>343</v>
+        <v>155</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>79</v>
@@ -12156,21 +12293,21 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>79</v>
@@ -12179,18 +12316,20 @@
         <v>79</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>345</v>
+        <v>135</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>346</v>
+        <v>169</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N85" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>79</v>
@@ -12227,43 +12366,43 @@
         <v>79</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>344</v>
+        <v>159</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>348</v>
+        <v>79</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>349</v>
+        <v>79</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>350</v>
+        <v>155</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>351</v>
+        <v>79</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>79</v>
@@ -12271,10 +12410,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12282,7 +12421,7 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G86" t="s" s="2">
         <v>90</v>
@@ -12294,19 +12433,23 @@
         <v>79</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>353</v>
+        <v>104</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N86" s="2"/>
-      <c r="O86" s="2"/>
+        <v>343</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>345</v>
+      </c>
       <c r="P86" t="s" s="2">
         <v>79</v>
       </c>
@@ -12315,7 +12458,7 @@
         <v>79</v>
       </c>
       <c r="S86" t="s" s="2">
-        <v>79</v>
+        <v>346</v>
       </c>
       <c r="T86" t="s" s="2">
         <v>79</v>
@@ -12354,7 +12497,7 @@
         <v>79</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12369,16 +12512,16 @@
         <v>102</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>356</v>
+        <v>79</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>359</v>
+        <v>79</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>79</v>
@@ -12386,10 +12529,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12397,7 +12540,7 @@
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
         <v>90</v>
@@ -12412,16 +12555,16 @@
         <v>91</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>361</v>
+        <v>151</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12459,20 +12602,22 @@
         <v>79</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="AC87" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>366</v>
+        <v>79</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>90</v>
@@ -12484,31 +12629,29 @@
         <v>102</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>367</v>
+        <v>79</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>370</v>
+        <v>79</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>371</v>
+        <v>79</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>372</v>
+        <v>358</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="C88" t="s" s="2">
-        <v>373</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>79</v>
       </c>
@@ -12529,18 +12672,18 @@
         <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="L88" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="O88" s="2"/>
+      <c r="N88" s="2"/>
+      <c r="O88" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>79</v>
       </c>
@@ -12588,10 +12731,10 @@
         <v>79</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>90</v>
@@ -12603,27 +12746,27 @@
         <v>102</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>367</v>
+        <v>79</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>370</v>
+        <v>79</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>371</v>
+        <v>79</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12643,19 +12786,21 @@
         <v>79</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K89" t="s" s="2">
         <v>151</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
+      <c r="O89" t="s" s="2">
+        <v>370</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>79</v>
       </c>
@@ -12703,7 +12848,7 @@
         <v>79</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>154</v>
+        <v>371</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12715,16 +12860,16 @@
         <v>79</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>79</v>
+        <v>372</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>79</v>
+        <v>373</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>79</v>
@@ -12735,10 +12880,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12749,7 +12894,7 @@
         <v>80</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>79</v>
@@ -12758,19 +12903,23 @@
         <v>79</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>135</v>
+        <v>376</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>136</v>
+        <v>377</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>380</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>79</v>
       </c>
@@ -12806,38 +12955,40 @@
         <v>79</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AC90" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>159</v>
+        <v>381</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>79</v>
+        <v>382</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>79</v>
+        <v>383</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>79</v>
@@ -12848,14 +12999,12 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="C91" t="s" s="2">
-        <v>382</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
         <v>79</v>
       </c>
@@ -12873,19 +13022,23 @@
         <v>79</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>383</v>
+        <v>151</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
+        <v>386</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>79</v>
       </c>
@@ -12933,28 +13086,28 @@
         <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>159</v>
+        <v>389</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>79</v>
+        <v>390</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>79</v>
+        <v>391</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>79</v>
@@ -12965,10 +13118,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12976,7 +13129,7 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>90</v>
@@ -12988,16 +13141,16 @@
         <v>79</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>151</v>
+        <v>393</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>152</v>
+        <v>394</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>153</v>
+        <v>395</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13048,10 +13201,10 @@
         <v>79</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>154</v>
+        <v>392</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>90</v>
@@ -13060,19 +13213,19 @@
         <v>79</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>79</v>
+        <v>396</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>79</v>
+        <v>397</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>155</v>
+        <v>398</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>79</v>
+        <v>399</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>79</v>
@@ -13080,10 +13233,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13094,7 +13247,7 @@
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>79</v>
@@ -13106,13 +13259,13 @@
         <v>79</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>135</v>
+        <v>401</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>136</v>
+        <v>402</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>137</v>
+        <v>403</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13151,43 +13304,43 @@
         <v>79</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AC93" t="s" s="2">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="AD93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>159</v>
+        <v>400</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>79</v>
+        <v>404</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>79</v>
+        <v>405</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>79</v>
+        <v>406</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>79</v>
+        <v>407</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>79</v>
@@ -13195,10 +13348,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>391</v>
+        <v>408</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13218,19 +13371,19 @@
         <v>79</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>104</v>
+        <v>409</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>174</v>
+        <v>410</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>175</v>
+        <v>411</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>176</v>
+        <v>412</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13238,7 +13391,7 @@
       </c>
       <c r="Q94" s="2"/>
       <c r="R94" t="s" s="2">
-        <v>392</v>
+        <v>79</v>
       </c>
       <c r="S94" t="s" s="2">
         <v>79</v>
@@ -13268,19 +13421,17 @@
         <v>79</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="AC94" s="2"/>
       <c r="AD94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>79</v>
+        <v>414</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>178</v>
+        <v>408</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>90</v>
@@ -13292,32 +13443,34 @@
         <v>79</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>79</v>
+        <v>415</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>79</v>
+        <v>416</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>133</v>
+        <v>417</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>79</v>
+        <v>418</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>79</v>
+        <v>419</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>393</v>
+        <v>420</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="C95" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="C95" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="D95" t="s" s="2">
         <v>79</v>
       </c>
@@ -13335,18 +13488,20 @@
         <v>79</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>195</v>
+        <v>409</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>181</v>
+        <v>422</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N95" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>412</v>
+      </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>79</v>
@@ -13371,11 +13526,13 @@
         <v>79</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="Y95" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z95" t="s" s="2">
-        <v>395</v>
+        <v>79</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>79</v>
@@ -13393,10 +13550,10 @@
         <v>79</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>185</v>
+        <v>408</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>90</v>
@@ -13408,27 +13565,27 @@
         <v>102</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>79</v>
+        <v>415</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>79</v>
+        <v>416</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>133</v>
+        <v>417</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>79</v>
+        <v>418</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>79</v>
+        <v>419</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>396</v>
+        <v>423</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>397</v>
+        <v>424</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13451,13 +13608,13 @@
         <v>79</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>361</v>
+        <v>151</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>398</v>
+        <v>425</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>399</v>
+        <v>426</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13508,7 +13665,7 @@
         <v>79</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>400</v>
+        <v>154</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13540,10 +13697,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>401</v>
+        <v>427</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>401</v>
+        <v>428</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13554,7 +13711,7 @@
         <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>79</v>
@@ -13566,13 +13723,13 @@
         <v>79</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>361</v>
+        <v>135</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>402</v>
+        <v>136</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>403</v>
+        <v>137</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13611,31 +13768,29 @@
         <v>79</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AC97" s="2"/>
       <c r="AD97" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>401</v>
+        <v>159</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>79</v>
@@ -13644,10 +13799,10 @@
         <v>79</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>404</v>
+        <v>79</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>405</v>
+        <v>79</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>79</v>
@@ -13655,12 +13810,14 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>406</v>
+        <v>429</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="C98" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="C98" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="D98" t="s" s="2">
         <v>79</v>
       </c>
@@ -13678,20 +13835,18 @@
         <v>79</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>407</v>
+        <v>431</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>408</v>
+        <v>432</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>410</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="N98" s="2"/>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>79</v>
@@ -13740,31 +13895,31 @@
         <v>79</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>406</v>
+        <v>159</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>79</v>
+        <v>148</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>411</v>
+        <v>79</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>412</v>
+        <v>79</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>413</v>
+        <v>79</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>79</v>
@@ -13772,10 +13927,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>414</v>
+        <v>434</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>414</v>
+        <v>435</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13798,17 +13953,15 @@
         <v>79</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>195</v>
+        <v>151</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>415</v>
+        <v>152</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N99" s="2"/>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>79</v>
@@ -13833,13 +13986,13 @@
         <v>79</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>306</v>
+        <v>79</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>418</v>
+        <v>79</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>231</v>
+        <v>79</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>79</v>
@@ -13857,7 +14010,7 @@
         <v>79</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>414</v>
+        <v>154</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -13869,19 +14022,19 @@
         <v>79</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>411</v>
+        <v>79</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>419</v>
+        <v>155</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>413</v>
+        <v>79</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>79</v>
@@ -13889,10 +14042,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>420</v>
+        <v>436</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>420</v>
+        <v>437</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13903,7 +14056,7 @@
         <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>79</v>
@@ -13915,13 +14068,13 @@
         <v>79</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>421</v>
+        <v>135</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>422</v>
+        <v>136</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>423</v>
+        <v>137</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13960,43 +14113,43 @@
         <v>79</v>
       </c>
       <c r="AB100" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AC100" t="s" s="2">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="AD100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>420</v>
+        <v>159</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>424</v>
+        <v>79</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>425</v>
+        <v>79</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>426</v>
+        <v>79</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>427</v>
+        <v>79</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>79</v>
@@ -14004,10 +14157,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14015,7 +14168,7 @@
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G101" t="s" s="2">
         <v>90</v>
@@ -14030,22 +14183,24 @@
         <v>79</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>429</v>
+        <v>104</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>430</v>
+        <v>174</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N101" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>79</v>
+        <v>440</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>79</v>
@@ -14087,10 +14242,10 @@
         <v>79</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>428</v>
+        <v>178</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH101" t="s" s="2">
         <v>90</v>
@@ -14099,30 +14254,30 @@
         <v>79</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>432</v>
+        <v>79</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>433</v>
+        <v>133</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>434</v>
+        <v>79</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14145,13 +14300,13 @@
         <v>79</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>436</v>
+        <v>181</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>437</v>
+        <v>182</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14178,13 +14333,11 @@
         <v>79</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="Y102" s="2"/>
       <c r="Z102" t="s" s="2">
-        <v>79</v>
+        <v>443</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>79</v>
@@ -14202,7 +14355,7 @@
         <v>79</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>435</v>
+        <v>185</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14220,24 +14373,24 @@
         <v>79</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>438</v>
+        <v>79</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>439</v>
+        <v>133</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>440</v>
+        <v>79</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14260,13 +14413,13 @@
         <v>79</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>442</v>
+        <v>409</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14317,7 +14470,7 @@
         <v>79</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14329,16 +14482,16 @@
         <v>79</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>445</v>
+        <v>79</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>446</v>
+        <v>79</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>79</v>
@@ -14349,10 +14502,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14375,13 +14528,13 @@
         <v>79</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>195</v>
+        <v>409</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14408,11 +14561,13 @@
         <v>79</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="Y104" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z104" t="s" s="2">
-        <v>450</v>
+        <v>79</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>79</v>
@@ -14430,7 +14585,7 @@
         <v>79</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14448,16 +14603,16 @@
         <v>79</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>451</v>
+        <v>79</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>452</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>79</v>
+        <v>453</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>453</v>
+        <v>79</v>
       </c>
     </row>
     <row r="105">
@@ -14485,10 +14640,10 @@
         <v>79</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>195</v>
+        <v>376</v>
       </c>
       <c r="L105" t="s" s="2">
         <v>455</v>
@@ -14496,7 +14651,9 @@
       <c r="M105" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="N105" s="2"/>
+      <c r="N105" t="s" s="2">
+        <v>457</v>
+      </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>79</v>
@@ -14521,11 +14678,13 @@
         <v>79</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="Y105" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z105" t="s" s="2">
-        <v>457</v>
+        <v>79</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>79</v>
@@ -14567,10 +14726,10 @@
         <v>459</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>79</v>
+        <v>460</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>460</v>
+        <v>79</v>
       </c>
     </row>
     <row r="106">
@@ -14601,15 +14760,17 @@
         <v>79</v>
       </c>
       <c r="K106" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L106" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="L106" t="s" s="2">
+      <c r="M106" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="M106" t="s" s="2">
+      <c r="N106" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>79</v>
@@ -14634,13 +14795,13 @@
         <v>79</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>79</v>
+        <v>306</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>79</v>
+        <v>465</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>79</v>
+        <v>231</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>79</v>
@@ -14676,13 +14837,13 @@
         <v>79</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>466</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>79</v>
+        <v>460</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>79</v>
@@ -14704,7 +14865,7 @@
         <v>80</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>79</v>
@@ -14713,7 +14874,7 @@
         <v>79</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K107" t="s" s="2">
         <v>468</v>
@@ -14761,14 +14922,16 @@
         <v>79</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="AC107" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD107" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="AF107" t="s" s="2">
         <v>467</v>
@@ -14777,7 +14940,7 @@
         <v>80</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>79</v>
@@ -14786,16 +14949,16 @@
         <v>102</v>
       </c>
       <c r="AK107" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AL107" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="AL107" t="s" s="2">
+      <c r="AM107" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="AM107" t="s" s="2">
+      <c r="AN107" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>79</v>
@@ -14829,13 +14992,13 @@
         <v>79</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>151</v>
+        <v>476</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>152</v>
+        <v>477</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>153</v>
+        <v>478</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -14886,7 +15049,7 @@
         <v>79</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>154</v>
+        <v>475</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -14898,41 +15061,41 @@
         <v>79</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>79</v>
+        <v>479</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>155</v>
+        <v>480</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>79</v>
+        <v>481</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>79</v>
@@ -14944,17 +15107,15 @@
         <v>79</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>169</v>
+        <v>483</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>484</v>
+      </c>
+      <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>79</v>
@@ -15003,78 +15164,74 @@
         <v>79</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>159</v>
+        <v>482</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>79</v>
+        <v>485</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>155</v>
+        <v>486</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>79</v>
+        <v>487</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>478</v>
+        <v>79</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I110" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>135</v>
+        <v>489</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>491</v>
+      </c>
+      <c r="N110" s="2"/>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>79</v>
       </c>
@@ -15122,28 +15279,28 @@
         <v>79</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>79</v>
+        <v>492</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>133</v>
+        <v>493</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>79</v>
@@ -15154,10 +15311,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15177,16 +15334,16 @@
         <v>79</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K111" t="s" s="2">
         <v>195</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -15213,13 +15370,11 @@
         <v>79</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="Y111" t="s" s="2">
-        <v>486</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>79</v>
@@ -15237,7 +15392,7 @@
         <v>79</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15252,27 +15407,27 @@
         <v>102</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>488</v>
+        <v>79</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>79</v>
+        <v>498</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>79</v>
+        <v>500</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15280,7 +15435,7 @@
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G112" t="s" s="2">
         <v>90</v>
@@ -15292,20 +15447,18 @@
         <v>79</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>491</v>
+        <v>195</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>492</v>
+        <v>502</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>494</v>
-      </c>
+        <v>503</v>
+      </c>
+      <c r="N112" s="2"/>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>79</v>
@@ -15330,13 +15483,11 @@
         <v>79</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y112" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>79</v>
+        <v>504</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>79</v>
@@ -15354,10 +15505,10 @@
         <v>79</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH112" t="s" s="2">
         <v>90</v>
@@ -15369,31 +15520,29 @@
         <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>495</v>
+        <v>79</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>79</v>
+        <v>505</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>496</v>
+        <v>506</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>497</v>
+        <v>79</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>79</v>
+        <v>507</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>498</v>
+        <v>508</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="C113" t="s" s="2">
-        <v>499</v>
-      </c>
+        <v>508</v>
+      </c>
+      <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
         <v>79</v>
       </c>
@@ -15402,7 +15551,7 @@
         <v>80</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>79</v>
@@ -15411,16 +15560,16 @@
         <v>79</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>468</v>
+        <v>509</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>470</v>
+        <v>511</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -15471,13 +15620,13 @@
         <v>79</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>467</v>
+        <v>508</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>79</v>
@@ -15486,13 +15635,13 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>472</v>
+        <v>79</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>473</v>
+        <v>512</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>474</v>
+        <v>513</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>79</v>
@@ -15503,10 +15652,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>501</v>
+        <v>514</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>475</v>
+        <v>514</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15517,7 +15666,7 @@
         <v>80</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>79</v>
@@ -15526,16 +15675,16 @@
         <v>79</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>151</v>
+        <v>515</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>152</v>
+        <v>516</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>153</v>
+        <v>517</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -15574,40 +15723,38 @@
         <v>79</v>
       </c>
       <c r="AB114" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC114" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>518</v>
+      </c>
+      <c r="AC114" s="2"/>
       <c r="AD114" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE114" t="s" s="2">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>154</v>
+        <v>514</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>79</v>
+        <v>519</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>79</v>
+        <v>520</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>155</v>
+        <v>521</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>79</v>
@@ -15618,21 +15765,21 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>502</v>
+        <v>522</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>476</v>
+        <v>522</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>79</v>
@@ -15644,17 +15791,15 @@
         <v>79</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N115" s="2"/>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>79</v>
@@ -15703,19 +15848,19 @@
         <v>79</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>141</v>
+        <v>79</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>79</v>
@@ -15735,14 +15880,14 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>477</v>
+        <v>523</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>478</v>
+        <v>168</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -15755,26 +15900,24 @@
         <v>79</v>
       </c>
       <c r="I116" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K116" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>479</v>
+        <v>169</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>480</v>
+        <v>170</v>
       </c>
       <c r="N116" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="O116" t="s" s="2">
-        <v>282</v>
-      </c>
+      <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>79</v>
       </c>
@@ -15822,7 +15965,7 @@
         <v>79</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>481</v>
+        <v>159</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -15843,7 +15986,7 @@
         <v>79</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>79</v>
@@ -15854,42 +15997,46 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>504</v>
+        <v>524</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>482</v>
+        <v>524</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>79</v>
+        <v>525</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I117" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J117" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>195</v>
+        <v>135</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>483</v>
+        <v>526</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="N117" s="2"/>
-      <c r="O117" s="2"/>
+        <v>527</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="P117" t="s" s="2">
         <v>79</v>
       </c>
@@ -15898,7 +16045,7 @@
         <v>79</v>
       </c>
       <c r="S117" t="s" s="2">
-        <v>505</v>
+        <v>79</v>
       </c>
       <c r="T117" t="s" s="2">
         <v>79</v>
@@ -15913,13 +16060,13 @@
         <v>79</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>485</v>
+        <v>79</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>486</v>
+        <v>79</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>487</v>
+        <v>79</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>79</v>
@@ -15937,28 +16084,28 @@
         <v>79</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>482</v>
+        <v>528</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>488</v>
+        <v>79</v>
       </c>
       <c r="AL117" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>489</v>
+        <v>133</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>79</v>
@@ -15969,10 +16116,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>506</v>
+        <v>529</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>490</v>
+        <v>529</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15980,7 +16127,7 @@
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G118" t="s" s="2">
         <v>90</v>
@@ -15995,17 +16142,15 @@
         <v>91</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>507</v>
+        <v>195</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>492</v>
+        <v>530</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>494</v>
-      </c>
+        <v>531</v>
+      </c>
+      <c r="N118" s="2"/>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>79</v>
@@ -16030,13 +16175,13 @@
         <v>79</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>79</v>
+        <v>532</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>79</v>
+        <v>533</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>79</v>
+        <v>534</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>79</v>
@@ -16054,10 +16199,10 @@
         <v>79</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>490</v>
+        <v>529</v>
       </c>
       <c r="AG118" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH118" t="s" s="2">
         <v>90</v>
@@ -16069,16 +16214,16 @@
         <v>102</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>495</v>
+        <v>535</v>
       </c>
       <c r="AL118" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>496</v>
+        <v>536</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>497</v>
+        <v>79</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>79</v>
@@ -16086,10 +16231,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>508</v>
+        <v>537</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>508</v>
+        <v>537</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16097,10 +16242,10 @@
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>79</v>
@@ -16112,15 +16257,17 @@
         <v>91</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>509</v>
+        <v>538</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>510</v>
+        <v>539</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="N119" s="2"/>
+        <v>540</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>541</v>
+      </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>79</v>
@@ -16169,13 +16316,13 @@
         <v>79</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>508</v>
+        <v>537</v>
       </c>
       <c r="AG119" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>79</v>
@@ -16184,16 +16331,16 @@
         <v>102</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>512</v>
+        <v>542</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>513</v>
+        <v>79</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>514</v>
+        <v>543</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>79</v>
+        <v>544</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>79</v>
@@ -16201,12 +16348,14 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>515</v>
+        <v>545</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="C120" s="2"/>
+        <v>514</v>
+      </c>
+      <c r="C120" t="s" s="2">
+        <v>546</v>
+      </c>
       <c r="D120" t="s" s="2">
         <v>79</v>
       </c>
@@ -16215,7 +16364,7 @@
         <v>80</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>79</v>
@@ -16224,16 +16373,16 @@
         <v>79</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>151</v>
+        <v>515</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>152</v>
+        <v>547</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>153</v>
+        <v>517</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -16284,28 +16433,28 @@
         <v>79</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>154</v>
+        <v>514</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>79</v>
+        <v>519</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>79</v>
+        <v>520</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>155</v>
+        <v>521</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>79</v>
@@ -16316,21 +16465,21 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>516</v>
+        <v>548</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>79</v>
@@ -16342,17 +16491,15 @@
         <v>79</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N121" s="2"/>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>79</v>
@@ -16389,31 +16536,31 @@
         <v>79</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AC121" t="s" s="2">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="AD121" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE121" t="s" s="2">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>141</v>
+        <v>79</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>79</v>
@@ -16433,21 +16580,21 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>517</v>
+        <v>549</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>79</v>
@@ -16456,19 +16603,19 @@
         <v>79</v>
       </c>
       <c r="J122" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>518</v>
+        <v>135</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>519</v>
+        <v>169</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>520</v>
+        <v>170</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>521</v>
+        <v>171</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -16518,28 +16665,28 @@
         <v>79</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>522</v>
+        <v>159</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>523</v>
+        <v>155</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>79</v>
@@ -16550,42 +16697,46 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>524</v>
+        <v>550</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>524</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>79</v>
+        <v>525</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I123" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J123" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>361</v>
+        <v>135</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="N123" s="2"/>
-      <c r="O123" s="2"/>
+        <v>527</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="O123" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="P123" t="s" s="2">
         <v>79</v>
       </c>
@@ -16633,28 +16784,28 @@
         <v>79</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL123" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM123" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>79</v>
@@ -16665,7 +16816,7 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>529</v>
+        <v>551</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>529</v>
@@ -16676,7 +16827,7 @@
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G124" t="s" s="2">
         <v>90</v>
@@ -16691,13 +16842,13 @@
         <v>91</v>
       </c>
       <c r="K124" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L124" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="L124" t="s" s="2">
+      <c r="M124" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>532</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -16709,7 +16860,7 @@
         <v>79</v>
       </c>
       <c r="S124" t="s" s="2">
-        <v>79</v>
+        <v>552</v>
       </c>
       <c r="T124" t="s" s="2">
         <v>79</v>
@@ -16724,13 +16875,13 @@
         <v>79</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>79</v>
+        <v>532</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>79</v>
+        <v>533</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>79</v>
+        <v>534</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>79</v>
@@ -16748,10 +16899,10 @@
         <v>79</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="AG124" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH124" t="s" s="2">
         <v>90</v>
@@ -16763,13 +16914,13 @@
         <v>102</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>79</v>
+        <v>535</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>79</v>
@@ -16780,10 +16931,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>535</v>
+        <v>553</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16791,10 +16942,10 @@
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>79</v>
@@ -16803,18 +16954,20 @@
         <v>79</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>195</v>
+        <v>554</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N125" s="2"/>
+        <v>540</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>541</v>
+      </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
         <v>79</v>
@@ -16839,13 +16992,13 @@
         <v>79</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>306</v>
+        <v>79</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>538</v>
+        <v>79</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>539</v>
+        <v>79</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>79</v>
@@ -16863,13 +17016,13 @@
         <v>79</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AG125" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>79</v>
@@ -16878,16 +17031,16 @@
         <v>102</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="AL125" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>79</v>
+        <v>544</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>79</v>
@@ -16895,10 +17048,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>542</v>
+        <v>555</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>542</v>
+        <v>555</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16918,16 +17071,16 @@
         <v>79</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>543</v>
+        <v>556</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>544</v>
+        <v>557</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>545</v>
+        <v>558</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -16978,7 +17131,7 @@
         <v>79</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>542</v>
+        <v>555</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -16993,13 +17146,13 @@
         <v>102</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>546</v>
+        <v>559</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>79</v>
+        <v>560</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>133</v>
+        <v>561</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>79</v>
@@ -17010,10 +17163,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>547</v>
+        <v>562</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>547</v>
+        <v>562</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17030,30 +17183,26 @@
         <v>79</v>
       </c>
       <c r="I127" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J127" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>407</v>
+        <v>151</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>548</v>
+        <v>152</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>550</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N127" s="2"/>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="Q127" t="s" s="2">
-        <v>551</v>
-      </c>
+      <c r="Q127" s="2"/>
       <c r="R127" t="s" s="2">
         <v>79</v>
       </c>
@@ -17097,7 +17246,7 @@
         <v>79</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>547</v>
+        <v>154</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17109,16 +17258,16 @@
         <v>79</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>552</v>
+        <v>79</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>79</v>
@@ -17129,14 +17278,14 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>553</v>
+        <v>563</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>553</v>
+        <v>563</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -17155,15 +17304,17 @@
         <v>79</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>195</v>
+        <v>135</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>554</v>
+        <v>169</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="N128" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
         <v>79</v>
@@ -17188,31 +17339,31 @@
         <v>79</v>
       </c>
       <c r="X128" t="s" s="2">
-        <v>306</v>
+        <v>79</v>
       </c>
       <c r="Y128" t="s" s="2">
-        <v>556</v>
+        <v>79</v>
       </c>
       <c r="Z128" t="s" s="2">
-        <v>557</v>
+        <v>79</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB128" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AC128" t="s" s="2">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="AD128" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE128" t="s" s="2">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>553</v>
+        <v>159</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -17224,7 +17375,7 @@
         <v>79</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK128" t="s" s="2">
         <v>79</v>
@@ -17233,7 +17384,7 @@
         <v>79</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>79</v>
@@ -17244,10 +17395,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17258,7 +17409,7 @@
         <v>80</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>79</v>
@@ -17267,18 +17418,20 @@
         <v>79</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>468</v>
+        <v>565</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="N129" s="2"/>
+        <v>567</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>568</v>
+      </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
         <v>79</v>
@@ -17327,28 +17480,28 @@
         <v>79</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>558</v>
+        <v>569</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>561</v>
+        <v>102</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>133</v>
+        <v>570</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>79</v>
@@ -17359,10 +17512,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>562</v>
+        <v>571</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>562</v>
+        <v>571</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17382,16 +17535,16 @@
         <v>79</v>
       </c>
       <c r="J130" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>151</v>
+        <v>409</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>152</v>
+        <v>572</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>153</v>
+        <v>573</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -17442,7 +17595,7 @@
         <v>79</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>154</v>
+        <v>574</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -17454,16 +17607,16 @@
         <v>79</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK130" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>155</v>
+        <v>575</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>79</v>
@@ -17474,21 +17627,21 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>563</v>
+        <v>576</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>563</v>
+        <v>576</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>79</v>
@@ -17497,20 +17650,18 @@
         <v>79</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>135</v>
+        <v>577</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>169</v>
+        <v>578</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>579</v>
+      </c>
+      <c r="N131" s="2"/>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>79</v>
@@ -17559,28 +17710,28 @@
         <v>79</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>159</v>
+        <v>580</v>
       </c>
       <c r="AG131" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK131" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>155</v>
+        <v>581</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>79</v>
@@ -17591,14 +17742,14 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>564</v>
+        <v>582</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>564</v>
+        <v>582</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>478</v>
+        <v>79</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
@@ -17611,26 +17762,22 @@
         <v>79</v>
       </c>
       <c r="I132" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>135</v>
+        <v>195</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>479</v>
+        <v>583</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="N132" s="2"/>
+      <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>79</v>
       </c>
@@ -17654,13 +17801,13 @@
         <v>79</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>79</v>
+        <v>306</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>79</v>
+        <v>585</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>79</v>
+        <v>586</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>79</v>
@@ -17678,7 +17825,7 @@
         <v>79</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>481</v>
+        <v>582</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -17690,16 +17837,16 @@
         <v>79</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>79</v>
+        <v>587</v>
       </c>
       <c r="AL132" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>133</v>
+        <v>588</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>79</v>
@@ -17710,10 +17857,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>565</v>
+        <v>589</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>565</v>
+        <v>589</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17724,7 +17871,7 @@
         <v>80</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H133" t="s" s="2">
         <v>79</v>
@@ -17736,13 +17883,13 @@
         <v>79</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>151</v>
+        <v>590</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>566</v>
+        <v>591</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>567</v>
+        <v>592</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -17793,13 +17940,13 @@
         <v>79</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>565</v>
+        <v>589</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI133" t="s" s="2">
         <v>79</v>
@@ -17808,10 +17955,10 @@
         <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>79</v>
+        <v>593</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>568</v>
+        <v>79</v>
       </c>
       <c r="AM133" t="s" s="2">
         <v>133</v>
@@ -17825,10 +17972,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>569</v>
+        <v>594</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>569</v>
+        <v>594</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17845,26 +17992,30 @@
         <v>79</v>
       </c>
       <c r="I134" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J134" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>104</v>
+        <v>376</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>570</v>
+        <v>595</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="N134" s="2"/>
+        <v>596</v>
+      </c>
+      <c r="N134" t="s" s="2">
+        <v>597</v>
+      </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="Q134" s="2"/>
+      <c r="Q134" t="s" s="2">
+        <v>598</v>
+      </c>
       <c r="R134" t="s" s="2">
         <v>79</v>
       </c>
@@ -17908,7 +18059,7 @@
         <v>79</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>569</v>
+        <v>594</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -17926,7 +18077,7 @@
         <v>79</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>79</v>
+        <v>599</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>133</v>
@@ -17940,10 +18091,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>572</v>
+        <v>600</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>572</v>
+        <v>600</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17954,7 +18105,7 @@
         <v>80</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H135" t="s" s="2">
         <v>79</v>
@@ -17966,13 +18117,13 @@
         <v>79</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>361</v>
+        <v>195</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>574</v>
+        <v>602</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -17999,13 +18150,13 @@
         <v>79</v>
       </c>
       <c r="X135" t="s" s="2">
-        <v>79</v>
+        <v>306</v>
       </c>
       <c r="Y135" t="s" s="2">
-        <v>79</v>
+        <v>603</v>
       </c>
       <c r="Z135" t="s" s="2">
-        <v>79</v>
+        <v>604</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>79</v>
@@ -18023,13 +18174,13 @@
         <v>79</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>572</v>
+        <v>600</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH135" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI135" t="s" s="2">
         <v>79</v>
@@ -18041,7 +18192,7 @@
         <v>79</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>575</v>
+        <v>79</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>133</v>
@@ -18055,10 +18206,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>576</v>
+        <v>605</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>576</v>
+        <v>605</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18069,7 +18220,7 @@
         <v>80</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H136" t="s" s="2">
         <v>79</v>
@@ -18081,13 +18232,13 @@
         <v>79</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>361</v>
+        <v>515</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>577</v>
+        <v>606</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>578</v>
+        <v>607</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -18138,25 +18289,25 @@
         <v>79</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>576</v>
+        <v>605</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>102</v>
+        <v>608</v>
       </c>
       <c r="AK136" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>579</v>
+        <v>79</v>
       </c>
       <c r="AM136" t="s" s="2">
         <v>133</v>
@@ -18170,10 +18321,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>580</v>
+        <v>609</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>580</v>
+        <v>609</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18184,7 +18335,7 @@
         <v>80</v>
       </c>
       <c r="G137" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H137" t="s" s="2">
         <v>79</v>
@@ -18196,13 +18347,13 @@
         <v>79</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>195</v>
+        <v>151</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>581</v>
+        <v>152</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>582</v>
+        <v>153</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
@@ -18229,13 +18380,13 @@
         <v>79</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>306</v>
+        <v>79</v>
       </c>
       <c r="Y137" t="s" s="2">
-        <v>583</v>
+        <v>79</v>
       </c>
       <c r="Z137" t="s" s="2">
-        <v>584</v>
+        <v>79</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>79</v>
@@ -18253,28 +18404,28 @@
         <v>79</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>580</v>
+        <v>154</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI137" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK137" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>585</v>
+        <v>79</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>79</v>
@@ -18285,21 +18436,21 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>79</v>
@@ -18311,15 +18462,17 @@
         <v>79</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>195</v>
+        <v>135</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>587</v>
+        <v>169</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N138" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N138" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
         <v>79</v>
@@ -18344,13 +18497,13 @@
         <v>79</v>
       </c>
       <c r="X138" t="s" s="2">
-        <v>306</v>
+        <v>79</v>
       </c>
       <c r="Y138" t="s" s="2">
-        <v>589</v>
+        <v>79</v>
       </c>
       <c r="Z138" t="s" s="2">
-        <v>590</v>
+        <v>79</v>
       </c>
       <c r="AA138" t="s" s="2">
         <v>79</v>
@@ -18368,19 +18521,19 @@
         <v>79</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>586</v>
+        <v>159</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI138" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>79</v>
@@ -18389,7 +18542,7 @@
         <v>79</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="AN138" t="s" s="2">
         <v>79</v>
@@ -18400,14 +18553,14 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>591</v>
+        <v>611</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>591</v>
+        <v>611</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>79</v>
+        <v>525</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
@@ -18420,24 +18573,26 @@
         <v>79</v>
       </c>
       <c r="I139" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J139" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>468</v>
+        <v>135</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>592</v>
+        <v>526</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>593</v>
+        <v>527</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="O139" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="O139" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="P139" t="s" s="2">
         <v>79</v>
       </c>
@@ -18485,7 +18640,7 @@
         <v>79</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>591</v>
+        <v>528</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -18497,16 +18652,16 @@
         <v>79</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK139" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>595</v>
+        <v>79</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>596</v>
+        <v>133</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>79</v>
@@ -18517,10 +18672,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>597</v>
+        <v>612</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>597</v>
+        <v>612</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18546,10 +18701,10 @@
         <v>151</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>152</v>
+        <v>613</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>153</v>
+        <v>614</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -18600,7 +18755,7 @@
         <v>79</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>154</v>
+        <v>612</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -18612,16 +18767,16 @@
         <v>79</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK140" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>79</v>
+        <v>615</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>79</v>
@@ -18632,21 +18787,21 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>598</v>
+        <v>616</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>598</v>
+        <v>616</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>79</v>
@@ -18658,17 +18813,15 @@
         <v>79</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>169</v>
+        <v>617</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>618</v>
+      </c>
+      <c r="N141" s="2"/>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>79</v>
@@ -18717,19 +18870,19 @@
         <v>79</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>159</v>
+        <v>616</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI141" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK141" t="s" s="2">
         <v>79</v>
@@ -18738,7 +18891,7 @@
         <v>79</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>79</v>
@@ -18749,46 +18902,42 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>599</v>
+        <v>619</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>599</v>
+        <v>619</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>478</v>
+        <v>79</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H142" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I142" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>135</v>
+        <v>409</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>479</v>
+        <v>620</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O142" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>621</v>
+      </c>
+      <c r="N142" s="2"/>
+      <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
         <v>79</v>
       </c>
@@ -18836,25 +18985,25 @@
         <v>79</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>481</v>
+        <v>619</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH142" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI142" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK142" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>79</v>
+        <v>622</v>
       </c>
       <c r="AM142" t="s" s="2">
         <v>133</v>
@@ -18868,10 +19017,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>600</v>
+        <v>623</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>600</v>
+        <v>623</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18894,13 +19043,13 @@
         <v>79</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>361</v>
+        <v>409</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>601</v>
+        <v>624</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>602</v>
+        <v>625</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -18951,7 +19100,7 @@
         <v>79</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>600</v>
+        <v>623</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -18969,10 +19118,10 @@
         <v>79</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>603</v>
+        <v>626</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>369</v>
+        <v>133</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>79</v>
@@ -18983,10 +19132,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>604</v>
+        <v>627</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>604</v>
+        <v>627</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18997,7 +19146,7 @@
         <v>80</v>
       </c>
       <c r="G144" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H144" t="s" s="2">
         <v>79</v>
@@ -19009,13 +19158,13 @@
         <v>79</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>605</v>
+        <v>195</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>606</v>
+        <v>628</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>607</v>
+        <v>629</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
@@ -19042,13 +19191,13 @@
         <v>79</v>
       </c>
       <c r="X144" t="s" s="2">
-        <v>79</v>
+        <v>306</v>
       </c>
       <c r="Y144" t="s" s="2">
-        <v>79</v>
+        <v>630</v>
       </c>
       <c r="Z144" t="s" s="2">
-        <v>79</v>
+        <v>631</v>
       </c>
       <c r="AA144" t="s" s="2">
         <v>79</v>
@@ -19066,13 +19215,13 @@
         <v>79</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>604</v>
+        <v>627</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH144" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI144" t="s" s="2">
         <v>79</v>
@@ -19084,10 +19233,10 @@
         <v>79</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>608</v>
+        <v>632</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>609</v>
+        <v>133</v>
       </c>
       <c r="AN144" t="s" s="2">
         <v>79</v>
@@ -19098,10 +19247,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>610</v>
+        <v>633</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>610</v>
+        <v>633</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19124,13 +19273,13 @@
         <v>79</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>407</v>
+        <v>195</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>611</v>
+        <v>634</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>612</v>
+        <v>635</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -19157,13 +19306,13 @@
         <v>79</v>
       </c>
       <c r="X145" t="s" s="2">
-        <v>79</v>
+        <v>306</v>
       </c>
       <c r="Y145" t="s" s="2">
-        <v>79</v>
+        <v>636</v>
       </c>
       <c r="Z145" t="s" s="2">
-        <v>79</v>
+        <v>637</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>79</v>
@@ -19181,7 +19330,7 @@
         <v>79</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>610</v>
+        <v>633</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -19199,10 +19348,10 @@
         <v>79</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>613</v>
+        <v>79</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>614</v>
+        <v>133</v>
       </c>
       <c r="AN145" t="s" s="2">
         <v>79</v>
@@ -19213,10 +19362,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>615</v>
+        <v>638</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>615</v>
+        <v>638</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19239,15 +19388,17 @@
         <v>79</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>468</v>
+        <v>515</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>616</v>
+        <v>639</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="N146" s="2"/>
+        <v>640</v>
+      </c>
+      <c r="N146" t="s" s="2">
+        <v>641</v>
+      </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
         <v>79</v>
@@ -19296,7 +19447,7 @@
         <v>79</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>615</v>
+        <v>638</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -19314,10 +19465,10 @@
         <v>79</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>79</v>
+        <v>642</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>133</v>
+        <v>643</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>79</v>
@@ -19328,10 +19479,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>618</v>
+        <v>644</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>618</v>
+        <v>644</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19443,10 +19594,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>619</v>
+        <v>645</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>619</v>
+        <v>645</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19560,14 +19711,14 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>620</v>
+        <v>646</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>620</v>
+        <v>646</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
-        <v>478</v>
+        <v>525</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
@@ -19589,10 +19740,10 @@
         <v>135</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>479</v>
+        <v>526</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>480</v>
+        <v>527</v>
       </c>
       <c r="N149" t="s" s="2">
         <v>171</v>
@@ -19647,7 +19798,7 @@
         <v>79</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>481</v>
+        <v>528</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -19679,10 +19830,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>621</v>
+        <v>647</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>621</v>
+        <v>647</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19705,13 +19856,13 @@
         <v>79</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>151</v>
+        <v>409</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>622</v>
+        <v>648</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>623</v>
+        <v>649</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -19738,11 +19889,13 @@
         <v>79</v>
       </c>
       <c r="X150" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="Y150" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y150" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z150" t="s" s="2">
-        <v>624</v>
+        <v>79</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>79</v>
@@ -19760,7 +19913,7 @@
         <v>79</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>621</v>
+        <v>647</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -19778,10 +19931,10 @@
         <v>79</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>79</v>
+        <v>650</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>133</v>
+        <v>417</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>79</v>
@@ -19792,10 +19945,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>625</v>
+        <v>651</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>625</v>
+        <v>651</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -19818,13 +19971,13 @@
         <v>79</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>429</v>
+        <v>652</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>626</v>
+        <v>653</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>627</v>
+        <v>654</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -19875,7 +20028,7 @@
         <v>79</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>625</v>
+        <v>651</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -19893,10 +20046,10 @@
         <v>79</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>79</v>
+        <v>655</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>133</v>
+        <v>656</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>79</v>
@@ -19907,10 +20060,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>628</v>
+        <v>657</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>628</v>
+        <v>657</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19921,7 +20074,7 @@
         <v>80</v>
       </c>
       <c r="G152" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H152" t="s" s="2">
         <v>79</v>
@@ -19933,13 +20086,13 @@
         <v>79</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>195</v>
+        <v>376</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>629</v>
+        <v>658</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>630</v>
+        <v>659</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -19966,13 +20119,13 @@
         <v>79</v>
       </c>
       <c r="X152" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="Y152" t="s" s="2">
-        <v>631</v>
+        <v>79</v>
       </c>
       <c r="Z152" t="s" s="2">
-        <v>632</v>
+        <v>79</v>
       </c>
       <c r="AA152" t="s" s="2">
         <v>79</v>
@@ -19990,13 +20143,13 @@
         <v>79</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>628</v>
+        <v>657</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH152" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI152" t="s" s="2">
         <v>79</v>
@@ -20008,10 +20161,10 @@
         <v>79</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>79</v>
+        <v>660</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>133</v>
+        <v>661</v>
       </c>
       <c r="AN152" t="s" s="2">
         <v>79</v>
@@ -20022,10 +20175,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>633</v>
+        <v>662</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>633</v>
+        <v>662</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20033,10 +20186,10 @@
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G153" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H153" t="s" s="2">
         <v>79</v>
@@ -20048,17 +20201,15 @@
         <v>79</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>634</v>
+        <v>515</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>635</v>
+        <v>663</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>637</v>
-      </c>
+        <v>664</v>
+      </c>
+      <c r="N153" s="2"/>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
         <v>79</v>
@@ -20095,23 +20246,25 @@
         <v>79</v>
       </c>
       <c r="AB153" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="AC153" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC153" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD153" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE153" t="s" s="2">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>633</v>
+        <v>662</v>
       </c>
       <c r="AG153" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH153" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI153" t="s" s="2">
         <v>79</v>
@@ -20137,14 +20290,12 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>638</v>
+        <v>665</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="C154" t="s" s="2">
-        <v>639</v>
-      </c>
+        <v>665</v>
+      </c>
+      <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
         <v>79</v>
       </c>
@@ -20165,17 +20316,15 @@
         <v>79</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>640</v>
+        <v>151</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>641</v>
+        <v>152</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>637</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N154" s="2"/>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
         <v>79</v>
@@ -20224,10 +20373,10 @@
         <v>79</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>633</v>
+        <v>154</v>
       </c>
       <c r="AG154" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH154" t="s" s="2">
         <v>90</v>
@@ -20236,7 +20385,7 @@
         <v>79</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK154" t="s" s="2">
         <v>79</v>
@@ -20245,7 +20394,7 @@
         <v>79</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="AN154" t="s" s="2">
         <v>79</v>
@@ -20256,21 +20405,21 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>642</v>
+        <v>666</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>642</v>
+        <v>666</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G155" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H155" t="s" s="2">
         <v>79</v>
@@ -20282,16 +20431,16 @@
         <v>79</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>634</v>
+        <v>135</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>643</v>
+        <v>169</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>644</v>
+        <v>170</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>637</v>
+        <v>171</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -20341,33 +20490,846 @@
         <v>79</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>642</v>
+        <v>159</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH155" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI155" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ155" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM155" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AN155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO155" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="B156" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="C156" s="2"/>
+      <c r="D156" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="E156" s="2"/>
+      <c r="F156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G156" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H156" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I156" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J156" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K156" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L156" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="M156" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="N156" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="O156" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="P156" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q156" s="2"/>
+      <c r="R156" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S156" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T156" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U156" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V156" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W156" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X156" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y156" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z156" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA156" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB156" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC156" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD156" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE156" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF156" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AG156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH156" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI156" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ156" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK156" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL156" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM156" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN156" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO156" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="B157" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="C157" s="2"/>
+      <c r="D157" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E157" s="2"/>
+      <c r="F157" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G157" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H157" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I157" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J157" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K157" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="L157" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="M157" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="N157" s="2"/>
+      <c r="O157" s="2"/>
+      <c r="P157" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q157" s="2"/>
+      <c r="R157" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S157" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T157" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U157" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V157" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W157" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X157" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="Y157" s="2"/>
+      <c r="Z157" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="AA157" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB157" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC157" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD157" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE157" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF157" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="AG157" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH157" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI157" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ157" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AK155" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL155" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM155" t="s" s="2">
+      <c r="AK157" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL157" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM157" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="AN155" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO155" t="s" s="2">
+      <c r="AN157" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO157" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="B158" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="C158" s="2"/>
+      <c r="D158" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E158" s="2"/>
+      <c r="F158" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G158" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H158" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I158" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J158" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K158" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="L158" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="M158" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="N158" s="2"/>
+      <c r="O158" s="2"/>
+      <c r="P158" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q158" s="2"/>
+      <c r="R158" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S158" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T158" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U158" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V158" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W158" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X158" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y158" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z158" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA158" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB158" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC158" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD158" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE158" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF158" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="AG158" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH158" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI158" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ158" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK158" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL158" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM158" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN158" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO158" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="C159" s="2"/>
+      <c r="D159" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E159" s="2"/>
+      <c r="F159" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G159" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H159" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I159" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J159" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K159" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L159" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="M159" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="N159" s="2"/>
+      <c r="O159" s="2"/>
+      <c r="P159" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q159" s="2"/>
+      <c r="R159" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S159" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T159" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U159" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V159" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W159" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X159" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="Y159" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="Z159" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="AA159" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB159" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC159" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD159" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE159" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF159" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="AG159" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH159" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI159" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ159" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK159" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL159" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM159" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN159" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO159" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="C160" s="2"/>
+      <c r="D160" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E160" s="2"/>
+      <c r="F160" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G160" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H160" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I160" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J160" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K160" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="L160" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="M160" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="N160" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="O160" s="2"/>
+      <c r="P160" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q160" s="2"/>
+      <c r="R160" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S160" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T160" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U160" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V160" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W160" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X160" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y160" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z160" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA160" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB160" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AC160" s="2"/>
+      <c r="AD160" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE160" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AF160" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="AG160" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH160" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI160" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ160" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK160" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL160" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM160" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN160" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO160" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="B161" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="C161" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="D161" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E161" s="2"/>
+      <c r="F161" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G161" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H161" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I161" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J161" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K161" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="L161" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="M161" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="N161" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="O161" s="2"/>
+      <c r="P161" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q161" s="2"/>
+      <c r="R161" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S161" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T161" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U161" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V161" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W161" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X161" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y161" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z161" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA161" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB161" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC161" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD161" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE161" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF161" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="AG161" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH161" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI161" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ161" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK161" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL161" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM161" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN161" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO161" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="B162" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="C162" s="2"/>
+      <c r="D162" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E162" s="2"/>
+      <c r="F162" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G162" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H162" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I162" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J162" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K162" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="L162" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="M162" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="N162" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="O162" s="2"/>
+      <c r="P162" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q162" s="2"/>
+      <c r="R162" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S162" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T162" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U162" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V162" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W162" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X162" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y162" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z162" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA162" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB162" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC162" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD162" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE162" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF162" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="AG162" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH162" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI162" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ162" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK162" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL162" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM162" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN162" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO162" t="s" s="2">
         <v>79</v>
       </c>
     </row>

--- a/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
+++ b/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T16:55:52+00:00</t>
+    <t>2026-08-03T09:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
+++ b/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T09:04:08+00:00</t>
+    <t>2026-08-04T12:14:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
